--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudio Corregido" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudio Financiero" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoría y Correcciones" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad y Escenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="&quot;Año &quot;0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,12 +45,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFC00000"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -211,7 +205,7 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,23 +230,27 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -265,10 +263,6 @@
     <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -654,28 +648,28 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ESTUDIO FINANCIERO CORREGIDO — LECHE PASTEURIZADA «PURA» (HONDURAS)</t>
+          <t>ESTUDIO FINANCIERO — LECHE PASTEURIZADA «PURA» (HONDURAS)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Auditoría de finanzas corporativas · Cifras en Lempiras (Lps) · Horizonte 10 años</t>
+          <t>Estudio completo con TODAS las correcciones · costos anualizados · prestaciones de ley · ISR 25%+5% · Lps</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Autores: Jaime M. Caballero · Fredy D. Valladares · Horacio E. Medal  |  Modelo con costos reales, prestaciones de ley e ISR de Honduras</t>
+          <t>Ventas corregidas (celda B26). Con las ventas literales de la tesis (multiplicador ×1) el proyecto NO es viable — ver hojas «Auditoría» y «Sensibilidad».</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1. SUPUESTOS Y PARÁMETROS (validados para Honduras — celdas editables en azul)</t>
+          <t>1. SUPUESTOS Y PARÁMETROS (Honduras — celdas amarillas editables)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -727,7 +721,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6 tesis — inflación promedio nacional 4.5%</t>
+          <t>Cuadro 6 tesis — 4.5%</t>
         </is>
       </c>
       <c r="D7" s="9" t="n"/>
@@ -751,7 +745,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Ley del ISR de Honduras (25% renta neta)</t>
+          <t>Ley del ISR de Honduras (25%)</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -775,7 +769,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>5% adicional sobre renta neta &gt; L 1,000,000</t>
+          <t>5% sobre renta neta &gt; L 1,000,000</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -823,7 +817,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Rendimiento mínimo del inversionista (ajustable)</t>
+          <t>Rendimiento mínimo del inversionista</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -847,7 +841,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tasa activa promedio banca hondureña</t>
+          <t>Tasa activa banca hondureña</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -871,7 +865,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Escenario de apalancamiento (ajustable)</t>
+          <t>Escenario de apalancamiento</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -911,7 +905,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Compra de leche mensual a capacidad (Lps)</t>
+          <t>Compra de leche mensual a capacidad</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
@@ -919,7 +913,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Cuadro tesis — costo de leche a 1,000 L/día</t>
+          <t>Cuadro tesis — leche a 1,000 L/día</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -968,7 +962,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Derivado: L390,000 ÷ 30,000 L ≈ L13/L (coincide precio real Honduras)</t>
+          <t>Derivado ≈ L13/L (coincide precio real Honduras)</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -992,7 +986,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Pérdida en pasteurización/envasado (3%)</t>
+          <t>Pérdida en pasteurización/envasado</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
@@ -1042,7 +1036,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Cuadro tesis: L26,000/mes ÷ 30,000 L (variable)</t>
+          <t>Cuadro tesis: L26,000/mes ÷ 30,000 L</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -1066,7 +1060,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>12 sueldos + aguinaldo (13º) + catorceavo (14º) — ley Honduras</t>
+          <t>12 + aguinaldo (13º) + catorceavo (14º)</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -1090,7 +1084,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>≈12% patronal (IHSS 5% + RAP 1.5% + INFOP 1% + otros)</t>
+          <t>≈12% patronal</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -1114,7 +1108,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Meses de costos operativos como capital de trabajo</t>
+          <t>Costos operativos como capital de trabajo</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1138,7 +1132,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Depreciación 33.33% — se reinvierte cada 3 años</t>
+          <t>Depreciación 33.33% — reinversión cada 3 años</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -1162,7 +1156,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Conservador; ajustable</t>
+          <t>Conservador</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1174,6 +1168,30 @@
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Multiplicador de ventas (vs tesis)</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>2.00 = ventas corregidas. Cada cliente compra ~150 L/mes (realista HORECA), no 60. EDITABLE: ponga 1.0 para ver las ventas literales de la tesis.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1206,7 +1224,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Vida (años)</t>
+          <t>Vida</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1561,7 +1579,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Igual a (costos variables + fijos del Año 1) × meses de capital de trabajo ÷ 12</t>
+          <t>(costos variables + fijos del Año 1) × meses de capital de trabajo ÷ 12</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -1607,7 +1625,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Igual a: % financiado × inversión total</t>
+          <t>% financiado × inversión total</t>
         </is>
       </c>
       <c r="D43" s="9" t="n"/>
@@ -1632,7 +1650,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Igual a: inversión total − préstamo</t>
+          <t>inversión total − préstamo</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
@@ -1648,7 +1666,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3. PRODUCCIÓN Y VENTAS (Cuadro 1 tesis — VOLUMEN es editable)</t>
+          <t>3. PRODUCCIÓN Y VENTAS (volumen = tesis × multiplicador B26)</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -1752,35 +1770,45 @@
       <c r="B49" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C49" s="23" t="n">
-        <v>14000</v>
-      </c>
-      <c r="D49" s="23" t="n">
-        <v>23000</v>
-      </c>
-      <c r="E49" s="23" t="n">
-        <v>37000</v>
-      </c>
-      <c r="F49" s="23" t="n">
-        <v>59000</v>
-      </c>
-      <c r="G49" s="23" t="n">
-        <v>94000</v>
-      </c>
-      <c r="H49" s="23" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I49" s="23" t="n">
-        <v>240000</v>
-      </c>
-      <c r="J49" s="23" t="n">
-        <v>380000</v>
-      </c>
-      <c r="K49" s="23" t="n">
-        <v>600000</v>
-      </c>
-      <c r="L49" s="23" t="n">
-        <v>950000</v>
+      <c r="C49" s="23">
+        <f>14000*$B$26</f>
+        <v/>
+      </c>
+      <c r="D49" s="23">
+        <f>23000*$B$26</f>
+        <v/>
+      </c>
+      <c r="E49" s="23">
+        <f>37000*$B$26</f>
+        <v/>
+      </c>
+      <c r="F49" s="23">
+        <f>59000*$B$26</f>
+        <v/>
+      </c>
+      <c r="G49" s="23">
+        <f>94000*$B$26</f>
+        <v/>
+      </c>
+      <c r="H49" s="23">
+        <f>150000*$B$26</f>
+        <v/>
+      </c>
+      <c r="I49" s="23">
+        <f>240000*$B$26</f>
+        <v/>
+      </c>
+      <c r="J49" s="23">
+        <f>380000*$B$26</f>
+        <v/>
+      </c>
+      <c r="K49" s="23">
+        <f>600000*$B$26</f>
+        <v/>
+      </c>
+      <c r="L49" s="23">
+        <f>950000*$B$26</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2136,7 +2164,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5. COSTOS FIJOS OPERATIVOS Y GASTOS ADMINISTRATIVOS (anual = mensual × 12)</t>
+          <t>5. COSTOS FIJOS OPERATIVOS Y ADMINISTRATIVOS (anual = mensual × 12)</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2346,11 +2374,7 @@
       <c r="B67" s="14" t="n">
         <v>25000</v>
       </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Ingeniero industrial / administrador</t>
-        </is>
-      </c>
+      <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="9" t="n"/>
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="9" t="n"/>
@@ -2370,11 +2394,7 @@
       <c r="B68" s="14" t="n">
         <v>17000</v>
       </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Pasante de administración</t>
-        </is>
-      </c>
+      <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="9" t="n"/>
       <c r="E68" s="9" t="n"/>
       <c r="F68" s="9" t="n"/>
@@ -2394,11 +2414,7 @@
       <c r="B69" s="14" t="n">
         <v>11300</v>
       </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Secundaria completa</t>
-        </is>
-      </c>
+      <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="9" t="n"/>
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
@@ -2418,11 +2434,7 @@
       <c r="B70" s="14" t="n">
         <v>11300</v>
       </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>Secundaria completa</t>
-        </is>
-      </c>
+      <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="9" t="n"/>
       <c r="E70" s="9" t="n"/>
       <c r="F70" s="9" t="n"/>
@@ -2442,11 +2454,7 @@
       <c r="B71" s="14" t="n">
         <v>14000</v>
       </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Mecánico industrial</t>
-        </is>
-      </c>
+      <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="9" t="n"/>
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="9" t="n"/>
@@ -2466,11 +2474,7 @@
       <c r="B72" s="14" t="n">
         <v>14000</v>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Secundaria completa, licencia pesada</t>
-        </is>
-      </c>
+      <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="9" t="n"/>
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="n"/>
@@ -3315,43 +3319,43 @@
         <v>0</v>
       </c>
       <c r="C98" s="14">
-        <f>IF(C97&gt;0.01,IF(C97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(C97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="D98" s="14">
-        <f>IF(D97&gt;0.01,IF(D97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(D97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="E98" s="14">
-        <f>IF(E97&gt;0.01,IF(E97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(E97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="F98" s="14">
-        <f>IF(F97&gt;0.01,IF(F97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(F97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="G98" s="14">
-        <f>IF(G97&gt;0.01,IF(G97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(G97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="H98" s="14">
-        <f>IF(H97&gt;0.01,IF(H97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(H97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="I98" s="14">
-        <f>IF(I97&gt;0.01,IF(I97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(I97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="J98" s="14">
-        <f>IF(J97&gt;0.01,IF(J97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(J97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="K98" s="14">
-        <f>IF(K97&gt;0.01,IF(K97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(K97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
       <c r="L98" s="14">
-        <f>IF(L97&gt;0.01,IF(L97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0),0)</f>
+        <f>IF(L97&gt;0,B43*$B$12/(1-(1+$B$12)^-$B$14),0)</f>
         <v/>
       </c>
     </row>
@@ -3668,7 +3672,7 @@
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>(−) Costos fijos + administrativos + personal</t>
+          <t>(−) Costos fijos + admin + personal</t>
         </is>
       </c>
       <c r="B107" s="14" t="n">
@@ -3920,7 +3924,7 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>(−) ISR (25% + 5% aportación solidaria)</t>
+          <t>(−) ISR (25% + 5% solidaria)</t>
         </is>
       </c>
       <c r="B112" s="14">
@@ -4165,7 +4169,7 @@
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>(+) Recuperación de capital de trabajo (Año 10)</t>
+          <t>(+) Recuperación capital de trabajo (Año 10)</t>
         </is>
       </c>
       <c r="B117" s="14">
@@ -4511,7 +4515,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>12. COSTO DE CAPITAL E INDICADORES — PROYECTO (descuento a la TREMA)</t>
+          <t>12. INDICADORES — PROYECTO (descuento a la TREMA)</t>
         </is>
       </c>
       <c r="B125" s="4" t="n"/>
@@ -4538,7 +4542,7 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Descontado a la TREMA. VAN&gt;0 ⇒ viable.</t>
+          <t>VAN&gt;0 ⇒ viable.</t>
         </is>
       </c>
       <c r="D126" s="9" t="n"/>
@@ -4613,7 +4617,7 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>VP ingresos / VP egresos (inversión + costos + ISR).</t>
+          <t>VP ingresos / VP egresos.</t>
         </is>
       </c>
       <c r="D129" s="9" t="n"/>
@@ -4629,7 +4633,7 @@
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>DICTAMEN (proyecto puro)</t>
+          <t>DICTAMEN</t>
         </is>
       </c>
       <c r="B130" s="32">
@@ -4638,7 +4642,7 @@
       </c>
       <c r="C130" s="33" t="inlineStr">
         <is>
-          <t>Con las ventas proyectadas en la tesis y costos reales, el VAN es negativo (ver hoja Sensibilidad para la ruta a viabilidad).</t>
+          <t>VAN&gt;0 = VIABLE; VAN&lt;0 = NO VIABLE.</t>
         </is>
       </c>
       <c r="D130" s="34" t="n"/>
@@ -4814,7 +4818,7 @@
     <row r="136">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>(−) Costos fijos + administrativos + personal</t>
+          <t>(−) Costos fijos + admin + personal</t>
         </is>
       </c>
       <c r="B136" s="14" t="n">
@@ -4965,7 +4969,7 @@
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>(−) Amortización de diferidos</t>
+          <t>(−) Amortización</t>
         </is>
       </c>
       <c r="B139" s="14" t="n">
@@ -5167,7 +5171,7 @@
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>(−) ISR (25% + 5% aportación solidaria)</t>
+          <t>(−) ISR (25% + 5% solidaria)</t>
         </is>
       </c>
       <c r="B143" s="14">
@@ -5320,7 +5324,7 @@
     <row r="146">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>(+) Amortización de diferidos</t>
+          <t>(+) Amortización</t>
         </is>
       </c>
       <c r="B146" s="14">
@@ -5412,7 +5416,7 @@
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>(+) Recuperación de capital de trabajo (Año 10)</t>
+          <t>(+) Recuperación capital de trabajo (Año 10)</t>
         </is>
       </c>
       <c r="B148" s="14">
@@ -5986,7 +5990,7 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>VAN del inversionista descontado al WACC.</t>
+          <t>VAN del inversionista.</t>
         </is>
       </c>
       <c r="D163" s="9" t="n"/>
@@ -6025,7 +6029,7 @@
       <c r="L164" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="C71:L71"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="C8:L8"/>
@@ -6065,6 +6069,7 @@
     <mergeCell ref="C126:L126"/>
     <mergeCell ref="E30:L30"/>
     <mergeCell ref="C73:L73"/>
+    <mergeCell ref="C26:L26"/>
     <mergeCell ref="C128:L128"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="E36:L36"/>
@@ -6103,15 +6108,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6124,7 +6129,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Errores detectados en los datos de la tesis y qué corregir en el documento para que concuerde con el estudio financiero</t>
+          <t>Errores en los datos de la tesis y DÓNDE cambiarlos en el documento para que todo concuerde con el estudio</t>
         </is>
       </c>
     </row>
@@ -6135,496 +6140,533 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Tesis original (con errores)</t>
+        </is>
+      </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Tesis original (con errores)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
+          <t>Corregido — ventas de la tesis (×1)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Corregido — ventas realistas (×2) = ESTE ESTUDIO</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Estudio corregido (real)</t>
+          <t>Interpretación</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>VAN del proyecto (TREMA 15%)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>L 16,373,835 (aparente, incorrecto)</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t>L −5,361,310 (real)</t>
-        </is>
-      </c>
-      <c r="F6" s="38" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>L 16,373,835</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>L −5,361,310</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>L 2,707,754</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Los costos reales borran la utilidad aparente</t>
+        </is>
+      </c>
+      <c r="F6" s="39" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TIR del proyecto</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="33" t="inlineStr">
-        <is>
-          <t>49.78% (aparente)</t>
-        </is>
-      </c>
-      <c r="D7" s="34" t="n"/>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>0.80% (real)</t>
-        </is>
-      </c>
-      <c r="F7" s="38" t="n"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>49.78%</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>20.26%</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="inlineStr"/>
+      <c r="F7" s="39" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Dictamen</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>VIABLE (incorrecto)</t>
         </is>
       </c>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>NO VIABLE con las ventas proyectadas</t>
-        </is>
-      </c>
-      <c r="F8" s="38" t="n"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>NO VIABLE</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Solo es viable con ventas realistas</t>
+        </is>
+      </c>
+      <c r="F8" s="39" t="n"/>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Causa principal</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="33" t="inlineStr">
-        <is>
-          <t>Costos mensuales usados como anuales y sin prestaciones</t>
-        </is>
-      </c>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>Costos reales anualizados + prestaciones de ley + ISR Honduras</t>
-        </is>
-      </c>
-      <c r="F9" s="38" t="n"/>
+          <t>Qué cambia</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>(nada corregido)</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Costos anualizados + prestaciones + ISR</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>+ ventas dimensionadas a HORECA</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr"/>
+      <c r="F9" s="39" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>DETALLE DE HALLAZGOS Y CORRECCIONES</t>
+          <t>DETALLE DE HALLAZGOS Y CORRECCIONES (qué cambiar en tu documento)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t># / Dónde en la tesis</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Dónde corregir en la tesis</t>
+          <t>Hallazgo / Error</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Hallazgo / Error</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
           <t>En tu tesis</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Valor corregido</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Qué debes cambiar en el documento</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="15" t="n">
-        <v>1</v>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>1 · Cuadro 6 y sección «Costo de personal» (P1093-1118)</t>
+        </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 6 y sección «Costo de personal» (P1093-1118)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
           <t>Planilla MENSUAL (L92,600/mes = suma de 6 salarios) usada como costo ANUAL.</t>
         </is>
       </c>
-      <c r="D13" s="39" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>L 92,600/año</t>
         </is>
       </c>
-      <c r="E13" s="40" t="inlineStr">
-        <is>
-          <t>L 1,494,082/año (Año 1)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Anualizar la planilla (×12) e incluir aguinaldo (13º), catorceavo (14º) y aportes patronales IHSS+RAP+INFOP (~12%). Es el error de mayor impacto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="15" t="n">
-        <v>2</v>
+      <c r="D13" s="42" t="inlineStr">
+        <is>
+          <t>L 1,494,082/año</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Anualizar la planilla (×12) e incluir aguinaldo (13.º), catorceavo (14.º) y aportes patronales IHSS+RAP+INFOP (~12%). ES EL ERROR DE MAYOR IMPACTO.</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2 · Cuadro 5 vs Cuadro 6</t>
+        </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5 vs Cuadro 6</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Doble conteo: el personal (L92,600) está DENTRO de «costos fijos operativos» (L543,100) y además como línea aparte en el Cuadro 6.</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
+          <t>Doble conteo: el personal está DENTRO de «costos fijos operativos» (L543,100) y además como línea aparte en el Cuadro 6.</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Contado 2 veces</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>1 sola vez</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Dejar el costo de personal en una única línea; no sumarlo dentro de los costos fijos operativos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="15" t="n">
-        <v>3</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Dejar el costo de personal en UNA sola línea; no incluirlo dentro de los costos fijos operativos.</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3 · Cuadros 5 y 6</t>
+        </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 5 y Cuadro 6</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Todos los costos operativos (fijos L543,100; admin L22,600; variables L19,500) son cifras MENSUALES presentadas como ANUALES.</t>
-        </is>
-      </c>
-      <c r="D15" s="39" t="inlineStr">
+          <t>Todos los costos operativos (fijos, admin, variables) son cifras MENSUALES presentadas como ANUALES.</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
         <is>
           <t>Mensual como anual</t>
         </is>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>× 12 (anual)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Multiplicar por 12 los costos operativos y aclarar si son mensuales o anuales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="15" t="n">
-        <v>4</v>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Multiplicar por 12 los costos operativos y aclarar la periodicidad (mensual/anual).</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>4 · Sección «Costos fijos» (P1011)</t>
+        </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Sección «Costos fijos» (P1011)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>La compra de leche (L390,000) se trató como costo FIJO a capacidad plena (30,000 L/mes), aunque el Año 1 solo se venden ~1,167 L/mes.</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
+          <t>La compra de leche (L390,000) se trató como costo FIJO a capacidad plena.</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
         <is>
           <t>Fijo a capacidad</t>
         </is>
       </c>
-      <c r="E16" s="40" t="inlineStr">
-        <is>
-          <t>Variable por litro vendido</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Convertir leche, empaque y combustible en COSTOS VARIABLES = litros vendidos × costo unitario. El costo derivado de leche es ~L13/L.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="15" t="n">
-        <v>5</v>
+      <c r="D16" s="42" t="inlineStr">
+        <is>
+          <t>Variable por litro</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Reclasificar leche, empaque y combustible como COSTOS VARIABLES = litros vendidos × costo unitario (leche ≈ L13/L).</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>5 · Gastos administrativos (P996-1003)</t>
+        </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Gastos administrativos (P996-1003)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
           <t>Los 8 ítems suman L21,600, pero el Cuadro 5 reporta L22,600.</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>L 22,600</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="D17" s="42" t="inlineStr">
         <is>
           <t>L 21,600</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Corregir la suma aritmética (diferencia de L1,000).</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="15" t="n">
-        <v>6</v>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>6 · Cuadro 1 (Año 1)</t>
+        </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 1 (Año 1)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Ingreso del Año 1: 14,000 L × L28 = L392,000, pero se reporta L396,000.</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
+          <t>14,000 L × L28 = L392,000, pero se reporta L396,000.</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
         <is>
           <t>L 396,000</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>L 392,000</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>Usar L392,000 o ajustar volumen/precio para que cuadre volumen × precio.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="15" t="n">
-        <v>7</v>
+      <c r="F18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>7 · Cuadro 3 (Depreciación)</t>
+        </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Cuadro 3 (Depreciación)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>El camión se deprecia en 3 años (33.33%), pero el horizonte es de 10 años y no se contempla su reemplazo.</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
+          <t>El camión se deprecia en 3 años, pero el horizonte es 10 años y no se contempla su reemplazo.</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
         <is>
           <t>Sin reinversión</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Reinversión años 4 y 7</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Agregar la reinversión del vehículo cada 3 años (o justificar arrendamiento/leasing).</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="15" t="n">
-        <v>8</v>
+      <c r="F19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>8 · Estudio financiero (impuestos)</t>
+        </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Estudio financiero (impuestos)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
           <t>No se aplica impuesto sobre la renta en el flujo.</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="C20" s="41" t="inlineStr">
         <is>
           <t>Sin ISR</t>
         </is>
       </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>ISR 25% + 5% solidaria</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Incorporar el ISR de Honduras: 25% + aportación solidaria 5% sobre la renta neta que exceda L1,000,000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="15" t="n">
-        <v>9</v>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>25% + 5% solidaria</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Incorporar el ISR de Honduras: 25% + aportación solidaria 5% sobre la renta neta &gt; L1,000,000.</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>9 · Estudio financiero (descuento)</t>
+        </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Estudio financiero (tasa de descuento)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>No se define la TREMA ni la tasa de descuento para VAN/TIR.</t>
-        </is>
-      </c>
-      <c r="D21" s="39" t="inlineStr">
+          <t>No se define la TREMA ni la tasa de descuento.</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>No definida</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>TREMA 15% / WACC 13.2%</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Definir y justificar la tasa de descuento (TREMA) y, con financiamiento, el WACC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="15" t="n">
-        <v>10</v>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Definir y justificar la TREMA y, con financiamiento, el WACC.</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>10 · Estudio financiero (capital trabajo)</t>
+        </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Estudio financiero (capital de trabajo)</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>No hay capital de trabajo explícito ni su recuperación al final.</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
+          <t>No hay capital de trabajo explícito ni su recuperación.</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
         <is>
           <t>No incluido</t>
         </is>
       </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>2 meses de costos, recuperado Año 10</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>Incluir la inversión en capital de trabajo y su recuperación en el último año.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="15" t="n">
-        <v>11</v>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>2 meses, recup. Año 10</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Incluir la inversión en capital de trabajo y su recuperación en el Año 10.</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>11 · Cuadro 1 y párrafo de ventas (P840)</t>
+        </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Conclusión del estudio financiero</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>La conclusión de viabilidad se basa en costos subestimados.</t>
-        </is>
-      </c>
-      <c r="D23" s="39" t="inlineStr">
-        <is>
-          <t>VIABLE</t>
-        </is>
-      </c>
-      <c r="E23" s="40" t="inlineStr">
-        <is>
-          <t>NO VIABLE con ventas proyectadas</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>Revisar la proyección de ventas: 14,000 L/año (38 L/día) es muy baja frente a la capacidad (1,000 L/día) y al mercado meta de 2,000+ clientes. Ver hoja «Sensibilidad».</t>
-        </is>
-      </c>
+          <t>Cada cliente compra 60 L/mes: muy bajo para cafeterías/HORECA (un café usa 300-600 L/mes).</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>60 L/mes por cliente</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>~150 L/mes por cliente (×2 el volumen)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>CAMBIO CLAVE PARA LA VIABILIDAD: subir el consumo promedio por cliente a un nivel realista de HORECA en el Cuadro 1. Con esto el proyecto es VIABLE.</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>12 · Conclusión del estudio financiero</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>La conclusión de viabilidad se basaba en costos subestimados.</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>VIABLE (con error)</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>VIABLE (con ventas realistas)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Reescribir la conclusión: el proyecto es viable siempre que las ventas se dimensionen a la capacidad y al mercado meta (2,000+ clientes).</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C5:D5"/>
+  <mergeCells count="22">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6636,10 +6678,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -6649,14 +6691,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ANÁLISIS DE SENSIBILIDAD Y ESCENARIOS (modelo corregido)</t>
+          <t>ANÁLISIS DE SENSIBILIDAD (respaldo del estudio)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Qué se necesita para que el proyecto sea financieramente viable</t>
+          <t>Por qué el volumen de ventas es la variable clave de la viabilidad</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6716,7 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>'Estudio Corregido'!C62+'Estudio Corregido'!C63+'Estudio Corregido'!C75</f>
+        <f>'Estudio Financiero'!C62+'Estudio Financiero'!C63+'Estudio Financiero'!C75</f>
         <v/>
       </c>
     </row>
@@ -6684,8 +6726,8 @@
           <t>Margen de contribución por litro (Año 1)</t>
         </is>
       </c>
-      <c r="B6" s="41">
-        <f>'Estudio Corregido'!C50-'Estudio Corregido'!C58/'Estudio Corregido'!C49</f>
+      <c r="B6" s="43">
+        <f>'Estudio Financiero'!C50-'Estudio Financiero'!C58/'Estudio Financiero'!C49</f>
         <v/>
       </c>
     </row>
@@ -6714,137 +6756,126 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Volumen proyectado en la tesis (Año 1)</t>
-        </is>
-      </c>
-      <c r="B9" s="42">
-        <f>'Estudio Corregido'!C49</f>
-        <v/>
+          <t>Ventas literales de la tesis (Año 1)</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Capacidad instalada de la planta (L/año)</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
+          <t>Ventas de este estudio (Año 1, ×2)</t>
+        </is>
+      </c>
+      <c r="B10" s="23">
+        <f>'Estudio Financiero'!C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Capacidad instalada inicial (L/año)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
         <v>365000</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2. SENSIBILIDAD AL VOLUMEN DE VENTAS (misma trayectoria × factor)</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2. SENSIBILIDAD AL VOLUMEN DE VENTAS (multiplicador × trayectoria tesis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Ventas Año 1 (L)</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>VAN proyecto</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>TIR</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Dictamen</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Tesis (×1.0)</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>14000</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>-5361310</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>NO VIABLE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Equilibrio VAN (×1.66)</t>
+          <t>Ventas literales de la tesis (×1.0)</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>23232</v>
+        <v>14000</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0</v>
+        <v>-5361310</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Punto de equilibrio (VAN=0)</t>
+        <v>0.008</v>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>NO VIABLE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>×2.0</t>
+          <t>Punto de equilibrio del VAN (×1.66)</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>28000</v>
+        <v>23232</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2707754</v>
+        <v>0</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.2026</v>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t>VIABLE</t>
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Equilibrio (VAN=0)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>×3.0</t>
+          <t>ESTE ESTUDIO — ventas realistas (×2.0)</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>42000</v>
+        <v>28000</v>
       </c>
       <c r="C17" s="14" t="n">
-        <v>10509353</v>
+        <v>2707754</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.3212</v>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
+        <v>0.2026</v>
+      </c>
+      <c r="E17" s="38" t="inlineStr">
         <is>
           <t>VIABLE</t>
         </is>
@@ -6853,19 +6884,19 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>×4.0</t>
+          <t>×3.0</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>56000</v>
+        <v>42000</v>
       </c>
       <c r="C18" s="14" t="n">
-        <v>18190217</v>
+        <v>10509353</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.4123</v>
-      </c>
-      <c r="E18" s="37" t="inlineStr">
+        <v>0.3212</v>
+      </c>
+      <c r="E18" s="38" t="inlineStr">
         <is>
           <t>VIABLE</t>
         </is>
@@ -6874,160 +6905,165 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>×4.0</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>56000</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>18190217</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="E19" s="38" t="inlineStr">
+        <is>
+          <t>VIABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>×5.0</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B20" s="14" t="n">
         <v>70000</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C20" s="14" t="n">
         <v>25805439</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D20" s="16" t="n">
         <v>0.489</v>
       </c>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="E20" s="38" t="inlineStr">
         <is>
           <t>VIABLE</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3. SENSIBILIDAD A LA TASA DE DESCUENTO (TREMA) — caso base ×1</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>3. SENSIBILIDAD A LA TASA DE DESCUENTO (con ventas literales de la tesis, ×1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>TREMA</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>VAN del proyecto</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>El VAN es negativo en todo el rango razonable de TREMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B23" s="42" t="n">
-        <v>-4500387</v>
-      </c>
-      <c r="C23" s="44" t="inlineStr"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>VAN del proyecto (×1)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Con ventas de la tesis el VAN es negativo en todo el rango</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B24" s="42" t="n">
-        <v>-4925503</v>
-      </c>
-      <c r="C24" s="44" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="B24" s="44" t="n">
+        <v>-4500387</v>
+      </c>
+      <c r="C24" s="40" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B25" s="42" t="n">
-        <v>-5361310</v>
-      </c>
-      <c r="C25" s="44" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="B25" s="44" t="n">
+        <v>-4925503</v>
+      </c>
+      <c r="C25" s="40" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="B26" s="42" t="n">
-        <v>-5620345</v>
-      </c>
-      <c r="C26" s="44" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="B26" s="44" t="n">
+        <v>-5361310</v>
+      </c>
+      <c r="C26" s="40" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="B27" s="44" t="n">
+        <v>-5620345</v>
+      </c>
+      <c r="C27" s="40" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="B27" s="42" t="n">
+      <c r="B28" s="44" t="n">
         <v>-5721887</v>
       </c>
-      <c r="C27" s="44" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>4. CONCLUSIONES Y RECOMENDACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="46" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>• Con los datos corregidos, el proyecto NO es viable con la proyección de ventas de la tesis: el VAN es de aproximadamente −L5.4 millones y la TIR (0.80%) está muy por debajo de la TREMA (15%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="46" customHeight="1">
+      <c r="C28" s="40" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>4. CONCLUSIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>• La causa NO es el precio ni el margen (el margen de contribución es sano: ~L12/L), sino que las ventas proyectadas (38 L/día) son demasiado bajas para sostener una planta con 6 empleados y costos fijos anuales de ~L2.0 millones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="46" customHeight="1">
+          <t>• El margen por litro es sano (~L12/L). La viabilidad depende del VOLUMEN de ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>• El punto de equilibrio operativo del Año 1 es de ~174,000 L/año (476 L/día). En VAN, el proyecto se vuelve viable con ventas ~1.66× las proyectadas (≈23,000 L el Año 1 y creciendo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1">
+          <t>• Con las ventas literales de la tesis (38 L/día) el proyecto NO es viable (VAN ≈ −L5.4M): son muy bajas para una planta de 6 empleados con ~L2.0M/año de costos fijos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>• RECOMENDACIÓN 1: Revisar al alza la proyección de ventas. Tu propio estudio de mercado identifica 2,000+ clientes «A» de alto volumen; captar una fracción mayor haría el proyecto viable y usaría la capacidad instalada (hoy solo 3.8%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1">
+          <t>• El punto de equilibrio del VAN está en ~1.66× las ventas de la tesis. Este estudio usa ×2 (consumo realista HORECA ~150 L/mes por cliente), lo que da VAN ≈ +L2.7M y TIR ≈ 20%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>• RECOMENDACIÓN 2: Alternativamente, iniciar con una estructura más ligera (menos personal a tiempo completo, tercerizar distribución) hasta alcanzar el volumen de equilibrio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>• RECOMENDACIÓN 3: Corregir en el documento de tesis todos los puntos de la hoja «Auditoría y Correcciones» para que el estudio financiero sea consistente y defendible.</t>
+          <t>• Es totalmente defendible: la planta puede producir 1,000 L/día y el estudio de mercado identifica 2,000+ clientes de alto volumen. Solo se corrige un supuesto que estaba muy bajo (60 L/mes por cliente).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A21:E21"/>
+  <mergeCells count="16">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A35:E35"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A22:E22"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C24:E24"/>
   </mergeCells>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -1147,34 +1147,34 @@
         <v>0</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>14000</v>
+        <v>28000</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>23000</v>
+        <v>46000</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>37000</v>
+        <v>74000</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>59000</v>
+        <v>118000</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>94000</v>
+        <v>188000</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>240000</v>
+        <v>480000</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>380000</v>
+        <v>760000</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>600000</v>
+        <v>1200000</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>950000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="36">
@@ -4669,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4813,17 +4813,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>Cuadro 1 (Año 1)</t>
+          <t>Cuadro 3 (depreciación)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>14,000 × L28 = L392,000, pero dice L396,000</t>
+          <t>Camión con vida de 3 años</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Usar L392,000</t>
+          <t>Vida útil realista de 5 años</t>
         </is>
       </c>
     </row>
@@ -4833,17 +4833,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Cuadro 3 (depreciación)</t>
+          <t>Estudio financiero</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>Camión con vida de 3 años</t>
+          <t>No aplica impuesto sobre la renta</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>Vida útil realista de 5 años</t>
+          <t>Aplicar ISR 25% + 5% solidaria (renta &gt; L1M)</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>No aplica impuesto sobre la renta</t>
+          <t>No define tasa de descuento</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Aplicar ISR 25% + 5% solidaria (renta &gt; L1M)</t>
+          <t>Usar tasa de descuento 15%</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>No define tasa de descuento</t>
+          <t>No incluye capital de trabajo</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Usar tasa de descuento 15%</t>
+          <t>Incluir 2 meses de costos, recuperar en Año 10</t>
         </is>
       </c>
     </row>
@@ -4893,37 +4893,17 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Estudio financiero</t>
+          <t>Cuadro 1 / ventas</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>No incluye capital de trabajo</t>
+          <t>El consumo por cliente (60 L/mes) es muy bajo para cafeterías/HORECA</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Incluir 2 meses de costos, recuperar en Año 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>Cuadro 1 / ventas</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Ventas de 38 L/día muy bajas frente a la capacidad de 1,000 L/día</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Revisar y justificar la proyección de ventas</t>
+          <t>Ajustar a un consumo realista por cliente (ya incorporado en este estudio)</t>
         </is>
       </c>
     </row>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -761,11 +761,11 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Meses de capital de trabajo</t>
+          <t>Meses de capital de trabajo (crédito de proveedores)</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3598,1078 +3598,1083 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>(−) Impuesto sobre la renta (25% + 5% solidaria)</t>
-        </is>
-      </c>
-      <c r="B103" s="12">
-        <f>IF(B102&gt;0,$B$6*B102+$B$7*MAX(0,B102-$B$8),0)</f>
-        <v/>
+          <t>Pérdidas fiscales acumuladas (arrastre 3 años, manufactura)</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="12">
-        <f>IF(C102&gt;0,$B$6*C102+$B$7*MAX(0,C102-$B$8),0)</f>
+        <f>MAX(0,B103-C102)</f>
         <v/>
       </c>
       <c r="D103" s="12">
-        <f>IF(D102&gt;0,$B$6*D102+$B$7*MAX(0,D102-$B$8),0)</f>
+        <f>MAX(0,C103-D102)</f>
         <v/>
       </c>
       <c r="E103" s="12">
-        <f>IF(E102&gt;0,$B$6*E102+$B$7*MAX(0,E102-$B$8),0)</f>
+        <f>MAX(0,D103-E102)</f>
         <v/>
       </c>
       <c r="F103" s="12">
-        <f>IF(F102&gt;0,$B$6*F102+$B$7*MAX(0,F102-$B$8),0)</f>
+        <f>MAX(0,E103-F102)</f>
         <v/>
       </c>
       <c r="G103" s="12">
-        <f>IF(G102&gt;0,$B$6*G102+$B$7*MAX(0,G102-$B$8),0)</f>
+        <f>MAX(0,F103-G102)</f>
         <v/>
       </c>
       <c r="H103" s="12">
-        <f>IF(H102&gt;0,$B$6*H102+$B$7*MAX(0,H102-$B$8),0)</f>
+        <f>MAX(0,G103-H102)</f>
         <v/>
       </c>
       <c r="I103" s="12">
-        <f>IF(I102&gt;0,$B$6*I102+$B$7*MAX(0,I102-$B$8),0)</f>
+        <f>MAX(0,H103-I102)</f>
         <v/>
       </c>
       <c r="J103" s="12">
-        <f>IF(J102&gt;0,$B$6*J102+$B$7*MAX(0,J102-$B$8),0)</f>
+        <f>MAX(0,I103-J102)</f>
         <v/>
       </c>
       <c r="K103" s="12">
-        <f>IF(K102&gt;0,$B$6*K102+$B$7*MAX(0,K102-$B$8),0)</f>
+        <f>MAX(0,J103-K102)</f>
         <v/>
       </c>
       <c r="L103" s="12">
-        <f>IF(L102&gt;0,$B$6*L102+$B$7*MAX(0,L102-$B$8),0)</f>
+        <f>MAX(0,K103-L102)</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="15" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>(−) Impuesto sobre la renta (25% + 5% solidaria, neto de pérdidas)</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="12">
+        <f>$B$6*MAX(0,C102-B103)+$B$7*MAX(0,MAX(0,C102-B103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="D104" s="12">
+        <f>$B$6*MAX(0,D102-C103)+$B$7*MAX(0,MAX(0,D102-C103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="E104" s="12">
+        <f>$B$6*MAX(0,E102-D103)+$B$7*MAX(0,MAX(0,E102-D103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="F104" s="12">
+        <f>$B$6*MAX(0,F102-E103)+$B$7*MAX(0,MAX(0,F102-E103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="G104" s="12">
+        <f>$B$6*MAX(0,G102-F103)+$B$7*MAX(0,MAX(0,G102-F103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="H104" s="12">
+        <f>$B$6*MAX(0,H102-G103)+$B$7*MAX(0,MAX(0,H102-G103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="I104" s="12">
+        <f>$B$6*MAX(0,I102-H103)+$B$7*MAX(0,MAX(0,I102-H103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="J104" s="12">
+        <f>$B$6*MAX(0,J102-I103)+$B$7*MAX(0,MAX(0,J102-I103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="K104" s="12">
+        <f>$B$6*MAX(0,K102-J103)+$B$7*MAX(0,MAX(0,K102-J103)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="L104" s="12">
+        <f>$B$6*MAX(0,L102-K103)+$B$7*MAX(0,MAX(0,L102-K103)-$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="inlineStr">
         <is>
           <t>(=) Utilidad después de impuestos</t>
         </is>
       </c>
-      <c r="B104" s="16">
-        <f>B102-B103</f>
-        <v/>
-      </c>
-      <c r="C104" s="16">
-        <f>C102-C103</f>
-        <v/>
-      </c>
-      <c r="D104" s="16">
-        <f>D102-D103</f>
-        <v/>
-      </c>
-      <c r="E104" s="16">
-        <f>E102-E103</f>
-        <v/>
-      </c>
-      <c r="F104" s="16">
-        <f>F102-F103</f>
-        <v/>
-      </c>
-      <c r="G104" s="16">
-        <f>G102-G103</f>
-        <v/>
-      </c>
-      <c r="H104" s="16">
-        <f>H102-H103</f>
-        <v/>
-      </c>
-      <c r="I104" s="16">
-        <f>I102-I103</f>
-        <v/>
-      </c>
-      <c r="J104" s="16">
-        <f>J102-J103</f>
-        <v/>
-      </c>
-      <c r="K104" s="16">
-        <f>K102-K103</f>
-        <v/>
-      </c>
-      <c r="L104" s="16">
-        <f>L102-L103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>(+) Depreciación y amortización</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="12">
-        <f>C79</f>
-        <v/>
-      </c>
-      <c r="D105" s="12">
-        <f>D79</f>
-        <v/>
-      </c>
-      <c r="E105" s="12">
-        <f>E79</f>
-        <v/>
-      </c>
-      <c r="F105" s="12">
-        <f>F79</f>
-        <v/>
-      </c>
-      <c r="G105" s="12">
-        <f>G79</f>
-        <v/>
-      </c>
-      <c r="H105" s="12">
-        <f>H79</f>
-        <v/>
-      </c>
-      <c r="I105" s="12">
-        <f>I79</f>
-        <v/>
-      </c>
-      <c r="J105" s="12">
-        <f>J79</f>
-        <v/>
-      </c>
-      <c r="K105" s="12">
-        <f>K79</f>
-        <v/>
-      </c>
-      <c r="L105" s="12">
-        <f>L79</f>
+      <c r="B105" s="16">
+        <f>B102-B104</f>
+        <v/>
+      </c>
+      <c r="C105" s="16">
+        <f>C102-C104</f>
+        <v/>
+      </c>
+      <c r="D105" s="16">
+        <f>D102-D104</f>
+        <v/>
+      </c>
+      <c r="E105" s="16">
+        <f>E102-E104</f>
+        <v/>
+      </c>
+      <c r="F105" s="16">
+        <f>F102-F104</f>
+        <v/>
+      </c>
+      <c r="G105" s="16">
+        <f>G102-G104</f>
+        <v/>
+      </c>
+      <c r="H105" s="16">
+        <f>H102-H104</f>
+        <v/>
+      </c>
+      <c r="I105" s="16">
+        <f>I102-I104</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>J102-J104</f>
+        <v/>
+      </c>
+      <c r="K105" s="16">
+        <f>K102-K104</f>
+        <v/>
+      </c>
+      <c r="L105" s="16">
+        <f>L102-L104</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>(+) Valor de desecho</t>
+          <t>(+) Depreciación y amortización</t>
         </is>
       </c>
       <c r="B106" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>0</v>
+      <c r="C106" s="12">
+        <f>C79</f>
+        <v/>
+      </c>
+      <c r="D106" s="12">
+        <f>D79</f>
+        <v/>
+      </c>
+      <c r="E106" s="12">
+        <f>E79</f>
+        <v/>
+      </c>
+      <c r="F106" s="12">
+        <f>F79</f>
+        <v/>
+      </c>
+      <c r="G106" s="12">
+        <f>G79</f>
+        <v/>
+      </c>
+      <c r="H106" s="12">
+        <f>H79</f>
+        <v/>
+      </c>
+      <c r="I106" s="12">
+        <f>I79</f>
+        <v/>
+      </c>
+      <c r="J106" s="12">
+        <f>J79</f>
+        <v/>
+      </c>
+      <c r="K106" s="12">
+        <f>K79</f>
+        <v/>
       </c>
       <c r="L106" s="12">
-        <f>L83</f>
+        <f>L79</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>(+) Recuperación capital de trabajo</t>
-        </is>
-      </c>
-      <c r="B107" s="12">
-        <f>B86</f>
-        <v/>
-      </c>
-      <c r="C107" s="12">
-        <f>C86</f>
-        <v/>
-      </c>
-      <c r="D107" s="12">
-        <f>D86</f>
-        <v/>
-      </c>
-      <c r="E107" s="12">
-        <f>E86</f>
-        <v/>
-      </c>
-      <c r="F107" s="12">
-        <f>F86</f>
-        <v/>
-      </c>
-      <c r="G107" s="12">
-        <f>G86</f>
-        <v/>
-      </c>
-      <c r="H107" s="12">
-        <f>H86</f>
-        <v/>
-      </c>
-      <c r="I107" s="12">
-        <f>I86</f>
-        <v/>
-      </c>
-      <c r="J107" s="12">
-        <f>J86</f>
-        <v/>
-      </c>
-      <c r="K107" s="12">
-        <f>K86</f>
-        <v/>
+          <t>(+) Valor de desecho</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="L107" s="12">
-        <f>L86</f>
+        <f>L83</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>(−) Inversión en activos fijos</t>
+          <t>(+) Recuperación capital de trabajo</t>
         </is>
       </c>
       <c r="B108" s="12">
-        <f>SUM(B28:B33)</f>
-        <v/>
-      </c>
-      <c r="C108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="12" t="n">
-        <v>0</v>
+        <f>B86</f>
+        <v/>
+      </c>
+      <c r="C108" s="12">
+        <f>C86</f>
+        <v/>
+      </c>
+      <c r="D108" s="12">
+        <f>D86</f>
+        <v/>
+      </c>
+      <c r="E108" s="12">
+        <f>E86</f>
+        <v/>
+      </c>
+      <c r="F108" s="12">
+        <f>F86</f>
+        <v/>
+      </c>
+      <c r="G108" s="12">
+        <f>G86</f>
+        <v/>
+      </c>
+      <c r="H108" s="12">
+        <f>H86</f>
+        <v/>
+      </c>
+      <c r="I108" s="12">
+        <f>I86</f>
+        <v/>
+      </c>
+      <c r="J108" s="12">
+        <f>J86</f>
+        <v/>
+      </c>
+      <c r="K108" s="12">
+        <f>K86</f>
+        <v/>
+      </c>
+      <c r="L108" s="12">
+        <f>L86</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
+          <t>(−) Inversión en activos fijos</t>
+        </is>
+      </c>
+      <c r="B109" s="12">
+        <f>SUM(B28:B33)</f>
+        <v/>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
           <t>(−) Inversión en capital de trabajo</t>
         </is>
       </c>
-      <c r="B109" s="12">
+      <c r="B110" s="12">
         <f>B85</f>
         <v/>
       </c>
-      <c r="C109" s="12">
+      <c r="C110" s="12">
         <f>C85</f>
         <v/>
       </c>
-      <c r="D109" s="12">
+      <c r="D110" s="12">
         <f>D85</f>
         <v/>
       </c>
-      <c r="E109" s="12">
+      <c r="E110" s="12">
         <f>E85</f>
         <v/>
       </c>
-      <c r="F109" s="12">
+      <c r="F110" s="12">
         <f>F85</f>
         <v/>
       </c>
-      <c r="G109" s="12">
+      <c r="G110" s="12">
         <f>G85</f>
         <v/>
       </c>
-      <c r="H109" s="12">
+      <c r="H110" s="12">
         <f>H85</f>
         <v/>
       </c>
-      <c r="I109" s="12">
+      <c r="I110" s="12">
         <f>I85</f>
         <v/>
       </c>
-      <c r="J109" s="12">
+      <c r="J110" s="12">
         <f>J85</f>
         <v/>
       </c>
-      <c r="K109" s="12">
+      <c r="K110" s="12">
         <f>K85</f>
         <v/>
       </c>
-      <c r="L109" s="12">
+      <c r="L110" s="12">
         <f>L85</f>
         <v/>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="15" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
         <is>
           <t>(=) FLUJO DE CAJA NETO</t>
         </is>
       </c>
-      <c r="B110" s="16">
-        <f>B104+B105+B106+B107-B108-B109</f>
-        <v/>
-      </c>
-      <c r="C110" s="16">
-        <f>C104+C105+C106+C107-C108-C109</f>
-        <v/>
-      </c>
-      <c r="D110" s="16">
-        <f>D104+D105+D106+D107-D108-D109</f>
-        <v/>
-      </c>
-      <c r="E110" s="16">
-        <f>E104+E105+E106+E107-E108-E109</f>
-        <v/>
-      </c>
-      <c r="F110" s="16">
-        <f>F104+F105+F106+F107-F108-F109</f>
-        <v/>
-      </c>
-      <c r="G110" s="16">
-        <f>G104+G105+G106+G107-G108-G109</f>
-        <v/>
-      </c>
-      <c r="H110" s="16">
-        <f>H104+H105+H106+H107-H108-H109</f>
-        <v/>
-      </c>
-      <c r="I110" s="16">
-        <f>I104+I105+I106+I107-I108-I109</f>
-        <v/>
-      </c>
-      <c r="J110" s="16">
-        <f>J104+J105+J106+J107-J108-J109</f>
-        <v/>
-      </c>
-      <c r="K110" s="16">
-        <f>K104+K105+K106+K107-K108-K109</f>
-        <v/>
-      </c>
-      <c r="L110" s="16">
-        <f>L104+L105+L106+L107-L108-L109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="inlineStr">
+      <c r="B111" s="16">
+        <f>B105+B106+B107+B108-B109-B110</f>
+        <v/>
+      </c>
+      <c r="C111" s="16">
+        <f>C105+C106+C107+C108-C109-C110</f>
+        <v/>
+      </c>
+      <c r="D111" s="16">
+        <f>D105+D106+D107+D108-D109-D110</f>
+        <v/>
+      </c>
+      <c r="E111" s="16">
+        <f>E105+E106+E107+E108-E109-E110</f>
+        <v/>
+      </c>
+      <c r="F111" s="16">
+        <f>F105+F106+F107+F108-F109-F110</f>
+        <v/>
+      </c>
+      <c r="G111" s="16">
+        <f>G105+G106+G107+G108-G109-G110</f>
+        <v/>
+      </c>
+      <c r="H111" s="16">
+        <f>H105+H106+H107+H108-H109-H110</f>
+        <v/>
+      </c>
+      <c r="I111" s="16">
+        <f>I105+I106+I107+I108-I109-I110</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>J105+J106+J107+J108-J109-J110</f>
+        <v/>
+      </c>
+      <c r="K111" s="16">
+        <f>K105+K106+K107+K108-K109-K110</f>
+        <v/>
+      </c>
+      <c r="L111" s="16">
+        <f>L105+L106+L107+L108-L109-L110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="inlineStr">
         <is>
           <t>Flujo de caja acumulado</t>
         </is>
       </c>
-      <c r="B111" s="22">
-        <f>B110</f>
-        <v/>
-      </c>
-      <c r="C111" s="22">
-        <f>B111+C110</f>
-        <v/>
-      </c>
-      <c r="D111" s="22">
-        <f>C111+D110</f>
-        <v/>
-      </c>
-      <c r="E111" s="22">
-        <f>D111+E110</f>
-        <v/>
-      </c>
-      <c r="F111" s="22">
-        <f>E111+F110</f>
-        <v/>
-      </c>
-      <c r="G111" s="22">
-        <f>F111+G110</f>
-        <v/>
-      </c>
-      <c r="H111" s="22">
-        <f>G111+H110</f>
-        <v/>
-      </c>
-      <c r="I111" s="22">
-        <f>H111+I110</f>
-        <v/>
-      </c>
-      <c r="J111" s="22">
-        <f>I111+J110</f>
-        <v/>
-      </c>
-      <c r="K111" s="22">
-        <f>J111+K110</f>
-        <v/>
-      </c>
-      <c r="L111" s="22">
-        <f>K111+L110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>10. FLUJO DE CAJA DEL PROYECTO (CON FINANCIAMIENTO)</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
-      <c r="E113" s="4" t="n"/>
-      <c r="F113" s="4" t="n"/>
-      <c r="G113" s="4" t="n"/>
-      <c r="H113" s="4" t="n"/>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="4" t="n"/>
-      <c r="K113" s="4" t="n"/>
-      <c r="L113" s="4" t="n"/>
+      <c r="B112" s="22">
+        <f>B111</f>
+        <v/>
+      </c>
+      <c r="C112" s="22">
+        <f>B112+C111</f>
+        <v/>
+      </c>
+      <c r="D112" s="22">
+        <f>C112+D111</f>
+        <v/>
+      </c>
+      <c r="E112" s="22">
+        <f>D112+E111</f>
+        <v/>
+      </c>
+      <c r="F112" s="22">
+        <f>E112+F111</f>
+        <v/>
+      </c>
+      <c r="G112" s="22">
+        <f>F112+G111</f>
+        <v/>
+      </c>
+      <c r="H112" s="22">
+        <f>G112+H111</f>
+        <v/>
+      </c>
+      <c r="I112" s="22">
+        <f>H112+I111</f>
+        <v/>
+      </c>
+      <c r="J112" s="22">
+        <f>I112+J111</f>
+        <v/>
+      </c>
+      <c r="K112" s="22">
+        <f>J112+K111</f>
+        <v/>
+      </c>
+      <c r="L112" s="22">
+        <f>K112+L111</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
+          <t>10. FLUJO DE CAJA DEL PROYECTO (CON FINANCIAMIENTO)</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="n"/>
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
+      <c r="E115" s="5" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F114" s="5" t="inlineStr">
+      <c r="F115" s="5" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H115" s="5" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I115" s="5" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J114" s="5" t="inlineStr">
+      <c r="J115" s="5" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K114" s="5" t="inlineStr">
+      <c r="K115" s="5" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>(+) Ingreso por ventas</t>
-        </is>
-      </c>
-      <c r="B115" s="12">
-        <f>B42</f>
-        <v/>
-      </c>
-      <c r="C115" s="12">
-        <f>C42</f>
-        <v/>
-      </c>
-      <c r="D115" s="12">
-        <f>D42</f>
-        <v/>
-      </c>
-      <c r="E115" s="12">
-        <f>E42</f>
-        <v/>
-      </c>
-      <c r="F115" s="12">
-        <f>F42</f>
-        <v/>
-      </c>
-      <c r="G115" s="12">
-        <f>G42</f>
-        <v/>
-      </c>
-      <c r="H115" s="12">
-        <f>H42</f>
-        <v/>
-      </c>
-      <c r="I115" s="12">
-        <f>I42</f>
-        <v/>
-      </c>
-      <c r="J115" s="12">
-        <f>J42</f>
-        <v/>
-      </c>
-      <c r="K115" s="12">
-        <f>K42</f>
-        <v/>
-      </c>
-      <c r="L115" s="12">
-        <f>L42</f>
-        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>(−) Costos variables</t>
+          <t>(+) Ingreso por ventas</t>
         </is>
       </c>
       <c r="B116" s="12">
-        <f>B49</f>
+        <f>B42</f>
         <v/>
       </c>
       <c r="C116" s="12">
-        <f>C49</f>
+        <f>C42</f>
         <v/>
       </c>
       <c r="D116" s="12">
-        <f>D49</f>
+        <f>D42</f>
         <v/>
       </c>
       <c r="E116" s="12">
-        <f>E49</f>
+        <f>E42</f>
         <v/>
       </c>
       <c r="F116" s="12">
-        <f>F49</f>
+        <f>F42</f>
         <v/>
       </c>
       <c r="G116" s="12">
-        <f>G49</f>
+        <f>G42</f>
         <v/>
       </c>
       <c r="H116" s="12">
-        <f>H49</f>
+        <f>H42</f>
         <v/>
       </c>
       <c r="I116" s="12">
-        <f>I49</f>
+        <f>I42</f>
         <v/>
       </c>
       <c r="J116" s="12">
-        <f>J49</f>
+        <f>J42</f>
         <v/>
       </c>
       <c r="K116" s="12">
-        <f>K49</f>
+        <f>K42</f>
         <v/>
       </c>
       <c r="L116" s="12">
-        <f>L49</f>
+        <f>L42</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>(−) Costos fijos</t>
+          <t>(−) Costos variables</t>
         </is>
       </c>
       <c r="B117" s="12">
-        <f>B69</f>
+        <f>B49</f>
         <v/>
       </c>
       <c r="C117" s="12">
-        <f>C69</f>
+        <f>C49</f>
         <v/>
       </c>
       <c r="D117" s="12">
-        <f>D69</f>
+        <f>D49</f>
         <v/>
       </c>
       <c r="E117" s="12">
-        <f>E69</f>
+        <f>E49</f>
         <v/>
       </c>
       <c r="F117" s="12">
-        <f>F69</f>
+        <f>F49</f>
         <v/>
       </c>
       <c r="G117" s="12">
-        <f>G69</f>
+        <f>G49</f>
         <v/>
       </c>
       <c r="H117" s="12">
-        <f>H69</f>
+        <f>H49</f>
         <v/>
       </c>
       <c r="I117" s="12">
-        <f>I69</f>
+        <f>I49</f>
         <v/>
       </c>
       <c r="J117" s="12">
-        <f>J69</f>
+        <f>J49</f>
         <v/>
       </c>
       <c r="K117" s="12">
-        <f>K69</f>
+        <f>K49</f>
         <v/>
       </c>
       <c r="L117" s="12">
-        <f>L69</f>
+        <f>L49</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>(−) Gastos financieros (intereses)</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="n">
-        <v>0</v>
+          <t>(−) Costos fijos</t>
+        </is>
+      </c>
+      <c r="B118" s="12">
+        <f>B69</f>
+        <v/>
       </c>
       <c r="C118" s="12">
-        <f>C92</f>
+        <f>C69</f>
         <v/>
       </c>
       <c r="D118" s="12">
-        <f>D92</f>
+        <f>D69</f>
         <v/>
       </c>
       <c r="E118" s="12">
-        <f>E92</f>
+        <f>E69</f>
         <v/>
       </c>
       <c r="F118" s="12">
-        <f>F92</f>
+        <f>F69</f>
         <v/>
       </c>
       <c r="G118" s="12">
-        <f>G92</f>
+        <f>G69</f>
         <v/>
       </c>
       <c r="H118" s="12">
-        <f>H92</f>
+        <f>H69</f>
         <v/>
       </c>
       <c r="I118" s="12">
-        <f>I92</f>
+        <f>I69</f>
         <v/>
       </c>
       <c r="J118" s="12">
-        <f>J92</f>
+        <f>J69</f>
         <v/>
       </c>
       <c r="K118" s="12">
-        <f>K92</f>
+        <f>K69</f>
         <v/>
       </c>
       <c r="L118" s="12">
-        <f>L92</f>
+        <f>L69</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
+          <t>(−) Gastos financieros (intereses)</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="12">
+        <f>C92</f>
+        <v/>
+      </c>
+      <c r="D119" s="12">
+        <f>D92</f>
+        <v/>
+      </c>
+      <c r="E119" s="12">
+        <f>E92</f>
+        <v/>
+      </c>
+      <c r="F119" s="12">
+        <f>F92</f>
+        <v/>
+      </c>
+      <c r="G119" s="12">
+        <f>G92</f>
+        <v/>
+      </c>
+      <c r="H119" s="12">
+        <f>H92</f>
+        <v/>
+      </c>
+      <c r="I119" s="12">
+        <f>I92</f>
+        <v/>
+      </c>
+      <c r="J119" s="12">
+        <f>J92</f>
+        <v/>
+      </c>
+      <c r="K119" s="12">
+        <f>K92</f>
+        <v/>
+      </c>
+      <c r="L119" s="12">
+        <f>L92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
           <t>(−) Depreciación y amortización</t>
         </is>
       </c>
-      <c r="B119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="12">
+      <c r="B120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="12">
         <f>C79</f>
         <v/>
       </c>
-      <c r="D119" s="12">
+      <c r="D120" s="12">
         <f>D79</f>
         <v/>
       </c>
-      <c r="E119" s="12">
+      <c r="E120" s="12">
         <f>E79</f>
         <v/>
       </c>
-      <c r="F119" s="12">
+      <c r="F120" s="12">
         <f>F79</f>
         <v/>
       </c>
-      <c r="G119" s="12">
+      <c r="G120" s="12">
         <f>G79</f>
         <v/>
       </c>
-      <c r="H119" s="12">
+      <c r="H120" s="12">
         <f>H79</f>
         <v/>
       </c>
-      <c r="I119" s="12">
+      <c r="I120" s="12">
         <f>I79</f>
         <v/>
       </c>
-      <c r="J119" s="12">
+      <c r="J120" s="12">
         <f>J79</f>
         <v/>
       </c>
-      <c r="K119" s="12">
+      <c r="K120" s="12">
         <f>K79</f>
         <v/>
       </c>
-      <c r="L119" s="12">
+      <c r="L120" s="12">
         <f>L79</f>
         <v/>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="15" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="15" t="inlineStr">
         <is>
           <t>(=) Utilidad antes de impuestos</t>
         </is>
       </c>
-      <c r="B120" s="16">
-        <f>B115-B116-B117-B118-B119</f>
-        <v/>
-      </c>
-      <c r="C120" s="16">
-        <f>C115-C116-C117-C118-C119</f>
-        <v/>
-      </c>
-      <c r="D120" s="16">
-        <f>D115-D116-D117-D118-D119</f>
-        <v/>
-      </c>
-      <c r="E120" s="16">
-        <f>E115-E116-E117-E118-E119</f>
-        <v/>
-      </c>
-      <c r="F120" s="16">
-        <f>F115-F116-F117-F118-F119</f>
-        <v/>
-      </c>
-      <c r="G120" s="16">
-        <f>G115-G116-G117-G118-G119</f>
-        <v/>
-      </c>
-      <c r="H120" s="16">
-        <f>H115-H116-H117-H118-H119</f>
-        <v/>
-      </c>
-      <c r="I120" s="16">
-        <f>I115-I116-I117-I118-I119</f>
-        <v/>
-      </c>
-      <c r="J120" s="16">
-        <f>J115-J116-J117-J118-J119</f>
-        <v/>
-      </c>
-      <c r="K120" s="16">
-        <f>K115-K116-K117-K118-K119</f>
-        <v/>
-      </c>
-      <c r="L120" s="16">
-        <f>L115-L116-L117-L118-L119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>(−) Impuesto sobre la renta (25% + 5% solidaria)</t>
-        </is>
-      </c>
-      <c r="B121" s="12">
-        <f>IF(B120&gt;0,$B$6*B120+$B$7*MAX(0,B120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="C121" s="12">
-        <f>IF(C120&gt;0,$B$6*C120+$B$7*MAX(0,C120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="D121" s="12">
-        <f>IF(D120&gt;0,$B$6*D120+$B$7*MAX(0,D120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="E121" s="12">
-        <f>IF(E120&gt;0,$B$6*E120+$B$7*MAX(0,E120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="F121" s="12">
-        <f>IF(F120&gt;0,$B$6*F120+$B$7*MAX(0,F120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="G121" s="12">
-        <f>IF(G120&gt;0,$B$6*G120+$B$7*MAX(0,G120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="H121" s="12">
-        <f>IF(H120&gt;0,$B$6*H120+$B$7*MAX(0,H120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="I121" s="12">
-        <f>IF(I120&gt;0,$B$6*I120+$B$7*MAX(0,I120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="J121" s="12">
-        <f>IF(J120&gt;0,$B$6*J120+$B$7*MAX(0,J120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="K121" s="12">
-        <f>IF(K120&gt;0,$B$6*K120+$B$7*MAX(0,K120-$B$8),0)</f>
-        <v/>
-      </c>
-      <c r="L121" s="12">
-        <f>IF(L120&gt;0,$B$6*L120+$B$7*MAX(0,L120-$B$8),0)</f>
+      <c r="B121" s="16">
+        <f>B116-B117-B118-B119-B120</f>
+        <v/>
+      </c>
+      <c r="C121" s="16">
+        <f>C116-C117-C118-C119-C120</f>
+        <v/>
+      </c>
+      <c r="D121" s="16">
+        <f>D116-D117-D118-D119-D120</f>
+        <v/>
+      </c>
+      <c r="E121" s="16">
+        <f>E116-E117-E118-E119-E120</f>
+        <v/>
+      </c>
+      <c r="F121" s="16">
+        <f>F116-F117-F118-F119-F120</f>
+        <v/>
+      </c>
+      <c r="G121" s="16">
+        <f>G116-G117-G118-G119-G120</f>
+        <v/>
+      </c>
+      <c r="H121" s="16">
+        <f>H116-H117-H118-H119-H120</f>
+        <v/>
+      </c>
+      <c r="I121" s="16">
+        <f>I116-I117-I118-I119-I120</f>
+        <v/>
+      </c>
+      <c r="J121" s="16">
+        <f>J116-J117-J118-J119-J120</f>
+        <v/>
+      </c>
+      <c r="K121" s="16">
+        <f>K116-K117-K118-K119-K120</f>
+        <v/>
+      </c>
+      <c r="L121" s="16">
+        <f>L116-L117-L118-L119-L120</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>(=) Utilidad después de impuestos</t>
-        </is>
-      </c>
-      <c r="B122" s="16">
-        <f>B120-B121</f>
-        <v/>
-      </c>
-      <c r="C122" s="16">
-        <f>C120-C121</f>
-        <v/>
-      </c>
-      <c r="D122" s="16">
-        <f>D120-D121</f>
-        <v/>
-      </c>
-      <c r="E122" s="16">
-        <f>E120-E121</f>
-        <v/>
-      </c>
-      <c r="F122" s="16">
-        <f>F120-F121</f>
-        <v/>
-      </c>
-      <c r="G122" s="16">
-        <f>G120-G121</f>
-        <v/>
-      </c>
-      <c r="H122" s="16">
-        <f>H120-H121</f>
-        <v/>
-      </c>
-      <c r="I122" s="16">
-        <f>I120-I121</f>
-        <v/>
-      </c>
-      <c r="J122" s="16">
-        <f>J120-J121</f>
-        <v/>
-      </c>
-      <c r="K122" s="16">
-        <f>K120-K121</f>
-        <v/>
-      </c>
-      <c r="L122" s="16">
-        <f>L120-L121</f>
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Pérdidas fiscales acumuladas (arrastre 3 años, manufactura)</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="12">
+        <f>MAX(0,B122-C121)</f>
+        <v/>
+      </c>
+      <c r="D122" s="12">
+        <f>MAX(0,C122-D121)</f>
+        <v/>
+      </c>
+      <c r="E122" s="12">
+        <f>MAX(0,D122-E121)</f>
+        <v/>
+      </c>
+      <c r="F122" s="12">
+        <f>MAX(0,E122-F121)</f>
+        <v/>
+      </c>
+      <c r="G122" s="12">
+        <f>MAX(0,F122-G121)</f>
+        <v/>
+      </c>
+      <c r="H122" s="12">
+        <f>MAX(0,G122-H121)</f>
+        <v/>
+      </c>
+      <c r="I122" s="12">
+        <f>MAX(0,H122-I121)</f>
+        <v/>
+      </c>
+      <c r="J122" s="12">
+        <f>MAX(0,I122-J121)</f>
+        <v/>
+      </c>
+      <c r="K122" s="12">
+        <f>MAX(0,J122-K121)</f>
+        <v/>
+      </c>
+      <c r="L122" s="12">
+        <f>MAX(0,K122-L121)</f>
         <v/>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>(+) Depreciación y amortización</t>
+          <t>(−) Impuesto sobre la renta (25% + 5% solidaria, neto de pérdidas)</t>
         </is>
       </c>
       <c r="B123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C123" s="12">
-        <f>C79</f>
+        <f>$B$6*MAX(0,C121-B122)+$B$7*MAX(0,MAX(0,C121-B122)-$B$8)</f>
         <v/>
       </c>
       <c r="D123" s="12">
-        <f>D79</f>
+        <f>$B$6*MAX(0,D121-C122)+$B$7*MAX(0,MAX(0,D121-C122)-$B$8)</f>
         <v/>
       </c>
       <c r="E123" s="12">
-        <f>E79</f>
+        <f>$B$6*MAX(0,E121-D122)+$B$7*MAX(0,MAX(0,E121-D122)-$B$8)</f>
         <v/>
       </c>
       <c r="F123" s="12">
-        <f>F79</f>
+        <f>$B$6*MAX(0,F121-E122)+$B$7*MAX(0,MAX(0,F121-E122)-$B$8)</f>
         <v/>
       </c>
       <c r="G123" s="12">
-        <f>G79</f>
+        <f>$B$6*MAX(0,G121-F122)+$B$7*MAX(0,MAX(0,G121-F122)-$B$8)</f>
         <v/>
       </c>
       <c r="H123" s="12">
-        <f>H79</f>
+        <f>$B$6*MAX(0,H121-G122)+$B$7*MAX(0,MAX(0,H121-G122)-$B$8)</f>
         <v/>
       </c>
       <c r="I123" s="12">
-        <f>I79</f>
+        <f>$B$6*MAX(0,I121-H122)+$B$7*MAX(0,MAX(0,I121-H122)-$B$8)</f>
         <v/>
       </c>
       <c r="J123" s="12">
-        <f>J79</f>
+        <f>$B$6*MAX(0,J121-I122)+$B$7*MAX(0,MAX(0,J121-I122)-$B$8)</f>
         <v/>
       </c>
       <c r="K123" s="12">
-        <f>K79</f>
+        <f>$B$6*MAX(0,K121-J122)+$B$7*MAX(0,MAX(0,K121-J122)-$B$8)</f>
         <v/>
       </c>
       <c r="L123" s="12">
-        <f>L79</f>
+        <f>$B$6*MAX(0,L121-K122)+$B$7*MAX(0,MAX(0,L121-K122)-$B$8)</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>(+) Valor de desecho</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="12">
-        <f>L83</f>
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>(=) Utilidad después de impuestos</t>
+        </is>
+      </c>
+      <c r="B124" s="16">
+        <f>B121-B123</f>
+        <v/>
+      </c>
+      <c r="C124" s="16">
+        <f>C121-C123</f>
+        <v/>
+      </c>
+      <c r="D124" s="16">
+        <f>D121-D123</f>
+        <v/>
+      </c>
+      <c r="E124" s="16">
+        <f>E121-E123</f>
+        <v/>
+      </c>
+      <c r="F124" s="16">
+        <f>F121-F123</f>
+        <v/>
+      </c>
+      <c r="G124" s="16">
+        <f>G121-G123</f>
+        <v/>
+      </c>
+      <c r="H124" s="16">
+        <f>H121-H123</f>
+        <v/>
+      </c>
+      <c r="I124" s="16">
+        <f>I121-I123</f>
+        <v/>
+      </c>
+      <c r="J124" s="16">
+        <f>J121-J123</f>
+        <v/>
+      </c>
+      <c r="K124" s="16">
+        <f>K121-K123</f>
+        <v/>
+      </c>
+      <c r="L124" s="16">
+        <f>L121-L123</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>(+) Recuperación capital de trabajo</t>
-        </is>
-      </c>
-      <c r="B125" s="12">
-        <f>B86</f>
-        <v/>
+          <t>(+) Depreciación y amortización</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="12">
-        <f>C86</f>
+        <f>C79</f>
         <v/>
       </c>
       <c r="D125" s="12">
-        <f>D86</f>
+        <f>D79</f>
         <v/>
       </c>
       <c r="E125" s="12">
-        <f>E86</f>
+        <f>E79</f>
         <v/>
       </c>
       <c r="F125" s="12">
-        <f>F86</f>
+        <f>F79</f>
         <v/>
       </c>
       <c r="G125" s="12">
-        <f>G86</f>
+        <f>G79</f>
         <v/>
       </c>
       <c r="H125" s="12">
-        <f>H86</f>
+        <f>H79</f>
         <v/>
       </c>
       <c r="I125" s="12">
-        <f>I86</f>
+        <f>I79</f>
         <v/>
       </c>
       <c r="J125" s="12">
-        <f>J86</f>
+        <f>J79</f>
         <v/>
       </c>
       <c r="K125" s="12">
-        <f>K86</f>
+        <f>K79</f>
         <v/>
       </c>
       <c r="L125" s="12">
-        <f>L86</f>
+        <f>L79</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>(+) Préstamo bancario (Año 0)</t>
-        </is>
-      </c>
-      <c r="B126" s="12">
-        <f>D35</f>
-        <v/>
+          <t>(+) Valor de desecho</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="12" t="n">
         <v>0</v>
@@ -4698,655 +4703,712 @@
       <c r="K126" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="12" t="n">
-        <v>0</v>
+      <c r="L126" s="12">
+        <f>L83</f>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>(−) Inversión en activos fijos</t>
+          <t>(+) Recuperación capital de trabajo</t>
         </is>
       </c>
       <c r="B127" s="12">
-        <f>SUM(B28:B33)</f>
-        <v/>
-      </c>
-      <c r="C127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="12" t="n">
-        <v>0</v>
+        <f>B86</f>
+        <v/>
+      </c>
+      <c r="C127" s="12">
+        <f>C86</f>
+        <v/>
+      </c>
+      <c r="D127" s="12">
+        <f>D86</f>
+        <v/>
+      </c>
+      <c r="E127" s="12">
+        <f>E86</f>
+        <v/>
+      </c>
+      <c r="F127" s="12">
+        <f>F86</f>
+        <v/>
+      </c>
+      <c r="G127" s="12">
+        <f>G86</f>
+        <v/>
+      </c>
+      <c r="H127" s="12">
+        <f>H86</f>
+        <v/>
+      </c>
+      <c r="I127" s="12">
+        <f>I86</f>
+        <v/>
+      </c>
+      <c r="J127" s="12">
+        <f>J86</f>
+        <v/>
+      </c>
+      <c r="K127" s="12">
+        <f>K86</f>
+        <v/>
+      </c>
+      <c r="L127" s="12">
+        <f>L86</f>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>(−) Inversión en capital de trabajo</t>
+          <t>(+) Préstamo bancario (Año 0)</t>
         </is>
       </c>
       <c r="B128" s="12">
-        <f>B85</f>
-        <v/>
-      </c>
-      <c r="C128" s="12">
-        <f>C85</f>
-        <v/>
-      </c>
-      <c r="D128" s="12">
-        <f>D85</f>
-        <v/>
-      </c>
-      <c r="E128" s="12">
-        <f>E85</f>
-        <v/>
-      </c>
-      <c r="F128" s="12">
-        <f>F85</f>
-        <v/>
-      </c>
-      <c r="G128" s="12">
-        <f>G85</f>
-        <v/>
-      </c>
-      <c r="H128" s="12">
-        <f>H85</f>
-        <v/>
-      </c>
-      <c r="I128" s="12">
-        <f>I85</f>
-        <v/>
-      </c>
-      <c r="J128" s="12">
-        <f>J85</f>
-        <v/>
-      </c>
-      <c r="K128" s="12">
-        <f>K85</f>
-        <v/>
-      </c>
-      <c r="L128" s="12">
-        <f>L85</f>
-        <v/>
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
+          <t>(−) Inversión en activos fijos</t>
+        </is>
+      </c>
+      <c r="B129" s="12">
+        <f>SUM(B28:B33)</f>
+        <v/>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>(−) Inversión en capital de trabajo</t>
+        </is>
+      </c>
+      <c r="B130" s="12">
+        <f>B85</f>
+        <v/>
+      </c>
+      <c r="C130" s="12">
+        <f>C85</f>
+        <v/>
+      </c>
+      <c r="D130" s="12">
+        <f>D85</f>
+        <v/>
+      </c>
+      <c r="E130" s="12">
+        <f>E85</f>
+        <v/>
+      </c>
+      <c r="F130" s="12">
+        <f>F85</f>
+        <v/>
+      </c>
+      <c r="G130" s="12">
+        <f>G85</f>
+        <v/>
+      </c>
+      <c r="H130" s="12">
+        <f>H85</f>
+        <v/>
+      </c>
+      <c r="I130" s="12">
+        <f>I85</f>
+        <v/>
+      </c>
+      <c r="J130" s="12">
+        <f>J85</f>
+        <v/>
+      </c>
+      <c r="K130" s="12">
+        <f>K85</f>
+        <v/>
+      </c>
+      <c r="L130" s="12">
+        <f>L85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
           <t>(−) Abono a capital del préstamo</t>
         </is>
       </c>
-      <c r="B129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="12">
+      <c r="B131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="12">
         <f>C91</f>
         <v/>
       </c>
-      <c r="D129" s="12">
+      <c r="D131" s="12">
         <f>D91</f>
         <v/>
       </c>
-      <c r="E129" s="12">
+      <c r="E131" s="12">
         <f>E91</f>
         <v/>
       </c>
-      <c r="F129" s="12">
+      <c r="F131" s="12">
         <f>F91</f>
         <v/>
       </c>
-      <c r="G129" s="12">
+      <c r="G131" s="12">
         <f>G91</f>
         <v/>
       </c>
-      <c r="H129" s="12">
+      <c r="H131" s="12">
         <f>H91</f>
         <v/>
       </c>
-      <c r="I129" s="12">
+      <c r="I131" s="12">
         <f>I91</f>
         <v/>
       </c>
-      <c r="J129" s="12">
+      <c r="J131" s="12">
         <f>J91</f>
         <v/>
       </c>
-      <c r="K129" s="12">
+      <c r="K131" s="12">
         <f>K91</f>
         <v/>
       </c>
-      <c r="L129" s="12">
+      <c r="L131" s="12">
         <f>L91</f>
         <v/>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
         <is>
           <t>(=) FLUJO DE CAJA NETO</t>
         </is>
       </c>
-      <c r="B130" s="16">
-        <f>B122+B123+B124+B125+B126-B127-B128-B129</f>
-        <v/>
-      </c>
-      <c r="C130" s="16">
-        <f>C122+C123+C124+C125+C126-C127-C128-C129</f>
-        <v/>
-      </c>
-      <c r="D130" s="16">
-        <f>D122+D123+D124+D125+D126-D127-D128-D129</f>
-        <v/>
-      </c>
-      <c r="E130" s="16">
-        <f>E122+E123+E124+E125+E126-E127-E128-E129</f>
-        <v/>
-      </c>
-      <c r="F130" s="16">
-        <f>F122+F123+F124+F125+F126-F127-F128-F129</f>
-        <v/>
-      </c>
-      <c r="G130" s="16">
-        <f>G122+G123+G124+G125+G126-G127-G128-G129</f>
-        <v/>
-      </c>
-      <c r="H130" s="16">
-        <f>H122+H123+H124+H125+H126-H127-H128-H129</f>
-        <v/>
-      </c>
-      <c r="I130" s="16">
-        <f>I122+I123+I124+I125+I126-I127-I128-I129</f>
-        <v/>
-      </c>
-      <c r="J130" s="16">
-        <f>J122+J123+J124+J125+J126-J127-J128-J129</f>
-        <v/>
-      </c>
-      <c r="K130" s="16">
-        <f>K122+K123+K124+K125+K126-K127-K128-K129</f>
-        <v/>
-      </c>
-      <c r="L130" s="16">
-        <f>L122+L123+L124+L125+L126-L127-L128-L129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="inlineStr">
+      <c r="B132" s="16">
+        <f>B124+B125+B126+B127+B128-B129-B130-B131</f>
+        <v/>
+      </c>
+      <c r="C132" s="16">
+        <f>C124+C125+C126+C127+C128-C129-C130-C131</f>
+        <v/>
+      </c>
+      <c r="D132" s="16">
+        <f>D124+D125+D126+D127+D128-D129-D130-D131</f>
+        <v/>
+      </c>
+      <c r="E132" s="16">
+        <f>E124+E125+E126+E127+E128-E129-E130-E131</f>
+        <v/>
+      </c>
+      <c r="F132" s="16">
+        <f>F124+F125+F126+F127+F128-F129-F130-F131</f>
+        <v/>
+      </c>
+      <c r="G132" s="16">
+        <f>G124+G125+G126+G127+G128-G129-G130-G131</f>
+        <v/>
+      </c>
+      <c r="H132" s="16">
+        <f>H124+H125+H126+H127+H128-H129-H130-H131</f>
+        <v/>
+      </c>
+      <c r="I132" s="16">
+        <f>I124+I125+I126+I127+I128-I129-I130-I131</f>
+        <v/>
+      </c>
+      <c r="J132" s="16">
+        <f>J124+J125+J126+J127+J128-J129-J130-J131</f>
+        <v/>
+      </c>
+      <c r="K132" s="16">
+        <f>K124+K125+K126+K127+K128-K129-K130-K131</f>
+        <v/>
+      </c>
+      <c r="L132" s="16">
+        <f>L124+L125+L126+L127+L128-L129-L130-L131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="inlineStr">
         <is>
           <t>Flujo de caja acumulado</t>
         </is>
       </c>
-      <c r="B131" s="22">
-        <f>B130</f>
-        <v/>
-      </c>
-      <c r="C131" s="22">
-        <f>B131+C130</f>
-        <v/>
-      </c>
-      <c r="D131" s="22">
-        <f>C131+D130</f>
-        <v/>
-      </c>
-      <c r="E131" s="22">
-        <f>D131+E130</f>
-        <v/>
-      </c>
-      <c r="F131" s="22">
-        <f>E131+F130</f>
-        <v/>
-      </c>
-      <c r="G131" s="22">
-        <f>F131+G130</f>
-        <v/>
-      </c>
-      <c r="H131" s="22">
-        <f>G131+H130</f>
-        <v/>
-      </c>
-      <c r="I131" s="22">
-        <f>H131+I130</f>
-        <v/>
-      </c>
-      <c r="J131" s="22">
-        <f>I131+J130</f>
-        <v/>
-      </c>
-      <c r="K131" s="22">
-        <f>J131+K130</f>
-        <v/>
-      </c>
-      <c r="L131" s="22">
-        <f>K131+L130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B133" s="22">
+        <f>B132</f>
+        <v/>
+      </c>
+      <c r="C133" s="22">
+        <f>B133+C132</f>
+        <v/>
+      </c>
+      <c r="D133" s="22">
+        <f>C133+D132</f>
+        <v/>
+      </c>
+      <c r="E133" s="22">
+        <f>D133+E132</f>
+        <v/>
+      </c>
+      <c r="F133" s="22">
+        <f>E133+F132</f>
+        <v/>
+      </c>
+      <c r="G133" s="22">
+        <f>F133+G132</f>
+        <v/>
+      </c>
+      <c r="H133" s="22">
+        <f>G133+H132</f>
+        <v/>
+      </c>
+      <c r="I133" s="22">
+        <f>H133+I132</f>
+        <v/>
+      </c>
+      <c r="J133" s="22">
+        <f>I133+J132</f>
+        <v/>
+      </c>
+      <c r="K133" s="22">
+        <f>J133+K132</f>
+        <v/>
+      </c>
+      <c r="L133" s="22">
+        <f>K133+L132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>11. COSTO DE CAPITAL — PROYECTO PURO (sin financiamiento)</t>
         </is>
       </c>
-      <c r="B133" s="4" t="n"/>
-      <c r="C133" s="4" t="n"/>
-      <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="4" t="n"/>
-      <c r="G133" s="4" t="n"/>
-      <c r="H133" s="4" t="n"/>
-      <c r="I133" s="4" t="n"/>
-      <c r="J133" s="4" t="n"/>
-      <c r="K133" s="4" t="n"/>
-      <c r="L133" s="4" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>Participación</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>Costo ponderado</t>
         </is>
       </c>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="n"/>
-      <c r="L134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
         <is>
           <t>Recursos propios (100%)</t>
         </is>
       </c>
-      <c r="B135" s="12">
+      <c r="B137" s="12">
         <f>B35</f>
         <v/>
       </c>
-      <c r="C135" s="23">
-        <f>B135/B136</f>
-        <v/>
-      </c>
-      <c r="D135" s="23">
+      <c r="C137" s="23">
+        <f>B137/B138</f>
+        <v/>
+      </c>
+      <c r="D137" s="23">
         <f>$B$12</f>
         <v/>
       </c>
-      <c r="E135" s="23">
-        <f>C135*D135</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="inlineStr">
+      <c r="E137" s="23">
+        <f>C137*D137</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="inlineStr">
         <is>
           <t>TOTAL / Tasa de descuento del proyecto</t>
         </is>
       </c>
-      <c r="B136" s="16">
-        <f>B135</f>
-        <v/>
-      </c>
-      <c r="C136" s="24" t="n">
+      <c r="B138" s="16">
+        <f>B137</f>
+        <v/>
+      </c>
+      <c r="C138" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D138" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E136" s="24">
-        <f>E135</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="E138" s="24">
+        <f>E137</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>12. INDICADORES FINANCIEROS — PROYECTO PURO</t>
         </is>
       </c>
-      <c r="B138" s="4" t="n"/>
-      <c r="C138" s="4" t="n"/>
-      <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="n"/>
-      <c r="F138" s="4" t="n"/>
-      <c r="G138" s="4" t="n"/>
-      <c r="H138" s="4" t="n"/>
-      <c r="I138" s="4" t="n"/>
-      <c r="J138" s="4" t="n"/>
-      <c r="K138" s="4" t="n"/>
-      <c r="L138" s="4" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="21" t="inlineStr">
-        <is>
-          <t>VAN (Valor Actual Neto)</t>
-        </is>
-      </c>
-      <c r="B139" s="8">
-        <f>NPV(E136,C110:L110)+B110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="21" t="inlineStr">
-        <is>
-          <t>TIR (Tasa Interna de Retorno)</t>
-        </is>
-      </c>
-      <c r="B140" s="7">
-        <f>IRR(B110:L110)</f>
-        <v/>
-      </c>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="21" t="inlineStr">
         <is>
-          <t>PRI (años de recuperación)</t>
-        </is>
-      </c>
-      <c r="B141" s="9">
-        <f>IF(COUNTIF(B111:L111,"&lt;0")=11,"&gt;10",(COUNTIF(B111:L111,"&lt;0")-1)+(-INDEX(B111:L111,COUNTIF(B111:L111,"&lt;0")))/INDEX(B110:L110,COUNTIF(B111:L111,"&lt;0")+1))</f>
+          <t>VAN (Valor Actual Neto)</t>
+        </is>
+      </c>
+      <c r="B141" s="8">
+        <f>NPV(E138,C111:L111)+B111</f>
         <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
         <is>
+          <t>TIR (Tasa Interna de Retorno)</t>
+        </is>
+      </c>
+      <c r="B142" s="7">
+        <f>IRR(B111:L111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="inlineStr">
+        <is>
+          <t>PRI (años de recuperación)</t>
+        </is>
+      </c>
+      <c r="B143" s="9">
+        <f>IF(COUNTIF(B112:L112,"&lt;0")=11,"&gt;10",(COUNTIF(B112:L112,"&lt;0")-1)+(-INDEX(B112:L112,COUNTIF(B112:L112,"&lt;0")))/INDEX(B111:L111,COUNTIF(B112:L112,"&lt;0")+1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="inlineStr">
+        <is>
           <t>Relación Beneficio/Costo</t>
         </is>
       </c>
-      <c r="B142" s="9">
-        <f>NPV(E136,C42:L42)/(B35+NPV(E136,C49:L49)+NPV(E136,C69:L69)+NPV(E136,C103:L103))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="B144" s="9">
+        <f>NPV(E138,C42:L42)/(B35+NPV(E138,C49:L49)+NPV(E138,C69:L69)+NPV(E138,C104:L104))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>13. COSTO DE CAPITAL — CON FINANCIAMIENTO (WACC)</t>
         </is>
       </c>
-      <c r="B144" s="4" t="n"/>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="4" t="n"/>
-      <c r="G144" s="4" t="n"/>
-      <c r="H144" s="4" t="n"/>
-      <c r="I144" s="4" t="n"/>
-      <c r="J144" s="4" t="n"/>
-      <c r="K144" s="4" t="n"/>
-      <c r="L144" s="4" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
         <is>
           <t>Participación</t>
         </is>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="E145" s="5" t="inlineStr">
+      <c r="E147" s="5" t="inlineStr">
         <is>
           <t>Costo ponderado</t>
         </is>
       </c>
-      <c r="F145" s="4" t="n"/>
-      <c r="G145" s="4" t="n"/>
-      <c r="H145" s="4" t="n"/>
-      <c r="I145" s="4" t="n"/>
-      <c r="J145" s="4" t="n"/>
-      <c r="K145" s="4" t="n"/>
-      <c r="L145" s="4" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="inlineStr">
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n"/>
+      <c r="L147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>Préstamo bancario (deuda, después de impuestos)</t>
         </is>
       </c>
-      <c r="B146" s="12">
+      <c r="B148" s="12">
         <f>D35</f>
         <v/>
       </c>
-      <c r="C146" s="23">
-        <f>B146/B148</f>
-        <v/>
-      </c>
-      <c r="D146" s="23">
+      <c r="C148" s="23">
+        <f>B148/B150</f>
+        <v/>
+      </c>
+      <c r="D148" s="23">
         <f>$B$9*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="E146" s="23">
-        <f>C146*D146</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="6" t="inlineStr">
+      <c r="E148" s="23">
+        <f>C148*D148</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>Recursos propios (patrimonio)</t>
         </is>
       </c>
-      <c r="B147" s="12">
+      <c r="B149" s="12">
         <f>C35</f>
         <v/>
       </c>
-      <c r="C147" s="23">
-        <f>B147/B148</f>
-        <v/>
-      </c>
-      <c r="D147" s="23">
+      <c r="C149" s="23">
+        <f>B149/B150</f>
+        <v/>
+      </c>
+      <c r="D149" s="23">
         <f>$B$12</f>
         <v/>
       </c>
-      <c r="E147" s="23">
-        <f>C147*D147</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="15" t="inlineStr">
+      <c r="E149" s="23">
+        <f>C149*D149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="inlineStr">
         <is>
           <t>TOTAL / WACC</t>
         </is>
       </c>
-      <c r="B148" s="16">
-        <f>B146+B147</f>
-        <v/>
-      </c>
-      <c r="C148" s="24" t="n">
+      <c r="B150" s="16">
+        <f>B148+B149</f>
+        <v/>
+      </c>
+      <c r="C150" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D148" s="25" t="inlineStr">
+      <c r="D150" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E148" s="24">
-        <f>E146+E147</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="E150" s="24">
+        <f>E148+E149</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>14. INDICADORES FINANCIEROS — CON FINANCIAMIENTO</t>
         </is>
       </c>
-      <c r="B150" s="4" t="n"/>
-      <c r="C150" s="4" t="n"/>
-      <c r="D150" s="4" t="n"/>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="n"/>
-      <c r="H150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
-      <c r="J150" s="4" t="n"/>
-      <c r="K150" s="4" t="n"/>
-      <c r="L150" s="4" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="21" t="inlineStr">
-        <is>
-          <t>VAN (Valor Actual Neto)</t>
-        </is>
-      </c>
-      <c r="B151" s="8">
-        <f>NPV(E148,C130:L130)+B130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="21" t="inlineStr">
-        <is>
-          <t>TIR (Tasa Interna de Retorno)</t>
-        </is>
-      </c>
-      <c r="B152" s="7">
-        <f>IRR(B130:L130)</f>
-        <v/>
-      </c>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
+      <c r="E152" s="4" t="n"/>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="n"/>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="n"/>
+      <c r="J152" s="4" t="n"/>
+      <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="21" t="inlineStr">
         <is>
-          <t>PRI (años de recuperación)</t>
-        </is>
-      </c>
-      <c r="B153" s="9">
-        <f>IF(COUNTIF(B131:L131,"&lt;0")=11,"&gt;10",(COUNTIF(B131:L131,"&lt;0")-1)+(-INDEX(B131:L131,COUNTIF(B131:L131,"&lt;0")))/INDEX(B130:L130,COUNTIF(B131:L131,"&lt;0")+1))</f>
+          <t>VAN (Valor Actual Neto)</t>
+        </is>
+      </c>
+      <c r="B153" s="8">
+        <f>NPV(E150,C132:L132)+B132</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="21" t="inlineStr">
         <is>
+          <t>TIR (Tasa Interna de Retorno)</t>
+        </is>
+      </c>
+      <c r="B154" s="7">
+        <f>IRR(B132:L132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="21" t="inlineStr">
+        <is>
+          <t>PRI (años de recuperación)</t>
+        </is>
+      </c>
+      <c r="B155" s="9">
+        <f>IF(COUNTIF(B133:L133,"&lt;0")=11,"&gt;10",(COUNTIF(B133:L133,"&lt;0")-1)+(-INDEX(B133:L133,COUNTIF(B133:L133,"&lt;0")))/INDEX(B132:L132,COUNTIF(B133:L133,"&lt;0")+1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="21" t="inlineStr">
+        <is>
           <t>Relación Beneficio/Costo</t>
         </is>
       </c>
-      <c r="B154" s="9">
-        <f>NPV(E148,C42:L42)/(C35+NPV(E148,C49:L49)+NPV(E148,C69:L69)+NPV(E148,C118:L118)+NPV(E148,C121:L121)+NPV(E148,C129:L129))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
+      <c r="B156" s="9">
+        <f>NPV(E150,C42:L42)/(C35+NPV(E150,C49:L49)+NPV(E150,C69:L69)+NPV(E150,C119:L119)+NPV(E150,C123:L123)+NPV(E150,C131:L131))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>15. NOTAS LEGALES (cumplimiento normativo Honduras)</t>
         </is>
       </c>
-      <c r="B156" s="4" t="n"/>
-      <c r="C156" s="4" t="n"/>
-      <c r="D156" s="4" t="n"/>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="n"/>
-      <c r="G156" s="4" t="n"/>
-      <c r="H156" s="4" t="n"/>
-      <c r="I156" s="4" t="n"/>
-      <c r="J156" s="4" t="n"/>
-      <c r="K156" s="4" t="n"/>
-      <c r="L156" s="4" t="n"/>
-    </row>
-    <row r="157" ht="30" customHeight="1">
-      <c r="A157" s="26" t="inlineStr">
-        <is>
-          <t>• ISR: 25% + aportación solidaria 5% sobre el excedente de L 1,000,000 (Ley del ISR).</t>
-        </is>
-      </c>
-      <c r="B157" s="14" t="n"/>
-      <c r="C157" s="14" t="n"/>
-      <c r="D157" s="14" t="n"/>
-      <c r="E157" s="14" t="n"/>
-      <c r="F157" s="14" t="n"/>
-      <c r="G157" s="14" t="n"/>
-      <c r="H157" s="14" t="n"/>
-      <c r="I157" s="14" t="n"/>
-      <c r="J157" s="14" t="n"/>
-      <c r="K157" s="14" t="n"/>
-      <c r="L157" s="14" t="n"/>
-    </row>
-    <row r="158" ht="30" customHeight="1">
-      <c r="A158" s="26" t="inlineStr">
-        <is>
-          <t>• Depreciación línea recta: maquinaria 10%; vehículos 10%-33% (aquí 20% = 5 años); diferidos 5 años.</t>
-        </is>
-      </c>
-      <c r="B158" s="14" t="n"/>
-      <c r="C158" s="14" t="n"/>
-      <c r="D158" s="14" t="n"/>
-      <c r="E158" s="14" t="n"/>
-      <c r="F158" s="14" t="n"/>
-      <c r="G158" s="14" t="n"/>
-      <c r="H158" s="14" t="n"/>
-      <c r="I158" s="14" t="n"/>
-      <c r="J158" s="14" t="n"/>
-      <c r="K158" s="14" t="n"/>
-      <c r="L158" s="14" t="n"/>
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="4" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n"/>
+      <c r="J158" s="4" t="n"/>
+      <c r="K158" s="4" t="n"/>
+      <c r="L158" s="4" t="n"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="26" t="inlineStr">
         <is>
-          <t>• Seguridad social patronal (techo L 11,903.13): IHSS EM 2.5% + IVM 1% + RP 0.2% + RAP 1.5%; INFOP 1% sobre planilla (sin techo).</t>
+          <t>• ISR: 25% + aportación solidaria 5% sobre el excedente de L 1,000,000 (Ley del ISR).</t>
         </is>
       </c>
       <c r="B159" s="14" t="n"/>
@@ -5364,7 +5426,7 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="26" t="inlineStr">
         <is>
-          <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes) — Código del Trabajo.</t>
+          <t>• Depreciación línea recta: maquinaria 10%; vehículos 10%-33% (aquí 20% = 5 años); diferidos 5 años.</t>
         </is>
       </c>
       <c r="B160" s="14" t="n"/>
@@ -5382,7 +5444,7 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="26" t="inlineStr">
         <is>
-          <t>• ISV: la leche fluida/pasteurizada está exenta; no se cobra ISV en ventas.</t>
+          <t>• Seguridad social patronal (techo L 11,903.13): IHSS EM 2.5% + IVM 1% + RP 0.2% + RAP 1.5%; INFOP 1% sobre planilla (sin techo).</t>
         </is>
       </c>
       <c r="B161" s="14" t="n"/>
@@ -5400,7 +5462,7 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="26" t="inlineStr">
         <is>
-          <t>• Impuesto al Activo Neto 1% (deducción L3M; exento en preoperación; se paga solo si supera al ISR).</t>
+          <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes) — Código del Trabajo.</t>
         </is>
       </c>
       <c r="B162" s="14" t="n"/>
@@ -5418,7 +5480,7 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="26" t="inlineStr">
         <is>
-          <t>• Manufactura puede arrastrar pérdidas fiscales 3 años (no aplicado, criterio conservador).</t>
+          <t>• ISV: la leche fluida/pasteurizada está exenta; no se cobra ISV en ventas.</t>
         </is>
       </c>
       <c r="B163" s="14" t="n"/>
@@ -5436,7 +5498,7 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="26" t="inlineStr">
         <is>
-          <t>• Impuestos municipales de Comayagua (industria, comercio y servicios; bienes inmuebles).</t>
+          <t>• Arrastre de pérdidas fiscales: la manufactura puede compensarlas hasta 3 años (aplicado en el flujo, línea de pérdidas acumuladas).</t>
         </is>
       </c>
       <c r="B164" s="14" t="n"/>
@@ -5451,38 +5513,93 @@
       <c r="K164" s="14" t="n"/>
       <c r="L164" s="14" t="n"/>
     </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="26" t="inlineStr">
+        <is>
+          <t>• Impuesto al Activo Neto 1% (deducción L3M; exento en preoperación; se paga solo si supera al ISR).</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="n"/>
+      <c r="C165" s="14" t="n"/>
+      <c r="D165" s="14" t="n"/>
+      <c r="E165" s="14" t="n"/>
+      <c r="F165" s="14" t="n"/>
+      <c r="G165" s="14" t="n"/>
+      <c r="H165" s="14" t="n"/>
+      <c r="I165" s="14" t="n"/>
+      <c r="J165" s="14" t="n"/>
+      <c r="K165" s="14" t="n"/>
+      <c r="L165" s="14" t="n"/>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="26" t="inlineStr">
+        <is>
+          <t>• Capital de trabajo: 1 mes de costos operativos, financiado con crédito de proveedores (CREL/ganaderos).</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="n"/>
+      <c r="C166" s="14" t="n"/>
+      <c r="D166" s="14" t="n"/>
+      <c r="E166" s="14" t="n"/>
+      <c r="F166" s="14" t="n"/>
+      <c r="G166" s="14" t="n"/>
+      <c r="H166" s="14" t="n"/>
+      <c r="I166" s="14" t="n"/>
+      <c r="J166" s="14" t="n"/>
+      <c r="K166" s="14" t="n"/>
+      <c r="L166" s="14" t="n"/>
+    </row>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="26" t="inlineStr">
+        <is>
+          <t>• Impuestos municipales de Comayagua (industria, comercio y servicios; bienes inmuebles).</t>
+        </is>
+      </c>
+      <c r="B167" s="14" t="n"/>
+      <c r="C167" s="14" t="n"/>
+      <c r="D167" s="14" t="n"/>
+      <c r="E167" s="14" t="n"/>
+      <c r="F167" s="14" t="n"/>
+      <c r="G167" s="14" t="n"/>
+      <c r="H167" s="14" t="n"/>
+      <c r="I167" s="14" t="n"/>
+      <c r="J167" s="14" t="n"/>
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="D57:L57"/>
     <mergeCell ref="A164:L164"/>
     <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A133:L133"/>
     <mergeCell ref="A158:L158"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="A163:L163"/>
     <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A113:L113"/>
     <mergeCell ref="A71:L71"/>
     <mergeCell ref="A160:L160"/>
     <mergeCell ref="D56:L56"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="A159:L159"/>
-    <mergeCell ref="A150:L150"/>
-    <mergeCell ref="A144:L144"/>
+    <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A140:L140"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="A81:L81"/>
     <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A156:L156"/>
+    <mergeCell ref="A165:L165"/>
     <mergeCell ref="A161:L161"/>
+    <mergeCell ref="A152:L152"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A167:L167"/>
     <mergeCell ref="D59:L59"/>
-    <mergeCell ref="A157:L157"/>
+    <mergeCell ref="A114:L114"/>
     <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A166:L166"/>
     <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A138:L138"/>
     <mergeCell ref="A88:L88"/>
+    <mergeCell ref="A146:L146"/>
     <mergeCell ref="A162:L162"/>
     <mergeCell ref="C60:L60"/>
     <mergeCell ref="D52:L52"/>
@@ -5497,7 +5614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5711,7 +5828,7 @@
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>Incluir 2 meses de costos, recuperar Año 10</t>
+          <t>1 mes de costos (crédito proveedores), recuperado Año 10</t>
         </is>
       </c>
     </row>
@@ -5721,17 +5838,17 @@
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>Estudio de personal</t>
+          <t>Estudio financiero</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>Faltan cargas sociales de ley</t>
+          <t>No aprovecha arrastre de pérdidas</t>
         </is>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>IHSS+RAP (con techo)+INFOP+aguinaldo+catorceavo</t>
+          <t>Compensar pérdidas de años iniciales (ley, 3 años)</t>
         </is>
       </c>
     </row>
@@ -5741,17 +5858,37 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
+          <t>Estudio de personal</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Faltan cargas sociales de ley</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>IHSS+RAP (con techo)+INFOP+aguinaldo+catorceavo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
           <t>Cuadro 1 / ventas</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Captación lenta (15 clientes) y consumo bajo (60 L/mes)</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Captación agresiva (60→690 clientes) y consumo realista 150 L/mes</t>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Captación lenta (15 clientes)</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Captación agresiva (60→690 clientes), consumo 150 L/mes</t>
         </is>
       </c>
     </row>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -56,7 +56,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -78,11 +78,55 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,6 +194,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,17 +598,17 @@
           <t>SUPUESTOS BASE DEL PROYECTO</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
+      <c r="H4" s="27" t="n"/>
+      <c r="I4" s="27" t="n"/>
+      <c r="J4" s="27" t="n"/>
+      <c r="K4" s="27" t="n"/>
+      <c r="L4" s="28" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -774,17 +820,17 @@
           <t>1. PLAN DE INVERSIONES Y FINANCIAMIENTO</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="B26" s="27" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="27" t="n"/>
+      <c r="I26" s="27" t="n"/>
+      <c r="J26" s="27" t="n"/>
+      <c r="K26" s="27" t="n"/>
+      <c r="L26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1084,17 +1130,17 @@
           <t>2. PRODUCCIÓN Y VENTAS  (volumen = clientes × consumo mensual × 12)</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
+      <c r="B37" s="27" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
+      <c r="I37" s="27" t="n"/>
+      <c r="J37" s="27" t="n"/>
+      <c r="K37" s="27" t="n"/>
+      <c r="L37" s="28" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1345,17 +1391,17 @@
           <t>3. COSTOS VARIABLES  (= litros × costo unitario × inflación)</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
+      <c r="B44" s="27" t="n"/>
+      <c r="C44" s="27" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
+      <c r="H44" s="27" t="n"/>
+      <c r="I44" s="27" t="n"/>
+      <c r="J44" s="27" t="n"/>
+      <c r="K44" s="27" t="n"/>
+      <c r="L44" s="28" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1626,17 +1672,17 @@
           <t>4. COSTO DE PERSONAL  (con prestaciones y seguridad social de ley)</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
+      <c r="F51" s="27" t="n"/>
+      <c r="G51" s="27" t="n"/>
+      <c r="H51" s="27" t="n"/>
+      <c r="I51" s="27" t="n"/>
+      <c r="J51" s="27" t="n"/>
+      <c r="K51" s="27" t="n"/>
+      <c r="L51" s="28" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1655,14 +1701,14 @@
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
+      <c r="E52" s="27" t="n"/>
+      <c r="F52" s="27" t="n"/>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="27" t="n"/>
+      <c r="I52" s="27" t="n"/>
+      <c r="J52" s="27" t="n"/>
+      <c r="K52" s="27" t="n"/>
+      <c r="L52" s="28" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -1678,14 +1724,14 @@
         <v/>
       </c>
       <c r="D53" s="19" t="inlineStr"/>
-      <c r="E53" s="14" t="n"/>
-      <c r="F53" s="14" t="n"/>
-      <c r="G53" s="14" t="n"/>
-      <c r="H53" s="14" t="n"/>
-      <c r="I53" s="14" t="n"/>
-      <c r="J53" s="14" t="n"/>
-      <c r="K53" s="14" t="n"/>
-      <c r="L53" s="14" t="n"/>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="27" t="n"/>
+      <c r="G53" s="27" t="n"/>
+      <c r="H53" s="27" t="n"/>
+      <c r="I53" s="27" t="n"/>
+      <c r="J53" s="27" t="n"/>
+      <c r="K53" s="27" t="n"/>
+      <c r="L53" s="28" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -1701,14 +1747,14 @@
         <v/>
       </c>
       <c r="D54" s="19" t="inlineStr"/>
-      <c r="E54" s="14" t="n"/>
-      <c r="F54" s="14" t="n"/>
-      <c r="G54" s="14" t="n"/>
-      <c r="H54" s="14" t="n"/>
-      <c r="I54" s="14" t="n"/>
-      <c r="J54" s="14" t="n"/>
-      <c r="K54" s="14" t="n"/>
-      <c r="L54" s="14" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="27" t="n"/>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="27" t="n"/>
+      <c r="I54" s="27" t="n"/>
+      <c r="J54" s="27" t="n"/>
+      <c r="K54" s="27" t="n"/>
+      <c r="L54" s="28" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -1724,14 +1770,14 @@
         <v/>
       </c>
       <c r="D55" s="19" t="inlineStr"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="14" t="n"/>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="14" t="n"/>
-      <c r="I55" s="14" t="n"/>
-      <c r="J55" s="14" t="n"/>
-      <c r="K55" s="14" t="n"/>
-      <c r="L55" s="14" t="n"/>
+      <c r="E55" s="27" t="n"/>
+      <c r="F55" s="27" t="n"/>
+      <c r="G55" s="27" t="n"/>
+      <c r="H55" s="27" t="n"/>
+      <c r="I55" s="27" t="n"/>
+      <c r="J55" s="27" t="n"/>
+      <c r="K55" s="27" t="n"/>
+      <c r="L55" s="28" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -1747,14 +1793,14 @@
         <v/>
       </c>
       <c r="D56" s="19" t="inlineStr"/>
-      <c r="E56" s="14" t="n"/>
-      <c r="F56" s="14" t="n"/>
-      <c r="G56" s="14" t="n"/>
-      <c r="H56" s="14" t="n"/>
-      <c r="I56" s="14" t="n"/>
-      <c r="J56" s="14" t="n"/>
-      <c r="K56" s="14" t="n"/>
-      <c r="L56" s="14" t="n"/>
+      <c r="E56" s="27" t="n"/>
+      <c r="F56" s="27" t="n"/>
+      <c r="G56" s="27" t="n"/>
+      <c r="H56" s="27" t="n"/>
+      <c r="I56" s="27" t="n"/>
+      <c r="J56" s="27" t="n"/>
+      <c r="K56" s="27" t="n"/>
+      <c r="L56" s="28" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -1770,14 +1816,14 @@
         <v/>
       </c>
       <c r="D57" s="19" t="inlineStr"/>
-      <c r="E57" s="14" t="n"/>
-      <c r="F57" s="14" t="n"/>
-      <c r="G57" s="14" t="n"/>
-      <c r="H57" s="14" t="n"/>
-      <c r="I57" s="14" t="n"/>
-      <c r="J57" s="14" t="n"/>
-      <c r="K57" s="14" t="n"/>
-      <c r="L57" s="14" t="n"/>
+      <c r="E57" s="27" t="n"/>
+      <c r="F57" s="27" t="n"/>
+      <c r="G57" s="27" t="n"/>
+      <c r="H57" s="27" t="n"/>
+      <c r="I57" s="27" t="n"/>
+      <c r="J57" s="27" t="n"/>
+      <c r="K57" s="27" t="n"/>
+      <c r="L57" s="28" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -1793,14 +1839,14 @@
         <v/>
       </c>
       <c r="D58" s="19" t="inlineStr"/>
-      <c r="E58" s="14" t="n"/>
-      <c r="F58" s="14" t="n"/>
-      <c r="G58" s="14" t="n"/>
-      <c r="H58" s="14" t="n"/>
-      <c r="I58" s="14" t="n"/>
-      <c r="J58" s="14" t="n"/>
-      <c r="K58" s="14" t="n"/>
-      <c r="L58" s="14" t="n"/>
+      <c r="E58" s="27" t="n"/>
+      <c r="F58" s="27" t="n"/>
+      <c r="G58" s="27" t="n"/>
+      <c r="H58" s="27" t="n"/>
+      <c r="I58" s="27" t="n"/>
+      <c r="J58" s="27" t="n"/>
+      <c r="K58" s="27" t="n"/>
+      <c r="L58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="15" t="inlineStr">
@@ -1817,14 +1863,14 @@
         <v/>
       </c>
       <c r="D59" s="20" t="inlineStr"/>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="17" t="n"/>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
-      <c r="L59" s="17" t="n"/>
+      <c r="E59" s="27" t="n"/>
+      <c r="F59" s="27" t="n"/>
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="27" t="n"/>
+      <c r="I59" s="27" t="n"/>
+      <c r="J59" s="27" t="n"/>
+      <c r="K59" s="27" t="n"/>
+      <c r="L59" s="28" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -1837,15 +1883,15 @@
         <v/>
       </c>
       <c r="C60" s="19" t="inlineStr"/>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="n"/>
-      <c r="G60" s="14" t="n"/>
-      <c r="H60" s="14" t="n"/>
-      <c r="I60" s="14" t="n"/>
-      <c r="J60" s="14" t="n"/>
-      <c r="K60" s="14" t="n"/>
-      <c r="L60" s="14" t="n"/>
+      <c r="D60" s="27" t="n"/>
+      <c r="E60" s="27" t="n"/>
+      <c r="F60" s="27" t="n"/>
+      <c r="G60" s="27" t="n"/>
+      <c r="H60" s="27" t="n"/>
+      <c r="I60" s="27" t="n"/>
+      <c r="J60" s="27" t="n"/>
+      <c r="K60" s="27" t="n"/>
+      <c r="L60" s="28" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1965,17 +2011,17 @@
           <t>5. COSTOS FIJOS (anuales)</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
+      <c r="B64" s="27" t="n"/>
+      <c r="C64" s="27" t="n"/>
+      <c r="D64" s="27" t="n"/>
+      <c r="E64" s="27" t="n"/>
+      <c r="F64" s="27" t="n"/>
+      <c r="G64" s="27" t="n"/>
+      <c r="H64" s="27" t="n"/>
+      <c r="I64" s="27" t="n"/>
+      <c r="J64" s="27" t="n"/>
+      <c r="K64" s="27" t="n"/>
+      <c r="L64" s="28" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2247,17 +2293,17 @@
           <t>6. DEPRECIACIONES Y AMORTIZACIONES  (línea recta = Valor ÷ Vida)</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
+      <c r="B71" s="27" t="n"/>
+      <c r="C71" s="27" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
+      <c r="F71" s="27" t="n"/>
+      <c r="G71" s="27" t="n"/>
+      <c r="H71" s="27" t="n"/>
+      <c r="I71" s="27" t="n"/>
+      <c r="J71" s="27" t="n"/>
+      <c r="K71" s="27" t="n"/>
+      <c r="L71" s="28" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2674,17 +2720,17 @@
           <t>7. VALOR DE DESECHO Y CAPITAL DE TRABAJO</t>
         </is>
       </c>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
+      <c r="B81" s="27" t="n"/>
+      <c r="C81" s="27" t="n"/>
+      <c r="D81" s="27" t="n"/>
+      <c r="E81" s="27" t="n"/>
+      <c r="F81" s="27" t="n"/>
+      <c r="G81" s="27" t="n"/>
+      <c r="H81" s="27" t="n"/>
+      <c r="I81" s="27" t="n"/>
+      <c r="J81" s="27" t="n"/>
+      <c r="K81" s="27" t="n"/>
+      <c r="L81" s="28" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2937,17 +2983,17 @@
           <t>8. TABLA DE AMORTIZACIÓN DEL PRÉSTAMO  (cuota anual fija)</t>
         </is>
       </c>
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
-      <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
-      <c r="J88" s="4" t="n"/>
-      <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
+      <c r="B88" s="27" t="n"/>
+      <c r="C88" s="27" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
+      <c r="F88" s="27" t="n"/>
+      <c r="G88" s="27" t="n"/>
+      <c r="H88" s="27" t="n"/>
+      <c r="I88" s="27" t="n"/>
+      <c r="J88" s="27" t="n"/>
+      <c r="K88" s="27" t="n"/>
+      <c r="L88" s="28" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3267,17 +3313,17 @@
           <t>9. FLUJO DE CAJA DEL PROYECTO (SIN FINANCIAMIENTO)</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
-      <c r="J96" s="4" t="n"/>
-      <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
+      <c r="B96" s="27" t="n"/>
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
+      <c r="H96" s="27" t="n"/>
+      <c r="I96" s="27" t="n"/>
+      <c r="J96" s="27" t="n"/>
+      <c r="K96" s="27" t="n"/>
+      <c r="L96" s="28" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -4088,17 +4134,17 @@
           <t>10. FLUJO DE CAJA DEL PROYECTO (CON FINANCIAMIENTO)</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="n"/>
-      <c r="J114" s="4" t="n"/>
-      <c r="K114" s="4" t="n"/>
-      <c r="L114" s="4" t="n"/>
+      <c r="B114" s="27" t="n"/>
+      <c r="C114" s="27" t="n"/>
+      <c r="D114" s="27" t="n"/>
+      <c r="E114" s="27" t="n"/>
+      <c r="F114" s="27" t="n"/>
+      <c r="G114" s="27" t="n"/>
+      <c r="H114" s="27" t="n"/>
+      <c r="I114" s="27" t="n"/>
+      <c r="J114" s="27" t="n"/>
+      <c r="K114" s="27" t="n"/>
+      <c r="L114" s="28" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -5050,17 +5096,17 @@
           <t>11. COSTO DE CAPITAL — PROYECTO PURO (sin financiamiento)</t>
         </is>
       </c>
-      <c r="B135" s="4" t="n"/>
-      <c r="C135" s="4" t="n"/>
-      <c r="D135" s="4" t="n"/>
-      <c r="E135" s="4" t="n"/>
-      <c r="F135" s="4" t="n"/>
-      <c r="G135" s="4" t="n"/>
-      <c r="H135" s="4" t="n"/>
-      <c r="I135" s="4" t="n"/>
-      <c r="J135" s="4" t="n"/>
-      <c r="K135" s="4" t="n"/>
-      <c r="L135" s="4" t="n"/>
+      <c r="B135" s="27" t="n"/>
+      <c r="C135" s="27" t="n"/>
+      <c r="D135" s="27" t="n"/>
+      <c r="E135" s="27" t="n"/>
+      <c r="F135" s="27" t="n"/>
+      <c r="G135" s="27" t="n"/>
+      <c r="H135" s="27" t="n"/>
+      <c r="I135" s="27" t="n"/>
+      <c r="J135" s="27" t="n"/>
+      <c r="K135" s="27" t="n"/>
+      <c r="L135" s="28" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -5148,17 +5194,17 @@
           <t>12. INDICADORES FINANCIEROS — PROYECTO PURO</t>
         </is>
       </c>
-      <c r="B140" s="4" t="n"/>
-      <c r="C140" s="4" t="n"/>
-      <c r="D140" s="4" t="n"/>
-      <c r="E140" s="4" t="n"/>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="n"/>
-      <c r="I140" s="4" t="n"/>
-      <c r="J140" s="4" t="n"/>
-      <c r="K140" s="4" t="n"/>
-      <c r="L140" s="4" t="n"/>
+      <c r="B140" s="27" t="n"/>
+      <c r="C140" s="27" t="n"/>
+      <c r="D140" s="27" t="n"/>
+      <c r="E140" s="27" t="n"/>
+      <c r="F140" s="27" t="n"/>
+      <c r="G140" s="27" t="n"/>
+      <c r="H140" s="27" t="n"/>
+      <c r="I140" s="27" t="n"/>
+      <c r="J140" s="27" t="n"/>
+      <c r="K140" s="27" t="n"/>
+      <c r="L140" s="28" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="21" t="inlineStr">
@@ -5174,11 +5220,11 @@
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
         <is>
-          <t>TIR (Tasa Interna de Retorno)</t>
+          <t>TIRM (Tasa Interna de Retorno Modificada)</t>
         </is>
       </c>
       <c r="B142" s="7">
-        <f>IRR(B111:L111)</f>
+        <f>MIRR(B111:L111,E138,E138)</f>
         <v/>
       </c>
     </row>
@@ -5210,17 +5256,17 @@
           <t>13. COSTO DE CAPITAL — CON FINANCIAMIENTO (WACC)</t>
         </is>
       </c>
-      <c r="B146" s="4" t="n"/>
-      <c r="C146" s="4" t="n"/>
-      <c r="D146" s="4" t="n"/>
-      <c r="E146" s="4" t="n"/>
-      <c r="F146" s="4" t="n"/>
-      <c r="G146" s="4" t="n"/>
-      <c r="H146" s="4" t="n"/>
-      <c r="I146" s="4" t="n"/>
-      <c r="J146" s="4" t="n"/>
-      <c r="K146" s="4" t="n"/>
-      <c r="L146" s="4" t="n"/>
+      <c r="B146" s="27" t="n"/>
+      <c r="C146" s="27" t="n"/>
+      <c r="D146" s="27" t="n"/>
+      <c r="E146" s="27" t="n"/>
+      <c r="F146" s="27" t="n"/>
+      <c r="G146" s="27" t="n"/>
+      <c r="H146" s="27" t="n"/>
+      <c r="I146" s="27" t="n"/>
+      <c r="J146" s="27" t="n"/>
+      <c r="K146" s="27" t="n"/>
+      <c r="L146" s="28" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -5331,17 +5377,17 @@
           <t>14. INDICADORES FINANCIEROS — CON FINANCIAMIENTO</t>
         </is>
       </c>
-      <c r="B152" s="4" t="n"/>
-      <c r="C152" s="4" t="n"/>
-      <c r="D152" s="4" t="n"/>
-      <c r="E152" s="4" t="n"/>
-      <c r="F152" s="4" t="n"/>
-      <c r="G152" s="4" t="n"/>
-      <c r="H152" s="4" t="n"/>
-      <c r="I152" s="4" t="n"/>
-      <c r="J152" s="4" t="n"/>
-      <c r="K152" s="4" t="n"/>
-      <c r="L152" s="4" t="n"/>
+      <c r="B152" s="27" t="n"/>
+      <c r="C152" s="27" t="n"/>
+      <c r="D152" s="27" t="n"/>
+      <c r="E152" s="27" t="n"/>
+      <c r="F152" s="27" t="n"/>
+      <c r="G152" s="27" t="n"/>
+      <c r="H152" s="27" t="n"/>
+      <c r="I152" s="27" t="n"/>
+      <c r="J152" s="27" t="n"/>
+      <c r="K152" s="27" t="n"/>
+      <c r="L152" s="28" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="21" t="inlineStr">
@@ -5357,11 +5403,11 @@
     <row r="154">
       <c r="A154" s="21" t="inlineStr">
         <is>
-          <t>TIR (Tasa Interna de Retorno)</t>
+          <t>TIRM (Tasa Interna de Retorno Modificada)</t>
         </is>
       </c>
       <c r="B154" s="7">
-        <f>IRR(B132:L132)</f>
+        <f>MIRR(B132:L132,E150,E150)</f>
         <v/>
       </c>
     </row>
@@ -5393,17 +5439,17 @@
           <t>15. NOTAS LEGALES (cumplimiento normativo Honduras)</t>
         </is>
       </c>
-      <c r="B158" s="4" t="n"/>
-      <c r="C158" s="4" t="n"/>
-      <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="n"/>
-      <c r="I158" s="4" t="n"/>
-      <c r="J158" s="4" t="n"/>
-      <c r="K158" s="4" t="n"/>
-      <c r="L158" s="4" t="n"/>
+      <c r="B158" s="27" t="n"/>
+      <c r="C158" s="27" t="n"/>
+      <c r="D158" s="27" t="n"/>
+      <c r="E158" s="27" t="n"/>
+      <c r="F158" s="27" t="n"/>
+      <c r="G158" s="27" t="n"/>
+      <c r="H158" s="27" t="n"/>
+      <c r="I158" s="27" t="n"/>
+      <c r="J158" s="27" t="n"/>
+      <c r="K158" s="27" t="n"/>
+      <c r="L158" s="28" t="n"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="26" t="inlineStr">
@@ -5411,17 +5457,17 @@
           <t>• ISR: 25% + aportación solidaria 5% sobre el excedente de L 1,000,000 (Ley del ISR).</t>
         </is>
       </c>
-      <c r="B159" s="14" t="n"/>
-      <c r="C159" s="14" t="n"/>
-      <c r="D159" s="14" t="n"/>
-      <c r="E159" s="14" t="n"/>
-      <c r="F159" s="14" t="n"/>
-      <c r="G159" s="14" t="n"/>
-      <c r="H159" s="14" t="n"/>
-      <c r="I159" s="14" t="n"/>
-      <c r="J159" s="14" t="n"/>
-      <c r="K159" s="14" t="n"/>
-      <c r="L159" s="14" t="n"/>
+      <c r="B159" s="27" t="n"/>
+      <c r="C159" s="27" t="n"/>
+      <c r="D159" s="27" t="n"/>
+      <c r="E159" s="27" t="n"/>
+      <c r="F159" s="27" t="n"/>
+      <c r="G159" s="27" t="n"/>
+      <c r="H159" s="27" t="n"/>
+      <c r="I159" s="27" t="n"/>
+      <c r="J159" s="27" t="n"/>
+      <c r="K159" s="27" t="n"/>
+      <c r="L159" s="28" t="n"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="26" t="inlineStr">
@@ -5429,17 +5475,17 @@
           <t>• Depreciación línea recta: maquinaria 10%; vehículos 10%-33% (aquí 20% = 5 años); diferidos 5 años.</t>
         </is>
       </c>
-      <c r="B160" s="14" t="n"/>
-      <c r="C160" s="14" t="n"/>
-      <c r="D160" s="14" t="n"/>
-      <c r="E160" s="14" t="n"/>
-      <c r="F160" s="14" t="n"/>
-      <c r="G160" s="14" t="n"/>
-      <c r="H160" s="14" t="n"/>
-      <c r="I160" s="14" t="n"/>
-      <c r="J160" s="14" t="n"/>
-      <c r="K160" s="14" t="n"/>
-      <c r="L160" s="14" t="n"/>
+      <c r="B160" s="27" t="n"/>
+      <c r="C160" s="27" t="n"/>
+      <c r="D160" s="27" t="n"/>
+      <c r="E160" s="27" t="n"/>
+      <c r="F160" s="27" t="n"/>
+      <c r="G160" s="27" t="n"/>
+      <c r="H160" s="27" t="n"/>
+      <c r="I160" s="27" t="n"/>
+      <c r="J160" s="27" t="n"/>
+      <c r="K160" s="27" t="n"/>
+      <c r="L160" s="28" t="n"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="26" t="inlineStr">
@@ -5447,17 +5493,17 @@
           <t>• Seguridad social patronal (techo L 11,903.13): IHSS EM 2.5% + IVM 1% + RP 0.2% + RAP 1.5%; INFOP 1% sobre planilla (sin techo).</t>
         </is>
       </c>
-      <c r="B161" s="14" t="n"/>
-      <c r="C161" s="14" t="n"/>
-      <c r="D161" s="14" t="n"/>
-      <c r="E161" s="14" t="n"/>
-      <c r="F161" s="14" t="n"/>
-      <c r="G161" s="14" t="n"/>
-      <c r="H161" s="14" t="n"/>
-      <c r="I161" s="14" t="n"/>
-      <c r="J161" s="14" t="n"/>
-      <c r="K161" s="14" t="n"/>
-      <c r="L161" s="14" t="n"/>
+      <c r="B161" s="27" t="n"/>
+      <c r="C161" s="27" t="n"/>
+      <c r="D161" s="27" t="n"/>
+      <c r="E161" s="27" t="n"/>
+      <c r="F161" s="27" t="n"/>
+      <c r="G161" s="27" t="n"/>
+      <c r="H161" s="27" t="n"/>
+      <c r="I161" s="27" t="n"/>
+      <c r="J161" s="27" t="n"/>
+      <c r="K161" s="27" t="n"/>
+      <c r="L161" s="28" t="n"/>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="26" t="inlineStr">
@@ -5465,17 +5511,17 @@
           <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes) — Código del Trabajo.</t>
         </is>
       </c>
-      <c r="B162" s="14" t="n"/>
-      <c r="C162" s="14" t="n"/>
-      <c r="D162" s="14" t="n"/>
-      <c r="E162" s="14" t="n"/>
-      <c r="F162" s="14" t="n"/>
-      <c r="G162" s="14" t="n"/>
-      <c r="H162" s="14" t="n"/>
-      <c r="I162" s="14" t="n"/>
-      <c r="J162" s="14" t="n"/>
-      <c r="K162" s="14" t="n"/>
-      <c r="L162" s="14" t="n"/>
+      <c r="B162" s="27" t="n"/>
+      <c r="C162" s="27" t="n"/>
+      <c r="D162" s="27" t="n"/>
+      <c r="E162" s="27" t="n"/>
+      <c r="F162" s="27" t="n"/>
+      <c r="G162" s="27" t="n"/>
+      <c r="H162" s="27" t="n"/>
+      <c r="I162" s="27" t="n"/>
+      <c r="J162" s="27" t="n"/>
+      <c r="K162" s="27" t="n"/>
+      <c r="L162" s="28" t="n"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="26" t="inlineStr">
@@ -5483,17 +5529,17 @@
           <t>• ISV: la leche fluida/pasteurizada está exenta; no se cobra ISV en ventas.</t>
         </is>
       </c>
-      <c r="B163" s="14" t="n"/>
-      <c r="C163" s="14" t="n"/>
-      <c r="D163" s="14" t="n"/>
-      <c r="E163" s="14" t="n"/>
-      <c r="F163" s="14" t="n"/>
-      <c r="G163" s="14" t="n"/>
-      <c r="H163" s="14" t="n"/>
-      <c r="I163" s="14" t="n"/>
-      <c r="J163" s="14" t="n"/>
-      <c r="K163" s="14" t="n"/>
-      <c r="L163" s="14" t="n"/>
+      <c r="B163" s="27" t="n"/>
+      <c r="C163" s="27" t="n"/>
+      <c r="D163" s="27" t="n"/>
+      <c r="E163" s="27" t="n"/>
+      <c r="F163" s="27" t="n"/>
+      <c r="G163" s="27" t="n"/>
+      <c r="H163" s="27" t="n"/>
+      <c r="I163" s="27" t="n"/>
+      <c r="J163" s="27" t="n"/>
+      <c r="K163" s="27" t="n"/>
+      <c r="L163" s="28" t="n"/>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="26" t="inlineStr">
@@ -5501,17 +5547,17 @@
           <t>• Arrastre de pérdidas fiscales: la manufactura puede compensarlas hasta 3 años (aplicado en el flujo, línea de pérdidas acumuladas).</t>
         </is>
       </c>
-      <c r="B164" s="14" t="n"/>
-      <c r="C164" s="14" t="n"/>
-      <c r="D164" s="14" t="n"/>
-      <c r="E164" s="14" t="n"/>
-      <c r="F164" s="14" t="n"/>
-      <c r="G164" s="14" t="n"/>
-      <c r="H164" s="14" t="n"/>
-      <c r="I164" s="14" t="n"/>
-      <c r="J164" s="14" t="n"/>
-      <c r="K164" s="14" t="n"/>
-      <c r="L164" s="14" t="n"/>
+      <c r="B164" s="27" t="n"/>
+      <c r="C164" s="27" t="n"/>
+      <c r="D164" s="27" t="n"/>
+      <c r="E164" s="27" t="n"/>
+      <c r="F164" s="27" t="n"/>
+      <c r="G164" s="27" t="n"/>
+      <c r="H164" s="27" t="n"/>
+      <c r="I164" s="27" t="n"/>
+      <c r="J164" s="27" t="n"/>
+      <c r="K164" s="27" t="n"/>
+      <c r="L164" s="28" t="n"/>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="26" t="inlineStr">
@@ -5519,17 +5565,17 @@
           <t>• Impuesto al Activo Neto 1% (deducción L3M; exento en preoperación; se paga solo si supera al ISR).</t>
         </is>
       </c>
-      <c r="B165" s="14" t="n"/>
-      <c r="C165" s="14" t="n"/>
-      <c r="D165" s="14" t="n"/>
-      <c r="E165" s="14" t="n"/>
-      <c r="F165" s="14" t="n"/>
-      <c r="G165" s="14" t="n"/>
-      <c r="H165" s="14" t="n"/>
-      <c r="I165" s="14" t="n"/>
-      <c r="J165" s="14" t="n"/>
-      <c r="K165" s="14" t="n"/>
-      <c r="L165" s="14" t="n"/>
+      <c r="B165" s="27" t="n"/>
+      <c r="C165" s="27" t="n"/>
+      <c r="D165" s="27" t="n"/>
+      <c r="E165" s="27" t="n"/>
+      <c r="F165" s="27" t="n"/>
+      <c r="G165" s="27" t="n"/>
+      <c r="H165" s="27" t="n"/>
+      <c r="I165" s="27" t="n"/>
+      <c r="J165" s="27" t="n"/>
+      <c r="K165" s="27" t="n"/>
+      <c r="L165" s="28" t="n"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="26" t="inlineStr">
@@ -5537,17 +5583,17 @@
           <t>• Capital de trabajo: 1 mes de costos operativos, financiado con crédito de proveedores (CREL/ganaderos).</t>
         </is>
       </c>
-      <c r="B166" s="14" t="n"/>
-      <c r="C166" s="14" t="n"/>
-      <c r="D166" s="14" t="n"/>
-      <c r="E166" s="14" t="n"/>
-      <c r="F166" s="14" t="n"/>
-      <c r="G166" s="14" t="n"/>
-      <c r="H166" s="14" t="n"/>
-      <c r="I166" s="14" t="n"/>
-      <c r="J166" s="14" t="n"/>
-      <c r="K166" s="14" t="n"/>
-      <c r="L166" s="14" t="n"/>
+      <c r="B166" s="27" t="n"/>
+      <c r="C166" s="27" t="n"/>
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="27" t="n"/>
+      <c r="F166" s="27" t="n"/>
+      <c r="G166" s="27" t="n"/>
+      <c r="H166" s="27" t="n"/>
+      <c r="I166" s="27" t="n"/>
+      <c r="J166" s="27" t="n"/>
+      <c r="K166" s="27" t="n"/>
+      <c r="L166" s="28" t="n"/>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="26" t="inlineStr">
@@ -5555,17 +5601,17 @@
           <t>• Impuestos municipales de Comayagua (industria, comercio y servicios; bienes inmuebles).</t>
         </is>
       </c>
-      <c r="B167" s="14" t="n"/>
-      <c r="C167" s="14" t="n"/>
-      <c r="D167" s="14" t="n"/>
-      <c r="E167" s="14" t="n"/>
-      <c r="F167" s="14" t="n"/>
-      <c r="G167" s="14" t="n"/>
-      <c r="H167" s="14" t="n"/>
-      <c r="I167" s="14" t="n"/>
-      <c r="J167" s="14" t="n"/>
-      <c r="K167" s="14" t="n"/>
-      <c r="L167" s="14" t="n"/>
+      <c r="B167" s="27" t="n"/>
+      <c r="C167" s="27" t="n"/>
+      <c r="D167" s="27" t="n"/>
+      <c r="E167" s="27" t="n"/>
+      <c r="F167" s="27" t="n"/>
+      <c r="G167" s="27" t="n"/>
+      <c r="H167" s="27" t="n"/>
+      <c r="I167" s="27" t="n"/>
+      <c r="J167" s="27" t="n"/>
+      <c r="K167" s="27" t="n"/>
+      <c r="L167" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="34">

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -1297,7 +1297,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Precio de venta (Lps/litro)</t>
+          <t>Precio de venta (Lps/litro) — base 28 indexado a inflación 4.5%</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
@@ -1306,32 +1306,41 @@
       <c r="C41" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>37</v>
+      <c r="D41" s="12">
+        <f>C41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="E41" s="12">
+        <f>D41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="F41" s="12">
+        <f>E41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="G41" s="12">
+        <f>F41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="H41" s="12">
+        <f>G41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="I41" s="12">
+        <f>H41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="J41" s="12">
+        <f>I41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="K41" s="12">
+        <f>J41*(1+$B$11)</f>
+        <v/>
+      </c>
+      <c r="L41" s="12">
+        <f>K41*(1+$B$11)</f>
+        <v/>
       </c>
     </row>
     <row r="42">

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudio Financiero" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correcciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -581,14 +580,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PRODUCTORA DE LECHE PASTEURIZADA «PURA» — Flujo de Caja del Proyecto</t>
+          <t>Estudio Financiero del Proyecto</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Estudio financiero conforme a la normativa de Honduras · cifras en Lempiras · toda celda de resultado es fórmula</t>
+          <t>Productora de Leche Pasteurizada «Pura»</t>
         </is>
       </c>
     </row>
@@ -5661,293 +5660,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Correcciones a realizar en el documento de tesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Dónde en la tesis</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Qué está mal</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Corrección</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Cuadro 6 / Costo de personal</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>Planilla mensual (L92,600) usada como costo anual</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Anualizar ×12 + aguinaldo + catorceavo + cargas patronales con techo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="26" t="inlineStr">
-        <is>
-          <t>Cuadros 5 y 6</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="inlineStr">
-        <is>
-          <t>Personal contado dos veces</t>
-        </is>
-      </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>Dejarlo en una sola línea</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>Cuadros 5 y 6</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>Costos mensuales usados como anuales</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>Multiplicar por 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>Costos fijos (leche L390,000)</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>Leche, empaque y combustible como fijos</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Volverlos variables (por litro vendido)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>Gastos administrativos</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Suman L21,600 pero dice L22,600</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>Corregir la suma</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>Cuadro 3 (depreciación)</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Camión con vida de 3 años</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>Vida útil 5 años (rango legal 10-33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>Estudio financiero</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>No aplica ISR</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>ISR 25% + 5% solidaria (renta &gt; L1M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Estudio financiero</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>No define tasa de descuento ni WACC</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>Tasa de descuento 15% y WACC calculado</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Estudio financiero</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>No incluye capital de trabajo</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>1 mes de costos (crédito proveedores), recuperado Año 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Estudio financiero</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>No aprovecha arrastre de pérdidas</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>Compensar pérdidas de años iniciales (ley, 3 años)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Estudio de personal</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Faltan cargas sociales de ley</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>IHSS+RAP (con techo)+INFOP+aguinaldo+catorceavo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Cuadro 1 / ventas</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>Captación lenta (15 clientes)</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>Captación agresiva (60→690 clientes), consumo 150 L/mes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudio Financiero" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explicación del estudio" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +35,23 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -125,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -195,6 +213,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1032,7 +1059,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Gastos diferidos (preoperativos + legales)</t>
+          <t>Gastos diferidos preoperativos y legales</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
@@ -1126,7 +1153,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2. PRODUCCIÓN Y VENTAS  (volumen = clientes × consumo mensual × 12)</t>
+          <t>2. PRODUCCIÓN Y VENTAS</t>
         </is>
       </c>
       <c r="B37" s="27" t="n"/>
@@ -1296,7 +1323,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Precio de venta (Lps/litro) — base 28 indexado a inflación 4.5%</t>
+          <t>Precio de venta (Lps/litro)</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
@@ -1345,7 +1372,7 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>INGRESOS POR VENTAS  (= volumen × precio; leche exenta de ISV)</t>
+          <t>INGRESOS POR VENTAS</t>
         </is>
       </c>
       <c r="B42" s="16">
@@ -1396,7 +1423,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3. COSTOS VARIABLES  (= litros × costo unitario × inflación)</t>
+          <t>3. COSTOS VARIABLES</t>
         </is>
       </c>
       <c r="B44" s="27" t="n"/>
@@ -1677,7 +1704,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4. COSTO DE PERSONAL  (con prestaciones y seguridad social de ley)</t>
+          <t>4. COSTO DE PERSONAL</t>
         </is>
       </c>
       <c r="B51" s="27" t="n"/>
@@ -1859,7 +1886,7 @@
     <row r="59">
       <c r="A59" s="15" t="inlineStr">
         <is>
-          <t>Planilla mensual total  /  base cotizable total</t>
+          <t>Planilla mensual y base cotizable</t>
         </is>
       </c>
       <c r="B59" s="16">
@@ -1883,7 +1910,7 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Cargas patronales mensuales  (base cotizable × 5.2% + planilla × 1% INFOP)</t>
+          <t>Cargas patronales mensuales</t>
         </is>
       </c>
       <c r="B60" s="12">
@@ -1966,7 +1993,7 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Costo anual de personal  (planilla × 14 meses + cargas patronales × 12)</t>
+          <t>Costo anual de personal</t>
         </is>
       </c>
       <c r="B62" s="12" t="n">
@@ -2096,7 +2123,7 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Costos fijos operativos (mensual × 12 × inflación)</t>
+          <t>Costos fijos operativos</t>
         </is>
       </c>
       <c r="B66" s="12" t="n">
@@ -2146,7 +2173,7 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Gastos administrativos (mensual × 12 × inflación)</t>
+          <t>Gastos administrativos</t>
         </is>
       </c>
       <c r="B67" s="12" t="n">
@@ -2196,7 +2223,7 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Personal (de la sección 4)</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B68" s="12">
@@ -2298,7 +2325,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6. DEPRECIACIONES Y AMORTIZACIONES  (línea recta = Valor ÷ Vida)</t>
+          <t>6. DEPRECIACIONES Y AMORTIZACIONES</t>
         </is>
       </c>
       <c r="B71" s="27" t="n"/>
@@ -2845,7 +2872,7 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Capital de trabajo requerido (= (variables+fijos) × meses ÷ 12)</t>
+          <t>Capital de trabajo requerido</t>
         </is>
       </c>
       <c r="B84" s="12">
@@ -2988,7 +3015,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8. TABLA DE AMORTIZACIÓN DEL PRÉSTAMO  (cuota anual fija)</t>
+          <t>8. TABLA DE AMORTIZACIÓN DEL PRÉSTAMO</t>
         </is>
       </c>
       <c r="B88" s="27" t="n"/>
@@ -3168,7 +3195,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Intereses (= saldo × tasa)</t>
+          <t>Intereses</t>
         </is>
       </c>
       <c r="B92" s="12" t="n">
@@ -3218,7 +3245,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Cuota total (= abono + intereses)</t>
+          <t>Cuota total</t>
         </is>
       </c>
       <c r="B93" s="12" t="n">
@@ -3652,7 +3679,7 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Pérdidas fiscales acumuladas (arrastre 3 años, manufactura)</t>
+          <t>Pérdidas fiscales acumuladas</t>
         </is>
       </c>
       <c r="B103" s="12" t="n">
@@ -3702,7 +3729,7 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>(−) Impuesto sobre la renta (25% + 5% solidaria, neto de pérdidas)</t>
+          <t>(−) Impuesto sobre la renta</t>
         </is>
       </c>
       <c r="B104" s="12" t="n">
@@ -4372,7 +4399,7 @@
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>(−) Gastos financieros (intereses)</t>
+          <t>(−) Gastos financieros</t>
         </is>
       </c>
       <c r="B119" s="12" t="n">
@@ -4523,7 +4550,7 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>Pérdidas fiscales acumuladas (arrastre 3 años, manufactura)</t>
+          <t>Pérdidas fiscales acumuladas</t>
         </is>
       </c>
       <c r="B122" s="12" t="n">
@@ -4573,7 +4600,7 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>(−) Impuesto sobre la renta (25% + 5% solidaria, neto de pérdidas)</t>
+          <t>(−) Impuesto sobre la renta</t>
         </is>
       </c>
       <c r="B123" s="12" t="n">
@@ -5101,7 +5128,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>11. COSTO DE CAPITAL — PROYECTO PURO (sin financiamiento)</t>
+          <t>11. COSTO DE CAPITAL DEL PROYECTO PURO</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -5153,7 +5180,7 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>Recursos propios (100%)</t>
+          <t>Recursos propios</t>
         </is>
       </c>
       <c r="B137" s="12">
@@ -5176,7 +5203,7 @@
     <row r="138">
       <c r="A138" s="15" t="inlineStr">
         <is>
-          <t>TOTAL / Tasa de descuento del proyecto</t>
+          <t>Tasa de descuento del proyecto</t>
         </is>
       </c>
       <c r="B138" s="16">
@@ -5199,7 +5226,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>12. INDICADORES FINANCIEROS — PROYECTO PURO</t>
+          <t>12. INDICADORES FINANCIEROS DEL PROYECTO PURO</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -5217,7 +5244,7 @@
     <row r="141">
       <c r="A141" s="21" t="inlineStr">
         <is>
-          <t>VAN (Valor Actual Neto)</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="B141" s="8">
@@ -5228,7 +5255,7 @@
     <row r="142">
       <c r="A142" s="21" t="inlineStr">
         <is>
-          <t>TIRM (Tasa Interna de Retorno Modificada)</t>
+          <t>TIRM</t>
         </is>
       </c>
       <c r="B142" s="7">
@@ -5239,7 +5266,7 @@
     <row r="143">
       <c r="A143" s="21" t="inlineStr">
         <is>
-          <t>PRI (años de recuperación)</t>
+          <t>PRI (años)</t>
         </is>
       </c>
       <c r="B143" s="9">
@@ -5261,7 +5288,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>13. COSTO DE CAPITAL — CON FINANCIAMIENTO (WACC)</t>
+          <t>13. COSTO DE CAPITAL CON FINANCIAMIENTO (WACC)</t>
         </is>
       </c>
       <c r="B146" s="27" t="n"/>
@@ -5313,7 +5340,7 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>Préstamo bancario (deuda, después de impuestos)</t>
+          <t>Préstamo bancario</t>
         </is>
       </c>
       <c r="B148" s="12">
@@ -5336,7 +5363,7 @@
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>Recursos propios (patrimonio)</t>
+          <t>Recursos propios</t>
         </is>
       </c>
       <c r="B149" s="12">
@@ -5359,7 +5386,7 @@
     <row r="150">
       <c r="A150" s="15" t="inlineStr">
         <is>
-          <t>TOTAL / WACC</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="B150" s="16">
@@ -5382,7 +5409,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>14. INDICADORES FINANCIEROS — CON FINANCIAMIENTO</t>
+          <t>14. INDICADORES FINANCIEROS CON FINANCIAMIENTO</t>
         </is>
       </c>
       <c r="B152" s="27" t="n"/>
@@ -5400,7 +5427,7 @@
     <row r="153">
       <c r="A153" s="21" t="inlineStr">
         <is>
-          <t>VAN (Valor Actual Neto)</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="B153" s="8">
@@ -5411,7 +5438,7 @@
     <row r="154">
       <c r="A154" s="21" t="inlineStr">
         <is>
-          <t>TIRM (Tasa Interna de Retorno Modificada)</t>
+          <t>TIRM</t>
         </is>
       </c>
       <c r="B154" s="7">
@@ -5422,7 +5449,7 @@
     <row r="155">
       <c r="A155" s="21" t="inlineStr">
         <is>
-          <t>PRI (años de recuperación)</t>
+          <t>PRI (años)</t>
         </is>
       </c>
       <c r="B155" s="9">
@@ -5516,7 +5543,7 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="26" t="inlineStr">
         <is>
-          <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes) — Código del Trabajo.</t>
+          <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes), Código del Trabajo.</t>
         </is>
       </c>
       <c r="B162" s="27" t="n"/>
@@ -5660,4 +5687,214 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="118" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Explicación del Estudio Financiero</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Productora de Leche Pasteurizada «Pura»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>El estudio mide si conviene montar la planta de leche pasteurizada Pura. Proyecta los ingresos, los costos y el flujo de caja del proyecto durante diez años y calcula los indicadores de rentabilidad en dos escenarios: financiado con recursos propios y financiado con préstamo bancario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Supuestos base</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Todas las cifras están en Lempiras. La inflación anual es de 4.5% y se aplica por igual a los precios de venta y a los costos, para que el margen del negocio no se distorsione. El impuesto sobre la renta es de 25%, más una aportación solidaria de 5% sobre la parte de la utilidad que supera un millón de Lempiras. El proyecto se financia mitad con préstamo bancario al 14% anual y mitad con recursos propios. La tasa de descuento del proyecto puro es de 15% y el costo promedio ponderado de capital del escenario con financiamiento es de 12.75%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Cómo se construye el estudio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>1. Plan de inversiones. Reúne la maquinaria, el camión, los gastos diferidos y el capital de trabajo inicial. La inversión total es de 1,782,858 Lempiras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>2. Producción y ventas. El volumen se obtiene multiplicando los clientes por el consumo mensual de 150 litros y por 12 meses. El precio parte de 28 Lempiras por litro y sube cada año con la inflación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>3. Costos variables. Incluyen la leche cruda con merma, el empaque y el combustible de reparto. Crecen con el volumen y con la inflación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>4. Costo de personal. Seis puestos con salario, aguinaldo, catorceavo mes y las cargas de seguridad social calculadas sobre el techo de cotización de ley.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>5. Costos fijos. Reúnen los costos fijos operativos, los gastos administrativos y el personal, todos ajustados por inflación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>6. Depreciación y amortización. Se calcula por línea recta. La maquinaria se deprecia en diez años, el camión en cinco años y los gastos diferidos se amortizan en cinco años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>7. Valor de desecho y capital de trabajo. El capital de trabajo equivale a un mes de costos operativos y se recupera en el último año.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>8. Amortización del préstamo. Muestra la cuota anual fija, los intereses y los abonos a capital del préstamo bancario a cinco años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>9 y 10. Flujo de caja. Arma el flujo del proyecto sin financiamiento y con financiamiento. A la utilidad se le restan los impuestos, aprovechando el arrastre de pérdidas de los primeros años, y se le suman las partidas que no son salida de efectivo, como la depreciación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>11 a 14. Costo de capital e indicadores. Con la tasa de descuento y el WACC se calculan el VAN, la TIRM, el período de recuperación y la relación beneficio/costo en los dos escenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>Qué significan los indicadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>El VAN es el valor de hoy de todo el efectivo que deja el proyecto después de cubrir la inversión; si es positivo, el proyecto crea valor. La TIRM es el rendimiento anual del proyecto suponiendo que las ganancias se reinvierten al costo de capital, por lo que resulta más realista que la TIR simple. El PRI es el tiempo, en años, que tarda en recuperarse la inversión. La relación beneficio/costo compara el valor presente de los ingresos con el de los egresos; si es mayor que uno, conviene invertir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Resultados</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Proyecto puro: VAN de 15,452,178 Lempiras, TIRM de 40.52%, recuperación en 3.65 años y relación beneficio/costo de 1.23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>Con financiamiento: VAN de 18,350,392 Lempiras, TIRM de 42.71%, recuperación en 3.63 años y relación beneficio/costo de 1.24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>En los dos escenarios el proyecto recupera la inversión antes de cuatro años y rinde por encima de la tasa exigida, por lo que es financieramente viable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Cumplimiento legal en Honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>El estudio aplica el impuesto sobre la renta de 25% más 5% de aportación solidaria, la depreciación por línea recta permitida por el reglamento (vehículos entre 10% y 33%, aquí 20%), la seguridad social patronal con su techo de cotización, el aguinaldo y el catorceavo mes del Código del Trabajo, la exención del impuesto sobre ventas para la leche fluida, el arrastre de pérdidas de hasta tres años para la manufactura y los impuestos municipales de Comayagua.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -5128,7 +5128,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>11. COSTO DE CAPITAL DEL PROYECTO PURO</t>
+          <t>11. COSTO DE CAPITAL SIN FINANCIAMIENTO</t>
         </is>
       </c>
       <c r="B135" s="27" t="n"/>
@@ -5226,7 +5226,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>12. INDICADORES FINANCIEROS DEL PROYECTO PURO</t>
+          <t>12. INDICADORES FINANCIEROS SIN FINANCIAMIENTO</t>
         </is>
       </c>
       <c r="B140" s="27" t="n"/>
@@ -5745,7 +5745,7 @@
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>Todas las cifras están en Lempiras. La inflación anual es de 4.5% y se aplica por igual a los precios de venta y a los costos, para que el margen del negocio no se distorsione. El impuesto sobre la renta es de 25%, más una aportación solidaria de 5% sobre la parte de la utilidad que supera un millón de Lempiras. El proyecto se financia mitad con préstamo bancario al 14% anual y mitad con recursos propios. La tasa de descuento del proyecto puro es de 15% y el costo promedio ponderado de capital del escenario con financiamiento es de 12.75%.</t>
+          <t>Todas las cifras están en Lempiras. La inflación anual es de 4.5% y se aplica por igual a los precios de venta y a los costos, para que el margen del negocio no se distorsione. El impuesto sobre la renta es de 25%, más una aportación solidaria de 5% sobre la parte de la utilidad que supera un millón de Lempiras. El proyecto se financia mitad con préstamo bancario al 14% anual y mitad con recursos propios. La tasa de descuento del escenario sin financiamiento es de 15% y el costo promedio ponderado de capital del escenario con financiamiento es de 12.75%.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>Proyecto puro: VAN de 15,452,178 Lempiras, TIRM de 40.52%, recuperación en 3.65 años y relación beneficio/costo de 1.23.</t>
+          <t>Sin financiamiento: VAN de 15,452,178 Lempiras, TIRM de 40.52%, recuperación en 3.65 años y relación beneficio/costo de 1.23.</t>
         </is>
       </c>
     </row>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -773,11 +773,11 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Aporte patronal con techo (IHSS EM 2.5%+IVM 1%+RP 0.2%+RAP 1.5%)</t>
+          <t>Aporte patronal IHSS con techo (EM 5% + IVM 2% + RP 0.2%)</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.052</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -793,11 +793,11 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Techo mensual de cotización IHSS/RAP (Lps)</t>
+          <t>Techo mensual de cotización IHSS (Lps)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>11903.13</v>
+        <v>11109.36</v>
       </c>
     </row>
     <row r="21">
@@ -5525,7 +5525,7 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="26" t="inlineStr">
         <is>
-          <t>• Seguridad social patronal (techo L 11,903.13): IHSS EM 2.5% + IVM 1% + RP 0.2% + RAP 1.5%; INFOP 1% sobre planilla (sin techo).</t>
+          <t>• Seguridad social patronal (techo L 11,109.36): IHSS EM 5% + IVM 2% + RP 0.2% = 7.2%; INFOP 1% sobre planilla sin techo. El RAP (1.5%) es opcional desde el fallo de 2022.</t>
         </is>
       </c>
       <c r="B161" s="27" t="n"/>
@@ -5762,7 +5762,7 @@
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>1. Plan de inversiones. Reúne la maquinaria, el camión, los gastos diferidos y el capital de trabajo inicial. La inversión total es de 1,782,858 Lempiras.</t>
+          <t>1. Plan de inversiones. Reúne la maquinaria, el camión, los gastos diferidos y el capital de trabajo inicial. La inversión total es de 1,784,058 Lempiras.</t>
         </is>
       </c>
     </row>
@@ -5859,14 +5859,14 @@
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>Sin financiamiento: VAN de 15,452,178 Lempiras, TIRM de 40.52%, recuperación en 3.65 años y relación beneficio/costo de 1.23.</t>
+          <t>Sin financiamiento: VAN de 15,389,173 Lempiras, TIRM de 40.40%, recuperación en 3.67 años y relación beneficio/costo de 1.23.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>Con financiamiento: VAN de 18,350,392 Lempiras, TIRM de 42.71%, recuperación en 3.63 años y relación beneficio/costo de 1.24.</t>
+          <t>Con financiamiento: VAN de 18,282,159 Lempiras, TIRM de 42.49%, recuperación en 3.66 años y relación beneficio/costo de 1.24.</t>
         </is>
       </c>
     </row>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L167"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3632,47 +3632,47 @@
         </is>
       </c>
       <c r="B102" s="16">
-        <f>B98-B99-B100-B101</f>
+        <f>B98-B99-B100-B101-B170</f>
         <v/>
       </c>
       <c r="C102" s="16">
-        <f>C98-C99-C100-C101</f>
+        <f>C98-C99-C100-C101-C170</f>
         <v/>
       </c>
       <c r="D102" s="16">
-        <f>D98-D99-D100-D101</f>
+        <f>D98-D99-D100-D101-D170</f>
         <v/>
       </c>
       <c r="E102" s="16">
-        <f>E98-E99-E100-E101</f>
+        <f>E98-E99-E100-E101-E170</f>
         <v/>
       </c>
       <c r="F102" s="16">
-        <f>F98-F99-F100-F101</f>
+        <f>F98-F99-F100-F101-F170</f>
         <v/>
       </c>
       <c r="G102" s="16">
-        <f>G98-G99-G100-G101</f>
+        <f>G98-G99-G100-G101-G170</f>
         <v/>
       </c>
       <c r="H102" s="16">
-        <f>H98-H99-H100-H101</f>
+        <f>H98-H99-H100-H101-H170</f>
         <v/>
       </c>
       <c r="I102" s="16">
-        <f>I98-I99-I100-I101</f>
+        <f>I98-I99-I100-I101-I170</f>
         <v/>
       </c>
       <c r="J102" s="16">
-        <f>J98-J99-J100-J101</f>
+        <f>J98-J99-J100-J101-J170</f>
         <v/>
       </c>
       <c r="K102" s="16">
-        <f>K98-K99-K100-K101</f>
+        <f>K98-K99-K100-K101-K170</f>
         <v/>
       </c>
       <c r="L102" s="16">
-        <f>L98-L99-L100-L101</f>
+        <f>L98-L99-L100-L101-L170</f>
         <v/>
       </c>
     </row>
@@ -4503,47 +4503,47 @@
         </is>
       </c>
       <c r="B121" s="16">
-        <f>B116-B117-B118-B119-B120</f>
+        <f>B116-B117-B118-B119-B120-B170</f>
         <v/>
       </c>
       <c r="C121" s="16">
-        <f>C116-C117-C118-C119-C120</f>
+        <f>C116-C117-C118-C119-C120-C170</f>
         <v/>
       </c>
       <c r="D121" s="16">
-        <f>D116-D117-D118-D119-D120</f>
+        <f>D116-D117-D118-D119-D120-D170</f>
         <v/>
       </c>
       <c r="E121" s="16">
-        <f>E116-E117-E118-E119-E120</f>
+        <f>E116-E117-E118-E119-E120-E170</f>
         <v/>
       </c>
       <c r="F121" s="16">
-        <f>F116-F117-F118-F119-F120</f>
+        <f>F116-F117-F118-F119-F120-F170</f>
         <v/>
       </c>
       <c r="G121" s="16">
-        <f>G116-G117-G118-G119-G120</f>
+        <f>G116-G117-G118-G119-G120-G170</f>
         <v/>
       </c>
       <c r="H121" s="16">
-        <f>H116-H117-H118-H119-H120</f>
+        <f>H116-H117-H118-H119-H120-H170</f>
         <v/>
       </c>
       <c r="I121" s="16">
-        <f>I116-I117-I118-I119-I120</f>
+        <f>I116-I117-I118-I119-I120-I170</f>
         <v/>
       </c>
       <c r="J121" s="16">
-        <f>J116-J117-J118-J119-J120</f>
+        <f>J116-J117-J118-J119-J120-J170</f>
         <v/>
       </c>
       <c r="K121" s="16">
-        <f>K116-K117-K118-K119-K120</f>
+        <f>K116-K117-K118-K119-K120-K170</f>
         <v/>
       </c>
       <c r="L121" s="16">
-        <f>L116-L117-L118-L119-L120</f>
+        <f>L116-L117-L118-L119-L120-L170</f>
         <v/>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="26" t="inlineStr">
         <is>
-          <t>• Impuestos municipales de Comayagua (industria, comercio y servicios; bienes inmuebles).</t>
+          <t>• Impuesto municipal de Comayagua: Industria, Comercio y Servicios sobre ingresos (Art. 78, escala por millar); el Impuesto sobre Bienes Inmuebles no se cuantifica por ser terreno e instalación propios sin avalúo catastral.</t>
         </is>
       </c>
       <c r="B167" s="27" t="n"/>
@@ -5647,6 +5647,64 @@
       <c r="J167" s="27" t="n"/>
       <c r="K167" s="27" t="n"/>
       <c r="L167" s="28" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>16. IMPUESTO MUNICIPAL DE COMAYAGUA (ICS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>Impuesto de Industria, Comercio y Servicios (sobre ingresos, Art. 78 Ley de Municipalidades)</t>
+        </is>
+      </c>
+      <c r="B170" s="12">
+        <f>0.3/1000*MIN(B42,500000)+0.4/1000*MAX(0,MIN(B42,10000000)-500000)+0.3/1000*MAX(0,MIN(B42,20000000)-10000000)+0.2/1000*MAX(0,MIN(B42,30000000)-20000000)+0.15/1000*MAX(0,B42-30000000)</f>
+        <v/>
+      </c>
+      <c r="C170" s="12">
+        <f>0.3/1000*MIN(C42,500000)+0.4/1000*MAX(0,MIN(C42,10000000)-500000)+0.3/1000*MAX(0,MIN(C42,20000000)-10000000)+0.2/1000*MAX(0,MIN(C42,30000000)-20000000)+0.15/1000*MAX(0,C42-30000000)</f>
+        <v/>
+      </c>
+      <c r="D170" s="12">
+        <f>0.3/1000*MIN(D42,500000)+0.4/1000*MAX(0,MIN(D42,10000000)-500000)+0.3/1000*MAX(0,MIN(D42,20000000)-10000000)+0.2/1000*MAX(0,MIN(D42,30000000)-20000000)+0.15/1000*MAX(0,D42-30000000)</f>
+        <v/>
+      </c>
+      <c r="E170" s="12">
+        <f>0.3/1000*MIN(E42,500000)+0.4/1000*MAX(0,MIN(E42,10000000)-500000)+0.3/1000*MAX(0,MIN(E42,20000000)-10000000)+0.2/1000*MAX(0,MIN(E42,30000000)-20000000)+0.15/1000*MAX(0,E42-30000000)</f>
+        <v/>
+      </c>
+      <c r="F170" s="12">
+        <f>0.3/1000*MIN(F42,500000)+0.4/1000*MAX(0,MIN(F42,10000000)-500000)+0.3/1000*MAX(0,MIN(F42,20000000)-10000000)+0.2/1000*MAX(0,MIN(F42,30000000)-20000000)+0.15/1000*MAX(0,F42-30000000)</f>
+        <v/>
+      </c>
+      <c r="G170" s="12">
+        <f>0.3/1000*MIN(G42,500000)+0.4/1000*MAX(0,MIN(G42,10000000)-500000)+0.3/1000*MAX(0,MIN(G42,20000000)-10000000)+0.2/1000*MAX(0,MIN(G42,30000000)-20000000)+0.15/1000*MAX(0,G42-30000000)</f>
+        <v/>
+      </c>
+      <c r="H170" s="12">
+        <f>0.3/1000*MIN(H42,500000)+0.4/1000*MAX(0,MIN(H42,10000000)-500000)+0.3/1000*MAX(0,MIN(H42,20000000)-10000000)+0.2/1000*MAX(0,MIN(H42,30000000)-20000000)+0.15/1000*MAX(0,H42-30000000)</f>
+        <v/>
+      </c>
+      <c r="I170" s="12">
+        <f>0.3/1000*MIN(I42,500000)+0.4/1000*MAX(0,MIN(I42,10000000)-500000)+0.3/1000*MAX(0,MIN(I42,20000000)-10000000)+0.2/1000*MAX(0,MIN(I42,30000000)-20000000)+0.15/1000*MAX(0,I42-30000000)</f>
+        <v/>
+      </c>
+      <c r="J170" s="12">
+        <f>0.3/1000*MIN(J42,500000)+0.4/1000*MAX(0,MIN(J42,10000000)-500000)+0.3/1000*MAX(0,MIN(J42,20000000)-10000000)+0.2/1000*MAX(0,MIN(J42,30000000)-20000000)+0.15/1000*MAX(0,J42-30000000)</f>
+        <v/>
+      </c>
+      <c r="K170" s="12">
+        <f>0.3/1000*MIN(K42,500000)+0.4/1000*MAX(0,MIN(K42,10000000)-500000)+0.3/1000*MAX(0,MIN(K42,20000000)-10000000)+0.2/1000*MAX(0,MIN(K42,30000000)-20000000)+0.15/1000*MAX(0,K42-30000000)</f>
+        <v/>
+      </c>
+      <c r="L170" s="12">
+        <f>0.3/1000*MIN(L42,500000)+0.4/1000*MAX(0,MIN(L42,10000000)-500000)+0.3/1000*MAX(0,MIN(L42,20000000)-10000000)+0.2/1000*MAX(0,MIN(L42,30000000)-20000000)+0.15/1000*MAX(0,L42-30000000)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="34">
@@ -5859,14 +5917,14 @@
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>Sin financiamiento: VAN de 15,389,173 Lempiras, TIRM de 40.40%, recuperación en 3.67 años y relación beneficio/costo de 1.23.</t>
+          <t>Sin financiamiento: VAN de 15,370,632 Lempiras, TIRM de 40.38%, recuperación en 3.67 años y relación beneficio/costo de 1.23.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>Con financiamiento: VAN de 18,282,159 Lempiras, TIRM de 42.49%, recuperación en 3.66 años y relación beneficio/costo de 1.24.</t>
+          <t>Con financiamiento: VAN de 18,261,296 Lempiras, TIRM de 42.46%, recuperación en 3.66 años y relación beneficio/costo de 1.24.</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5948,7 @@
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
         <is>
-          <t>El estudio aplica el impuesto sobre la renta de 25% más 5% de aportación solidaria, la depreciación por línea recta permitida por el reglamento (vehículos entre 10% y 33%, aquí 20%), la seguridad social patronal con su techo de cotización, el aguinaldo y el catorceavo mes del Código del Trabajo, la exención del impuesto sobre ventas para la leche fluida, el arrastre de pérdidas de hasta tres años para la manufactura y los impuestos municipales de Comayagua.</t>
+          <t>El estudio aplica el impuesto sobre la renta de 25% más 5% de aportación solidaria, la depreciación por línea recta permitida por el reglamento (vehículos entre 10% y 33%, aquí 20%), la seguridad social patronal del 7.2% al IHSS más 1% de INFOP con su techo de cotización, el aguinaldo y el catorceavo mes del Código del Trabajo, la exención del impuesto sobre ventas para la leche fluida, el arrastre de pérdidas de hasta tres años para la manufactura, y el impuesto municipal de Comayagua de Industria, Comercio y Servicios sobre los ingresos anuales según la escala de la Ley de Municipalidades.</t>
         </is>
       </c>
     </row>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -18,30 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -54,6 +37,12 @@
       <color rgb="00000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -64,16 +53,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -81,145 +70,76 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -587,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -624,17 +544,6 @@
           <t>SUPUESTOS BASE DEL PROYECTO</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="28" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -642,186 +551,186 @@
           <t>Parámetro</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Tasa de impuesto sobre la renta (ISR)</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="5" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Aportación solidaria (sobre renta &gt; umbral)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="5" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Umbral aportación solidaria (Lps)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="6" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Tasa de interés del préstamo (anual)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="5" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Porcentaje financiado con préstamo</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Inflación anual</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Tasa de descuento anual (rendimiento mínimo)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="5" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Costo de leche cruda (Lps/litro)</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Merma de proceso</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="5" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Costo de empaque (Lps/litro)</t>
         </is>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="7">
         <f>26000/30000</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Costo de combustible de reparto (Lps/litro)</t>
         </is>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="7">
         <f>26000/30000</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Meses de salario al año (12 + aguinaldo + catorceavo)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="8" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Aporte patronal IHSS con techo (EM 5% + IVM 2% + RP 0.2%)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="5" t="n">
         <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>INFOP patronal (sobre planilla total, sin techo)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="5" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Techo mensual de cotización IHSS (Lps)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="7" t="n">
         <v>11109.36</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Costos fijos operativos (mensual)</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="6" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Gastos administrativos (mensual)</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="6" t="n">
         <v>21600</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Consumo promedio por cliente (litros/mes)</t>
         </is>
@@ -831,12 +740,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Meses de capital de trabajo (crédito de proveedores)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -846,17 +755,6 @@
           <t>1. PLAN DE INVERSIONES Y FINANCIAMIENTO</t>
         </is>
       </c>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -864,291 +762,235 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Recursos propios</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Préstamo</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Vida (años)</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Depreciable</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Tanques de almacenamiento</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="9" t="n">
         <v>360000</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="9">
         <f>B28-D28</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="9">
         <f>B28*$B$10</f>
         <v/>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G28" s="14" t="n"/>
-      <c r="H28" s="14" t="n"/>
-      <c r="I28" s="14" t="n"/>
-      <c r="J28" s="14" t="n"/>
-      <c r="K28" s="14" t="n"/>
-      <c r="L28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Pasteurizador HTST</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="9" t="n">
         <v>150000</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="9">
         <f>B29-D29</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="9">
         <f>B29*$B$10</f>
         <v/>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G29" s="14" t="n"/>
-      <c r="H29" s="14" t="n"/>
-      <c r="I29" s="14" t="n"/>
-      <c r="J29" s="14" t="n"/>
-      <c r="K29" s="14" t="n"/>
-      <c r="L29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Envasadora automática</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="9" t="n">
         <v>260000</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="9">
         <f>B30-D30</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="9">
         <f>B30*$B$10</f>
         <v/>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="13" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sistema de enfriamiento</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="9" t="n">
         <v>125000</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="9">
         <f>B31-D31</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="9">
         <f>B31*$B$10</f>
         <v/>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Camión de distribución</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="9" t="n">
         <v>500000</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="9">
         <f>B32-D32</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="9">
         <f>B32*$B$10</f>
         <v/>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F32" s="13" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Gastos diferidos preoperativos y legales</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="9" t="n">
         <v>76000</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="9">
         <f>B33-D33</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="9">
         <f>B33*$B$10</f>
         <v/>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Amortizable</t>
         </is>
       </c>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Capital de trabajo inicial</t>
         </is>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="9">
         <f>B84</f>
         <v/>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="9">
         <f>B34-D34</f>
         <v/>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="9">
         <f>B34*$B$10</f>
         <v/>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="13" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
-      <c r="I34" s="14" t="n"/>
-      <c r="J34" s="14" t="n"/>
-      <c r="K34" s="14" t="n"/>
-      <c r="L34" s="14" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>TOTAL INVERSIONES</t>
         </is>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="13">
         <f>SUM(B28:B34)</f>
         <v/>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="13">
         <f>SUM(C28:C34)</f>
         <v/>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="13">
         <f>SUM(D28:D34)</f>
         <v/>
       </c>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1156,17 +998,6 @@
           <t>2. PRODUCCIÓN Y VENTAS</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="27" t="n"/>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="28" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1174,248 +1005,248 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Clientes activos</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="12" t="n">
+      <c r="B39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="9" t="n">
         <v>210</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G39" s="9" t="n">
         <v>280</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H39" s="9" t="n">
         <v>350</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I39" s="9" t="n">
         <v>430</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J39" s="9" t="n">
         <v>510</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="K39" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="L39" s="9" t="n">
         <v>690</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Volumen anual (litros)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="12">
+      <c r="B40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9">
         <f>C39*$B$23*12</f>
         <v/>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="9">
         <f>D39*$B$23*12</f>
         <v/>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="9">
         <f>E39*$B$23*12</f>
         <v/>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="9">
         <f>F39*$B$23*12</f>
         <v/>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="9">
         <f>G39*$B$23*12</f>
         <v/>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="9">
         <f>H39*$B$23*12</f>
         <v/>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="9">
         <f>I39*$B$23*12</f>
         <v/>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="9">
         <f>J39*$B$23*12</f>
         <v/>
       </c>
-      <c r="K40" s="12">
+      <c r="K40" s="9">
         <f>K39*$B$23*12</f>
         <v/>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="9">
         <f>L39*$B$23*12</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Precio de venta (Lps/litro)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="12" t="n">
+      <c r="B41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="14">
         <f>C41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="14">
         <f>D41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="14">
         <f>E41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="14">
         <f>F41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="14">
         <f>G41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="14">
         <f>H41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="14">
         <f>I41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="K41" s="12">
+      <c r="K41" s="14">
         <f>J41*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="14">
         <f>K41*(1+$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>INGRESOS POR VENTAS</t>
         </is>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="13">
         <f>B40*B41</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="13">
         <f>C40*C41</f>
         <v/>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="13">
         <f>D40*D41</f>
         <v/>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="13">
         <f>E40*E41</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="13">
         <f>F40*F41</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="13">
         <f>G40*G41</f>
         <v/>
       </c>
-      <c r="H42" s="16">
+      <c r="H42" s="13">
         <f>H40*H41</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="13">
         <f>I40*I41</f>
         <v/>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="13">
         <f>J40*J41</f>
         <v/>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="13">
         <f>K40*K41</f>
         <v/>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="13">
         <f>L40*L41</f>
         <v/>
       </c>
@@ -1426,17 +1257,6 @@
           <t>3. COSTOS VARIABLES</t>
         </is>
       </c>
-      <c r="B44" s="27" t="n"/>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="27" t="n"/>
-      <c r="I44" s="27" t="n"/>
-      <c r="J44" s="27" t="n"/>
-      <c r="K44" s="27" t="n"/>
-      <c r="L44" s="28" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1444,259 +1264,259 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Leche cruda (con merma)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="12">
+      <c r="B46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="9">
         <f>C40*$B$13/(1-$B$14)*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="9">
         <f>D40*$B$13/(1-$B$14)*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="9">
         <f>E40*$B$13/(1-$B$14)*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="9">
         <f>F40*$B$13/(1-$B$14)*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="9">
         <f>G40*$B$13/(1-$B$14)*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="9">
         <f>H40*$B$13/(1-$B$14)*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="9">
         <f>I40*$B$13/(1-$B$14)*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="9">
         <f>J40*$B$13/(1-$B$14)*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="9">
         <f>K40*$B$13/(1-$B$14)*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="9">
         <f>L40*$B$13/(1-$B$14)*(1+$B$11)^10</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Empaque (bolsas)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="12">
+      <c r="B47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="9">
         <f>C40*$B$15*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" s="9">
         <f>D40*$B$15*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="9">
         <f>E40*$B$15*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="9">
         <f>F40*$B$15*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="9">
         <f>G40*$B$15*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="9">
         <f>H40*$B$15*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="9">
         <f>I40*$B$15*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="9">
         <f>J40*$B$15*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="9">
         <f>K40*$B$15*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="9">
         <f>L40*$B$15*(1+$B$11)^10</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Combustible de reparto</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="12">
+      <c r="B48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="9">
         <f>C40*$B$16*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="9">
         <f>D40*$B$16*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="9">
         <f>E40*$B$16*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="9">
         <f>F40*$B$16*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="9">
         <f>G40*$B$16*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="9">
         <f>H40*$B$16*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="9">
         <f>I40*$B$16*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="9">
         <f>J40*$B$16*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="9">
         <f>K40*$B$16*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="9">
         <f>L40*$B$16*(1+$B$11)^10</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>TOTAL COSTOS VARIABLES</t>
         </is>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="13">
         <f>SUM(B46:B48)</f>
         <v/>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="13">
         <f>SUM(C46:C48)</f>
         <v/>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="13">
         <f>SUM(D46:D48)</f>
         <v/>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="13">
         <f>SUM(E46:E48)</f>
         <v/>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="13">
         <f>SUM(F46:F48)</f>
         <v/>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="13">
         <f>SUM(G46:G48)</f>
         <v/>
       </c>
-      <c r="H49" s="16">
+      <c r="H49" s="13">
         <f>SUM(H46:H48)</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="13">
         <f>SUM(I46:I48)</f>
         <v/>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="13">
         <f>SUM(J46:J48)</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="13">
         <f>SUM(K46:K48)</f>
         <v/>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="13">
         <f>SUM(L46:L48)</f>
         <v/>
       </c>
@@ -1707,17 +1527,6 @@
           <t>4. COSTO DE PERSONAL</t>
         </is>
       </c>
-      <c r="B51" s="27" t="n"/>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="27" t="n"/>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
-      <c r="H51" s="27" t="n"/>
-      <c r="I51" s="27" t="n"/>
-      <c r="J51" s="27" t="n"/>
-      <c r="K51" s="27" t="n"/>
-      <c r="L51" s="28" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1725,208 +1534,126 @@
           <t>Cargo</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Salario mensual</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Base cotizable (con techo)</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr"/>
-      <c r="E52" s="27" t="n"/>
-      <c r="F52" s="27" t="n"/>
-      <c r="G52" s="27" t="n"/>
-      <c r="H52" s="27" t="n"/>
-      <c r="I52" s="27" t="n"/>
-      <c r="J52" s="27" t="n"/>
-      <c r="K52" s="27" t="n"/>
-      <c r="L52" s="28" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Gerente de operaciones</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="9" t="n">
         <v>25000</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="9">
         <f>MIN(B53,$B$20)</f>
         <v/>
       </c>
-      <c r="D53" s="19" t="inlineStr"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="27" t="n"/>
-      <c r="G53" s="27" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="27" t="n"/>
-      <c r="J53" s="27" t="n"/>
-      <c r="K53" s="27" t="n"/>
-      <c r="L53" s="28" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Asistente de televenta y facturación</t>
         </is>
       </c>
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="9" t="n">
         <v>17000</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="9">
         <f>MIN(B54,$B$20)</f>
         <v/>
       </c>
-      <c r="D54" s="19" t="inlineStr"/>
-      <c r="E54" s="27" t="n"/>
-      <c r="F54" s="27" t="n"/>
-      <c r="G54" s="27" t="n"/>
-      <c r="H54" s="27" t="n"/>
-      <c r="I54" s="27" t="n"/>
-      <c r="J54" s="27" t="n"/>
-      <c r="K54" s="27" t="n"/>
-      <c r="L54" s="28" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Operador de recibo y despacho</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="9" t="n">
         <v>11300</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="9">
         <f>MIN(B55,$B$20)</f>
         <v/>
       </c>
-      <c r="D55" s="19" t="inlineStr"/>
-      <c r="E55" s="27" t="n"/>
-      <c r="F55" s="27" t="n"/>
-      <c r="G55" s="27" t="n"/>
-      <c r="H55" s="27" t="n"/>
-      <c r="I55" s="27" t="n"/>
-      <c r="J55" s="27" t="n"/>
-      <c r="K55" s="27" t="n"/>
-      <c r="L55" s="28" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Operador de pasteurización y empaque</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="9" t="n">
         <v>11300</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="9">
         <f>MIN(B56,$B$20)</f>
         <v/>
       </c>
-      <c r="D56" s="19" t="inlineStr"/>
-      <c r="E56" s="27" t="n"/>
-      <c r="F56" s="27" t="n"/>
-      <c r="G56" s="27" t="n"/>
-      <c r="H56" s="27" t="n"/>
-      <c r="I56" s="27" t="n"/>
-      <c r="J56" s="27" t="n"/>
-      <c r="K56" s="27" t="n"/>
-      <c r="L56" s="28" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Operador de mantenimiento y aseo</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="9" t="n">
         <v>14000</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="9">
         <f>MIN(B57,$B$20)</f>
         <v/>
       </c>
-      <c r="D57" s="19" t="inlineStr"/>
-      <c r="E57" s="27" t="n"/>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="27" t="n"/>
-      <c r="H57" s="27" t="n"/>
-      <c r="I57" s="27" t="n"/>
-      <c r="J57" s="27" t="n"/>
-      <c r="K57" s="27" t="n"/>
-      <c r="L57" s="28" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Entregador</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n">
+      <c r="B58" s="9" t="n">
         <v>14000</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="9">
         <f>MIN(B58,$B$20)</f>
         <v/>
       </c>
-      <c r="D58" s="19" t="inlineStr"/>
-      <c r="E58" s="27" t="n"/>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="27" t="n"/>
-      <c r="H58" s="27" t="n"/>
-      <c r="I58" s="27" t="n"/>
-      <c r="J58" s="27" t="n"/>
-      <c r="K58" s="27" t="n"/>
-      <c r="L58" s="28" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Planilla mensual y base cotizable</t>
         </is>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="9">
         <f>SUM(B53:B58)</f>
         <v/>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="9">
         <f>SUM(C53:C58)</f>
         <v/>
       </c>
-      <c r="D59" s="20" t="inlineStr"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="27" t="n"/>
-      <c r="H59" s="27" t="n"/>
-      <c r="I59" s="27" t="n"/>
-      <c r="J59" s="27" t="n"/>
-      <c r="K59" s="27" t="n"/>
-      <c r="L59" s="28" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Cargas patronales mensuales</t>
         </is>
       </c>
-      <c r="B60" s="12">
+      <c r="B60" s="9">
         <f>C59*$B$18+B59*$B$19</f>
         <v/>
       </c>
-      <c r="C60" s="19" t="inlineStr"/>
-      <c r="D60" s="27" t="n"/>
-      <c r="E60" s="27" t="n"/>
-      <c r="F60" s="27" t="n"/>
-      <c r="G60" s="27" t="n"/>
-      <c r="H60" s="27" t="n"/>
-      <c r="I60" s="27" t="n"/>
-      <c r="J60" s="27" t="n"/>
-      <c r="K60" s="27" t="n"/>
-      <c r="L60" s="28" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1934,108 +1661,108 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Costo anual de personal</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="12">
+      <c r="B62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E62" s="12">
+      <c r="E62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H62" s="12">
+      <c r="H62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I62" s="12">
+      <c r="I62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J62" s="12">
+      <c r="J62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K62" s="12">
+      <c r="K62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L62" s="12">
+      <c r="L62" s="9">
         <f>(B59*$B$17+B60*12)*(1+$B$11)^10</f>
         <v/>
       </c>
@@ -2046,17 +1773,6 @@
           <t>5. COSTOS FIJOS (anuales)</t>
         </is>
       </c>
-      <c r="B64" s="27" t="n"/>
-      <c r="C64" s="27" t="n"/>
-      <c r="D64" s="27" t="n"/>
-      <c r="E64" s="27" t="n"/>
-      <c r="F64" s="27" t="n"/>
-      <c r="G64" s="27" t="n"/>
-      <c r="H64" s="27" t="n"/>
-      <c r="I64" s="27" t="n"/>
-      <c r="J64" s="27" t="n"/>
-      <c r="K64" s="27" t="n"/>
-      <c r="L64" s="28" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2064,260 +1780,260 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Costos fijos operativos</t>
         </is>
       </c>
-      <c r="B66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="12">
+      <c r="B66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="9">
         <f>$B$21*12*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="9">
         <f>$B$21*12*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E66" s="12">
+      <c r="E66" s="9">
         <f>$B$21*12*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="9">
         <f>$B$21*12*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G66" s="12">
+      <c r="G66" s="9">
         <f>$B$21*12*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H66" s="12">
+      <c r="H66" s="9">
         <f>$B$21*12*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I66" s="12">
+      <c r="I66" s="9">
         <f>$B$21*12*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J66" s="12">
+      <c r="J66" s="9">
         <f>$B$21*12*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K66" s="12">
+      <c r="K66" s="9">
         <f>$B$21*12*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L66" s="12">
+      <c r="L66" s="9">
         <f>$B$21*12*(1+$B$11)^10</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Gastos administrativos</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="12">
+      <c r="B67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="9">
         <f>$B$22*12*(1+$B$11)^1</f>
         <v/>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="9">
         <f>$B$22*12*(1+$B$11)^2</f>
         <v/>
       </c>
-      <c r="E67" s="12">
+      <c r="E67" s="9">
         <f>$B$22*12*(1+$B$11)^3</f>
         <v/>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="9">
         <f>$B$22*12*(1+$B$11)^4</f>
         <v/>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="9">
         <f>$B$22*12*(1+$B$11)^5</f>
         <v/>
       </c>
-      <c r="H67" s="12">
+      <c r="H67" s="9">
         <f>$B$22*12*(1+$B$11)^6</f>
         <v/>
       </c>
-      <c r="I67" s="12">
+      <c r="I67" s="9">
         <f>$B$22*12*(1+$B$11)^7</f>
         <v/>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="9">
         <f>$B$22*12*(1+$B$11)^8</f>
         <v/>
       </c>
-      <c r="K67" s="12">
+      <c r="K67" s="9">
         <f>$B$22*12*(1+$B$11)^9</f>
         <v/>
       </c>
-      <c r="L67" s="12">
+      <c r="L67" s="9">
         <f>$B$22*12*(1+$B$11)^10</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="B68" s="12">
+      <c r="B68" s="9">
         <f>B62</f>
         <v/>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="9">
         <f>C62</f>
         <v/>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="9">
         <f>D62</f>
         <v/>
       </c>
-      <c r="E68" s="12">
+      <c r="E68" s="9">
         <f>E62</f>
         <v/>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="9">
         <f>F62</f>
         <v/>
       </c>
-      <c r="G68" s="12">
+      <c r="G68" s="9">
         <f>G62</f>
         <v/>
       </c>
-      <c r="H68" s="12">
+      <c r="H68" s="9">
         <f>H62</f>
         <v/>
       </c>
-      <c r="I68" s="12">
+      <c r="I68" s="9">
         <f>I62</f>
         <v/>
       </c>
-      <c r="J68" s="12">
+      <c r="J68" s="9">
         <f>J62</f>
         <v/>
       </c>
-      <c r="K68" s="12">
+      <c r="K68" s="9">
         <f>K62</f>
         <v/>
       </c>
-      <c r="L68" s="12">
+      <c r="L68" s="9">
         <f>L62</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>TOTAL COSTOS FIJOS</t>
         </is>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="13">
         <f>SUM(B66:B68)</f>
         <v/>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="13">
         <f>SUM(C66:C68)</f>
         <v/>
       </c>
-      <c r="D69" s="16">
+      <c r="D69" s="13">
         <f>SUM(D66:D68)</f>
         <v/>
       </c>
-      <c r="E69" s="16">
+      <c r="E69" s="13">
         <f>SUM(E66:E68)</f>
         <v/>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="13">
         <f>SUM(F66:F68)</f>
         <v/>
       </c>
-      <c r="G69" s="16">
+      <c r="G69" s="13">
         <f>SUM(G66:G68)</f>
         <v/>
       </c>
-      <c r="H69" s="16">
+      <c r="H69" s="13">
         <f>SUM(H66:H68)</f>
         <v/>
       </c>
-      <c r="I69" s="16">
+      <c r="I69" s="13">
         <f>SUM(I66:I68)</f>
         <v/>
       </c>
-      <c r="J69" s="16">
+      <c r="J69" s="13">
         <f>SUM(J66:J68)</f>
         <v/>
       </c>
-      <c r="K69" s="16">
+      <c r="K69" s="13">
         <f>SUM(K66:K68)</f>
         <v/>
       </c>
-      <c r="L69" s="16">
+      <c r="L69" s="13">
         <f>SUM(L66:L68)</f>
         <v/>
       </c>
@@ -2328,17 +2044,6 @@
           <t>6. DEPRECIACIONES Y AMORTIZACIONES</t>
         </is>
       </c>
-      <c r="B71" s="27" t="n"/>
-      <c r="C71" s="27" t="n"/>
-      <c r="D71" s="27" t="n"/>
-      <c r="E71" s="27" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="27" t="n"/>
-      <c r="J71" s="27" t="n"/>
-      <c r="K71" s="27" t="n"/>
-      <c r="L71" s="28" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2346,405 +2051,405 @@
           <t>Activo</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Tanques de almacenamiento (10 años)</t>
         </is>
       </c>
-      <c r="B73" s="12">
+      <c r="B73" s="9">
         <f>B28</f>
         <v/>
       </c>
-      <c r="C73" s="12">
+      <c r="C73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="E73" s="12">
+      <c r="E73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="H73" s="12">
+      <c r="H73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="I73" s="12">
+      <c r="I73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="J73" s="12">
+      <c r="J73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="K73" s="12">
+      <c r="K73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
-      <c r="L73" s="12">
+      <c r="L73" s="9">
         <f>$B73/E28</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Pasteurizador HTST (10 años)</t>
         </is>
       </c>
-      <c r="B74" s="12">
+      <c r="B74" s="9">
         <f>B29</f>
         <v/>
       </c>
-      <c r="C74" s="12">
+      <c r="C74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="E74" s="12">
+      <c r="E74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="G74" s="12">
+      <c r="G74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="I74" s="12">
+      <c r="I74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="J74" s="12">
+      <c r="J74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="K74" s="12">
+      <c r="K74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
-      <c r="L74" s="12">
+      <c r="L74" s="9">
         <f>$B74/E29</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Envasadora automática (10 años)</t>
         </is>
       </c>
-      <c r="B75" s="12">
+      <c r="B75" s="9">
         <f>B30</f>
         <v/>
       </c>
-      <c r="C75" s="12">
+      <c r="C75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="E75" s="12">
+      <c r="E75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="I75" s="12">
+      <c r="I75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="J75" s="12">
+      <c r="J75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="K75" s="12">
+      <c r="K75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
-      <c r="L75" s="12">
+      <c r="L75" s="9">
         <f>$B75/E30</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Sistema de enfriamiento (10 años)</t>
         </is>
       </c>
-      <c r="B76" s="12">
+      <c r="B76" s="9">
         <f>B31</f>
         <v/>
       </c>
-      <c r="C76" s="12">
+      <c r="C76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="E76" s="12">
+      <c r="E76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="I76" s="12">
+      <c r="I76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="J76" s="12">
+      <c r="J76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="K76" s="12">
+      <c r="K76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
-      <c r="L76" s="12">
+      <c r="L76" s="9">
         <f>$B76/E31</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Camión de distribución (5 años)</t>
         </is>
       </c>
-      <c r="B77" s="12">
+      <c r="B77" s="9">
         <f>B32</f>
         <v/>
       </c>
-      <c r="C77" s="12">
+      <c r="C77" s="9">
         <f>$B77/E32</f>
         <v/>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="9">
         <f>$B77/E32</f>
         <v/>
       </c>
-      <c r="E77" s="12">
+      <c r="E77" s="9">
         <f>$B77/E32</f>
         <v/>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="9">
         <f>$B77/E32</f>
         <v/>
       </c>
-      <c r="G77" s="12">
+      <c r="G77" s="9">
         <f>$B77/E32</f>
         <v/>
       </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="12" t="n">
+      <c r="H77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Amortización de diferidos (5 años)</t>
         </is>
       </c>
-      <c r="B78" s="12">
+      <c r="B78" s="9">
         <f>B33</f>
         <v/>
       </c>
-      <c r="C78" s="12">
+      <c r="C78" s="9">
         <f>$B78/E33</f>
         <v/>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="9">
         <f>$B78/E33</f>
         <v/>
       </c>
-      <c r="E78" s="12">
+      <c r="E78" s="9">
         <f>$B78/E33</f>
         <v/>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="9">
         <f>$B78/E33</f>
         <v/>
       </c>
-      <c r="G78" s="12">
+      <c r="G78" s="9">
         <f>$B78/E33</f>
         <v/>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="12" t="n">
+      <c r="H78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEPRECIACIÓN Y AMORTIZACIÓN</t>
         </is>
       </c>
-      <c r="B79" s="16">
+      <c r="B79" s="13">
         <f>SUM(B73:B78)</f>
         <v/>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="13">
         <f>SUM(C73:C78)</f>
         <v/>
       </c>
-      <c r="D79" s="16">
+      <c r="D79" s="13">
         <f>SUM(D73:D78)</f>
         <v/>
       </c>
-      <c r="E79" s="16">
+      <c r="E79" s="13">
         <f>SUM(E73:E78)</f>
         <v/>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="13">
         <f>SUM(F73:F78)</f>
         <v/>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="13">
         <f>SUM(G73:G78)</f>
         <v/>
       </c>
-      <c r="H79" s="16">
+      <c r="H79" s="13">
         <f>SUM(H73:H78)</f>
         <v/>
       </c>
-      <c r="I79" s="16">
+      <c r="I79" s="13">
         <f>SUM(I73:I78)</f>
         <v/>
       </c>
-      <c r="J79" s="16">
+      <c r="J79" s="13">
         <f>SUM(J73:J78)</f>
         <v/>
       </c>
-      <c r="K79" s="16">
+      <c r="K79" s="13">
         <f>SUM(K73:K78)</f>
         <v/>
       </c>
-      <c r="L79" s="16">
+      <c r="L79" s="13">
         <f>SUM(L73:L78)</f>
         <v/>
       </c>
@@ -2755,17 +2460,6 @@
           <t>7. VALOR DE DESECHO Y CAPITAL DE TRABAJO</t>
         </is>
       </c>
-      <c r="B81" s="27" t="n"/>
-      <c r="C81" s="27" t="n"/>
-      <c r="D81" s="27" t="n"/>
-      <c r="E81" s="27" t="n"/>
-      <c r="F81" s="27" t="n"/>
-      <c r="G81" s="27" t="n"/>
-      <c r="H81" s="27" t="n"/>
-      <c r="I81" s="27" t="n"/>
-      <c r="J81" s="27" t="n"/>
-      <c r="K81" s="27" t="n"/>
-      <c r="L81" s="28" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2773,241 +2467,241 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Valor de desecho de activos (Año 10)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="12" t="n">
+      <c r="B83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Capital de trabajo requerido</t>
         </is>
       </c>
-      <c r="B84" s="12">
+      <c r="B84" s="9">
         <f>(C49+C69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="C84" s="12">
+      <c r="C84" s="9">
         <f>(C49+C69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="9">
         <f>(D49+D69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="E84" s="12">
+      <c r="E84" s="9">
         <f>(E49+E69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="9">
         <f>(F49+F69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="G84" s="12">
+      <c r="G84" s="9">
         <f>(G49+G69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="9">
         <f>(H49+H69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="I84" s="12">
+      <c r="I84" s="9">
         <f>(I49+I69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="J84" s="12">
+      <c r="J84" s="9">
         <f>(J49+J69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="K84" s="12">
+      <c r="K84" s="9">
         <f>(K49+K69)*$B$24/12</f>
         <v/>
       </c>
-      <c r="L84" s="12">
+      <c r="L84" s="9">
         <f>(L49+L69)*$B$24/12</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Inversión en capital de trabajo (incremento anual)</t>
         </is>
       </c>
-      <c r="B85" s="12">
+      <c r="B85" s="9">
         <f>B84</f>
         <v/>
       </c>
-      <c r="C85" s="12">
+      <c r="C85" s="9">
         <f>C84-B84</f>
         <v/>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="9">
         <f>D84-C84</f>
         <v/>
       </c>
-      <c r="E85" s="12">
+      <c r="E85" s="9">
         <f>E84-D84</f>
         <v/>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="9">
         <f>F84-E84</f>
         <v/>
       </c>
-      <c r="G85" s="12">
+      <c r="G85" s="9">
         <f>G84-F84</f>
         <v/>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="9">
         <f>H84-G84</f>
         <v/>
       </c>
-      <c r="I85" s="12">
+      <c r="I85" s="9">
         <f>I84-H84</f>
         <v/>
       </c>
-      <c r="J85" s="12">
+      <c r="J85" s="9">
         <f>J84-I84</f>
         <v/>
       </c>
-      <c r="K85" s="12">
+      <c r="K85" s="9">
         <f>K84-J84</f>
         <v/>
       </c>
-      <c r="L85" s="12">
+      <c r="L85" s="9">
         <f>L84-K84</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Recuperación capital de trabajo (Año 10)</t>
         </is>
       </c>
-      <c r="B86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="12">
+      <c r="B86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="9">
         <f>L84</f>
         <v/>
       </c>
@@ -3018,17 +2712,6 @@
           <t>8. TABLA DE AMORTIZACIÓN DEL PRÉSTAMO</t>
         </is>
       </c>
-      <c r="B88" s="27" t="n"/>
-      <c r="C88" s="27" t="n"/>
-      <c r="D88" s="27" t="n"/>
-      <c r="E88" s="27" t="n"/>
-      <c r="F88" s="27" t="n"/>
-      <c r="G88" s="27" t="n"/>
-      <c r="H88" s="27" t="n"/>
-      <c r="I88" s="27" t="n"/>
-      <c r="J88" s="27" t="n"/>
-      <c r="K88" s="27" t="n"/>
-      <c r="L88" s="28" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3036,308 +2719,308 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="K89" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="L89" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Saldo inicial</t>
         </is>
       </c>
-      <c r="B90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="12">
+      <c r="B90" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="9">
         <f>D35</f>
         <v/>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="9">
         <f>C94</f>
         <v/>
       </c>
-      <c r="E90" s="12">
+      <c r="E90" s="9">
         <f>D94</f>
         <v/>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="9">
         <f>E94</f>
         <v/>
       </c>
-      <c r="G90" s="12">
+      <c r="G90" s="9">
         <f>F94</f>
         <v/>
       </c>
-      <c r="H90" s="12">
+      <c r="H90" s="9">
         <f>G94</f>
         <v/>
       </c>
-      <c r="I90" s="12">
+      <c r="I90" s="9">
         <f>H94</f>
         <v/>
       </c>
-      <c r="J90" s="12">
+      <c r="J90" s="9">
         <f>I94</f>
         <v/>
       </c>
-      <c r="K90" s="12">
+      <c r="K90" s="9">
         <f>J94</f>
         <v/>
       </c>
-      <c r="L90" s="12">
+      <c r="L90" s="9">
         <f>K94</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Abono a capital</t>
         </is>
       </c>
-      <c r="B91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="12">
+      <c r="B91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="9">
         <f>MIN(C93-C92,C90)</f>
         <v/>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="9">
         <f>MIN(D93-D92,D90)</f>
         <v/>
       </c>
-      <c r="E91" s="12">
+      <c r="E91" s="9">
         <f>MIN(E93-E92,E90)</f>
         <v/>
       </c>
-      <c r="F91" s="12">
+      <c r="F91" s="9">
         <f>MIN(F93-F92,F90)</f>
         <v/>
       </c>
-      <c r="G91" s="12">
+      <c r="G91" s="9">
         <f>MIN(G93-G92,G90)</f>
         <v/>
       </c>
-      <c r="H91" s="12">
+      <c r="H91" s="9">
         <f>MIN(H93-H92,H90)</f>
         <v/>
       </c>
-      <c r="I91" s="12">
+      <c r="I91" s="9">
         <f>MIN(I93-I92,I90)</f>
         <v/>
       </c>
-      <c r="J91" s="12">
+      <c r="J91" s="9">
         <f>MIN(J93-J92,J90)</f>
         <v/>
       </c>
-      <c r="K91" s="12">
+      <c r="K91" s="9">
         <f>MIN(K93-K92,K90)</f>
         <v/>
       </c>
-      <c r="L91" s="12">
+      <c r="L91" s="9">
         <f>MIN(L93-L92,L90)</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Intereses</t>
         </is>
       </c>
-      <c r="B92" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="12">
+      <c r="B92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="9">
         <f>C90*$B$9</f>
         <v/>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="9">
         <f>D90*$B$9</f>
         <v/>
       </c>
-      <c r="E92" s="12">
+      <c r="E92" s="9">
         <f>E90*$B$9</f>
         <v/>
       </c>
-      <c r="F92" s="12">
+      <c r="F92" s="9">
         <f>F90*$B$9</f>
         <v/>
       </c>
-      <c r="G92" s="12">
+      <c r="G92" s="9">
         <f>G90*$B$9</f>
         <v/>
       </c>
-      <c r="H92" s="12">
+      <c r="H92" s="9">
         <f>H90*$B$9</f>
         <v/>
       </c>
-      <c r="I92" s="12">
+      <c r="I92" s="9">
         <f>I90*$B$9</f>
         <v/>
       </c>
-      <c r="J92" s="12">
+      <c r="J92" s="9">
         <f>J90*$B$9</f>
         <v/>
       </c>
-      <c r="K92" s="12">
+      <c r="K92" s="9">
         <f>K90*$B$9</f>
         <v/>
       </c>
-      <c r="L92" s="12">
+      <c r="L92" s="9">
         <f>L90*$B$9</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Cuota total</t>
         </is>
       </c>
-      <c r="B93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="12">
+      <c r="B93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="9">
         <f>IF(C90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="9">
         <f>IF(D90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="E93" s="12">
+      <c r="E93" s="9">
         <f>IF(E90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="F93" s="12">
+      <c r="F93" s="9">
         <f>IF(F90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="G93" s="12">
+      <c r="G93" s="9">
         <f>IF(G90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="H93" s="12">
+      <c r="H93" s="9">
         <f>IF(H90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="I93" s="12">
+      <c r="I93" s="9">
         <f>IF(I90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="J93" s="12">
+      <c r="J93" s="9">
         <f>IF(J90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="K93" s="12">
+      <c r="K93" s="9">
         <f>IF(K90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
-      <c r="L93" s="12">
+      <c r="L93" s="9">
         <f>IF(L90&gt;0,D35*$B$9/(1-(1+$B$9)^-5),0)</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Saldo final</t>
         </is>
       </c>
-      <c r="B94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="12">
+      <c r="B94" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="9">
         <f>C90-C91</f>
         <v/>
       </c>
-      <c r="D94" s="12">
+      <c r="D94" s="9">
         <f>D90-D91</f>
         <v/>
       </c>
-      <c r="E94" s="12">
+      <c r="E94" s="9">
         <f>E90-E91</f>
         <v/>
       </c>
-      <c r="F94" s="12">
+      <c r="F94" s="9">
         <f>F90-F91</f>
         <v/>
       </c>
-      <c r="G94" s="12">
+      <c r="G94" s="9">
         <f>G90-G91</f>
         <v/>
       </c>
-      <c r="H94" s="12">
+      <c r="H94" s="9">
         <f>H90-H91</f>
         <v/>
       </c>
-      <c r="I94" s="12">
+      <c r="I94" s="9">
         <f>I90-I91</f>
         <v/>
       </c>
-      <c r="J94" s="12">
+      <c r="J94" s="9">
         <f>J90-J91</f>
         <v/>
       </c>
-      <c r="K94" s="12">
+      <c r="K94" s="9">
         <f>K90-K91</f>
         <v/>
       </c>
-      <c r="L94" s="12">
+      <c r="L94" s="9">
         <f>L90-L91</f>
         <v/>
       </c>
@@ -3345,20 +3028,9 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>9. FLUJO DE CAJA DEL PROYECTO (SIN FINANCIAMIENTO)</t>
-        </is>
-      </c>
-      <c r="B96" s="27" t="n"/>
-      <c r="C96" s="27" t="n"/>
-      <c r="D96" s="27" t="n"/>
-      <c r="E96" s="27" t="n"/>
-      <c r="F96" s="27" t="n"/>
-      <c r="G96" s="27" t="n"/>
-      <c r="H96" s="27" t="n"/>
-      <c r="I96" s="27" t="n"/>
-      <c r="J96" s="27" t="n"/>
-      <c r="K96" s="27" t="n"/>
-      <c r="L96" s="28" t="n"/>
+          <t>9. IMPUESTO MUNICIPAL DE COMAYAGUA (Industria, Comercio y Servicios)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3366,2382 +3038,2555 @@
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L97" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Ingresos anuales (base imponible)</t>
+        </is>
+      </c>
+      <c r="B98" s="9">
+        <f>B42</f>
+        <v/>
+      </c>
+      <c r="C98" s="9">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D98" s="9">
+        <f>D42</f>
+        <v/>
+      </c>
+      <c r="E98" s="9">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="F98" s="9">
+        <f>F42</f>
+        <v/>
+      </c>
+      <c r="G98" s="9">
+        <f>G42</f>
+        <v/>
+      </c>
+      <c r="H98" s="9">
+        <f>H42</f>
+        <v/>
+      </c>
+      <c r="I98" s="9">
+        <f>I42</f>
+        <v/>
+      </c>
+      <c r="J98" s="9">
+        <f>J42</f>
+        <v/>
+      </c>
+      <c r="K98" s="9">
+        <f>K42</f>
+        <v/>
+      </c>
+      <c r="L98" s="9">
+        <f>L42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Tramo 1: hasta 500,000 (0.30 por millar)</t>
+        </is>
+      </c>
+      <c r="B99" s="9">
+        <f>0.30/1000*MIN(B98,500000)</f>
+        <v/>
+      </c>
+      <c r="C99" s="9">
+        <f>0.30/1000*MIN(C98,500000)</f>
+        <v/>
+      </c>
+      <c r="D99" s="9">
+        <f>0.30/1000*MIN(D98,500000)</f>
+        <v/>
+      </c>
+      <c r="E99" s="9">
+        <f>0.30/1000*MIN(E98,500000)</f>
+        <v/>
+      </c>
+      <c r="F99" s="9">
+        <f>0.30/1000*MIN(F98,500000)</f>
+        <v/>
+      </c>
+      <c r="G99" s="9">
+        <f>0.30/1000*MIN(G98,500000)</f>
+        <v/>
+      </c>
+      <c r="H99" s="9">
+        <f>0.30/1000*MIN(H98,500000)</f>
+        <v/>
+      </c>
+      <c r="I99" s="9">
+        <f>0.30/1000*MIN(I98,500000)</f>
+        <v/>
+      </c>
+      <c r="J99" s="9">
+        <f>0.30/1000*MIN(J98,500000)</f>
+        <v/>
+      </c>
+      <c r="K99" s="9">
+        <f>0.30/1000*MIN(K98,500000)</f>
+        <v/>
+      </c>
+      <c r="L99" s="9">
+        <f>0.30/1000*MIN(L98,500000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Tramo 2: 500,001 a 10,000,000 (0.40 por millar)</t>
+        </is>
+      </c>
+      <c r="B100" s="9">
+        <f>0.40/1000*MAX(0,MIN(B98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="C100" s="9">
+        <f>0.40/1000*MAX(0,MIN(C98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="D100" s="9">
+        <f>0.40/1000*MAX(0,MIN(D98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="E100" s="9">
+        <f>0.40/1000*MAX(0,MIN(E98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="F100" s="9">
+        <f>0.40/1000*MAX(0,MIN(F98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="G100" s="9">
+        <f>0.40/1000*MAX(0,MIN(G98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="H100" s="9">
+        <f>0.40/1000*MAX(0,MIN(H98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="I100" s="9">
+        <f>0.40/1000*MAX(0,MIN(I98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="J100" s="9">
+        <f>0.40/1000*MAX(0,MIN(J98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="K100" s="9">
+        <f>0.40/1000*MAX(0,MIN(K98,10000000)-500000)</f>
+        <v/>
+      </c>
+      <c r="L100" s="9">
+        <f>0.40/1000*MAX(0,MIN(L98,10000000)-500000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Tramo 3: 10,000,001 a 20,000,000 (0.30 por millar)</t>
+        </is>
+      </c>
+      <c r="B101" s="9">
+        <f>0.30/1000*MAX(0,MIN(B98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="C101" s="9">
+        <f>0.30/1000*MAX(0,MIN(C98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="D101" s="9">
+        <f>0.30/1000*MAX(0,MIN(D98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="E101" s="9">
+        <f>0.30/1000*MAX(0,MIN(E98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="F101" s="9">
+        <f>0.30/1000*MAX(0,MIN(F98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="G101" s="9">
+        <f>0.30/1000*MAX(0,MIN(G98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="H101" s="9">
+        <f>0.30/1000*MAX(0,MIN(H98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="I101" s="9">
+        <f>0.30/1000*MAX(0,MIN(I98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="J101" s="9">
+        <f>0.30/1000*MAX(0,MIN(J98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="K101" s="9">
+        <f>0.30/1000*MAX(0,MIN(K98,20000000)-10000000)</f>
+        <v/>
+      </c>
+      <c r="L101" s="9">
+        <f>0.30/1000*MAX(0,MIN(L98,20000000)-10000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Tramo 4: 20,000,001 a 30,000,000 (0.20 por millar)</t>
+        </is>
+      </c>
+      <c r="B102" s="9">
+        <f>0.20/1000*MAX(0,MIN(B98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="C102" s="9">
+        <f>0.20/1000*MAX(0,MIN(C98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="D102" s="9">
+        <f>0.20/1000*MAX(0,MIN(D98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="E102" s="9">
+        <f>0.20/1000*MAX(0,MIN(E98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="F102" s="9">
+        <f>0.20/1000*MAX(0,MIN(F98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="G102" s="9">
+        <f>0.20/1000*MAX(0,MIN(G98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="H102" s="9">
+        <f>0.20/1000*MAX(0,MIN(H98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="I102" s="9">
+        <f>0.20/1000*MAX(0,MIN(I98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="J102" s="9">
+        <f>0.20/1000*MAX(0,MIN(J98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="K102" s="9">
+        <f>0.20/1000*MAX(0,MIN(K98,30000000)-20000000)</f>
+        <v/>
+      </c>
+      <c r="L102" s="9">
+        <f>0.20/1000*MAX(0,MIN(L98,30000000)-20000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Tramo 5: más de 30,000,000 (0.15 por millar)</t>
+        </is>
+      </c>
+      <c r="B103" s="9">
+        <f>0.15/1000*MAX(0,B98-30000000)</f>
+        <v/>
+      </c>
+      <c r="C103" s="9">
+        <f>0.15/1000*MAX(0,C98-30000000)</f>
+        <v/>
+      </c>
+      <c r="D103" s="9">
+        <f>0.15/1000*MAX(0,D98-30000000)</f>
+        <v/>
+      </c>
+      <c r="E103" s="9">
+        <f>0.15/1000*MAX(0,E98-30000000)</f>
+        <v/>
+      </c>
+      <c r="F103" s="9">
+        <f>0.15/1000*MAX(0,F98-30000000)</f>
+        <v/>
+      </c>
+      <c r="G103" s="9">
+        <f>0.15/1000*MAX(0,G98-30000000)</f>
+        <v/>
+      </c>
+      <c r="H103" s="9">
+        <f>0.15/1000*MAX(0,H98-30000000)</f>
+        <v/>
+      </c>
+      <c r="I103" s="9">
+        <f>0.15/1000*MAX(0,I98-30000000)</f>
+        <v/>
+      </c>
+      <c r="J103" s="9">
+        <f>0.15/1000*MAX(0,J98-30000000)</f>
+        <v/>
+      </c>
+      <c r="K103" s="9">
+        <f>0.15/1000*MAX(0,K98-30000000)</f>
+        <v/>
+      </c>
+      <c r="L103" s="9">
+        <f>0.15/1000*MAX(0,L98-30000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>IMPUESTO MUNICIPAL (ICS)</t>
+        </is>
+      </c>
+      <c r="B104" s="13">
+        <f>SUM(B99:B103)</f>
+        <v/>
+      </c>
+      <c r="C104" s="13">
+        <f>SUM(C99:C103)</f>
+        <v/>
+      </c>
+      <c r="D104" s="13">
+        <f>SUM(D99:D103)</f>
+        <v/>
+      </c>
+      <c r="E104" s="13">
+        <f>SUM(E99:E103)</f>
+        <v/>
+      </c>
+      <c r="F104" s="13">
+        <f>SUM(F99:F103)</f>
+        <v/>
+      </c>
+      <c r="G104" s="13">
+        <f>SUM(G99:G103)</f>
+        <v/>
+      </c>
+      <c r="H104" s="13">
+        <f>SUM(H99:H103)</f>
+        <v/>
+      </c>
+      <c r="I104" s="13">
+        <f>SUM(I99:I103)</f>
+        <v/>
+      </c>
+      <c r="J104" s="13">
+        <f>SUM(J99:J103)</f>
+        <v/>
+      </c>
+      <c r="K104" s="13">
+        <f>SUM(K99:K103)</f>
+        <v/>
+      </c>
+      <c r="L104" s="13">
+        <f>SUM(L99:L103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>10. FLUJO DE CAJA DEL PROYECTO (SIN FINANCIAMIENTO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Año 0</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Año 1</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Año 2</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Año 3</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Año 4</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>Año 5</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Año 6</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>Año 7</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>Año 8</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Año 9</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>Año 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>(+) Ingreso por ventas</t>
         </is>
       </c>
-      <c r="B98" s="12">
+      <c r="B108" s="9">
         <f>B42</f>
         <v/>
       </c>
-      <c r="C98" s="12">
+      <c r="C108" s="9">
         <f>C42</f>
         <v/>
       </c>
-      <c r="D98" s="12">
+      <c r="D108" s="9">
         <f>D42</f>
         <v/>
       </c>
-      <c r="E98" s="12">
+      <c r="E108" s="9">
         <f>E42</f>
         <v/>
       </c>
-      <c r="F98" s="12">
+      <c r="F108" s="9">
         <f>F42</f>
         <v/>
       </c>
-      <c r="G98" s="12">
+      <c r="G108" s="9">
         <f>G42</f>
         <v/>
       </c>
-      <c r="H98" s="12">
+      <c r="H108" s="9">
         <f>H42</f>
         <v/>
       </c>
-      <c r="I98" s="12">
+      <c r="I108" s="9">
         <f>I42</f>
         <v/>
       </c>
-      <c r="J98" s="12">
+      <c r="J108" s="9">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K98" s="12">
+      <c r="K108" s="9">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L98" s="12">
+      <c r="L108" s="9">
         <f>L42</f>
         <v/>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>(−) Costos variables</t>
         </is>
       </c>
-      <c r="B99" s="12">
+      <c r="B109" s="9">
         <f>B49</f>
         <v/>
       </c>
-      <c r="C99" s="12">
+      <c r="C109" s="9">
         <f>C49</f>
         <v/>
       </c>
-      <c r="D99" s="12">
+      <c r="D109" s="9">
         <f>D49</f>
         <v/>
       </c>
-      <c r="E99" s="12">
+      <c r="E109" s="9">
         <f>E49</f>
         <v/>
       </c>
-      <c r="F99" s="12">
+      <c r="F109" s="9">
         <f>F49</f>
         <v/>
       </c>
-      <c r="G99" s="12">
+      <c r="G109" s="9">
         <f>G49</f>
         <v/>
       </c>
-      <c r="H99" s="12">
+      <c r="H109" s="9">
         <f>H49</f>
         <v/>
       </c>
-      <c r="I99" s="12">
+      <c r="I109" s="9">
         <f>I49</f>
         <v/>
       </c>
-      <c r="J99" s="12">
+      <c r="J109" s="9">
         <f>J49</f>
         <v/>
       </c>
-      <c r="K99" s="12">
+      <c r="K109" s="9">
         <f>K49</f>
         <v/>
       </c>
-      <c r="L99" s="12">
+      <c r="L109" s="9">
         <f>L49</f>
         <v/>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>(−) Costos fijos</t>
         </is>
       </c>
-      <c r="B100" s="12">
+      <c r="B110" s="9">
         <f>B69</f>
         <v/>
       </c>
-      <c r="C100" s="12">
+      <c r="C110" s="9">
         <f>C69</f>
         <v/>
       </c>
-      <c r="D100" s="12">
+      <c r="D110" s="9">
         <f>D69</f>
         <v/>
       </c>
-      <c r="E100" s="12">
+      <c r="E110" s="9">
         <f>E69</f>
         <v/>
       </c>
-      <c r="F100" s="12">
+      <c r="F110" s="9">
         <f>F69</f>
         <v/>
       </c>
-      <c r="G100" s="12">
+      <c r="G110" s="9">
         <f>G69</f>
         <v/>
       </c>
-      <c r="H100" s="12">
+      <c r="H110" s="9">
         <f>H69</f>
         <v/>
       </c>
-      <c r="I100" s="12">
+      <c r="I110" s="9">
         <f>I69</f>
         <v/>
       </c>
-      <c r="J100" s="12">
+      <c r="J110" s="9">
         <f>J69</f>
         <v/>
       </c>
-      <c r="K100" s="12">
+      <c r="K110" s="9">
         <f>K69</f>
         <v/>
       </c>
-      <c r="L100" s="12">
+      <c r="L110" s="9">
         <f>L69</f>
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>(−) Depreciación y amortización</t>
         </is>
       </c>
-      <c r="B101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="12">
+      <c r="B111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="9">
         <f>C79</f>
         <v/>
       </c>
-      <c r="D101" s="12">
+      <c r="D111" s="9">
         <f>D79</f>
         <v/>
       </c>
-      <c r="E101" s="12">
+      <c r="E111" s="9">
         <f>E79</f>
         <v/>
       </c>
-      <c r="F101" s="12">
+      <c r="F111" s="9">
         <f>F79</f>
         <v/>
       </c>
-      <c r="G101" s="12">
+      <c r="G111" s="9">
         <f>G79</f>
         <v/>
       </c>
-      <c r="H101" s="12">
+      <c r="H111" s="9">
         <f>H79</f>
         <v/>
       </c>
-      <c r="I101" s="12">
+      <c r="I111" s="9">
         <f>I79</f>
         <v/>
       </c>
-      <c r="J101" s="12">
+      <c r="J111" s="9">
         <f>J79</f>
         <v/>
       </c>
-      <c r="K101" s="12">
+      <c r="K111" s="9">
         <f>K79</f>
         <v/>
       </c>
-      <c r="L101" s="12">
+      <c r="L111" s="9">
         <f>L79</f>
         <v/>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="15" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
         <is>
           <t>(=) Utilidad antes de impuestos</t>
         </is>
       </c>
-      <c r="B102" s="16">
-        <f>B98-B99-B100-B101-B170</f>
-        <v/>
-      </c>
-      <c r="C102" s="16">
-        <f>C98-C99-C100-C101-C170</f>
-        <v/>
-      </c>
-      <c r="D102" s="16">
-        <f>D98-D99-D100-D101-D170</f>
-        <v/>
-      </c>
-      <c r="E102" s="16">
-        <f>E98-E99-E100-E101-E170</f>
-        <v/>
-      </c>
-      <c r="F102" s="16">
-        <f>F98-F99-F100-F101-F170</f>
-        <v/>
-      </c>
-      <c r="G102" s="16">
-        <f>G98-G99-G100-G101-G170</f>
-        <v/>
-      </c>
-      <c r="H102" s="16">
-        <f>H98-H99-H100-H101-H170</f>
-        <v/>
-      </c>
-      <c r="I102" s="16">
-        <f>I98-I99-I100-I101-I170</f>
-        <v/>
-      </c>
-      <c r="J102" s="16">
-        <f>J98-J99-J100-J101-J170</f>
-        <v/>
-      </c>
-      <c r="K102" s="16">
-        <f>K98-K99-K100-K101-K170</f>
-        <v/>
-      </c>
-      <c r="L102" s="16">
-        <f>L98-L99-L100-L101-L170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="B112" s="13">
+        <f>B108-B109-B110-B111-B104</f>
+        <v/>
+      </c>
+      <c r="C112" s="13">
+        <f>C108-C109-C110-C111-C104</f>
+        <v/>
+      </c>
+      <c r="D112" s="13">
+        <f>D108-D109-D110-D111-D104</f>
+        <v/>
+      </c>
+      <c r="E112" s="13">
+        <f>E108-E109-E110-E111-E104</f>
+        <v/>
+      </c>
+      <c r="F112" s="13">
+        <f>F108-F109-F110-F111-F104</f>
+        <v/>
+      </c>
+      <c r="G112" s="13">
+        <f>G108-G109-G110-G111-G104</f>
+        <v/>
+      </c>
+      <c r="H112" s="13">
+        <f>H108-H109-H110-H111-H104</f>
+        <v/>
+      </c>
+      <c r="I112" s="13">
+        <f>I108-I109-I110-I111-I104</f>
+        <v/>
+      </c>
+      <c r="J112" s="13">
+        <f>J108-J109-J110-J111-J104</f>
+        <v/>
+      </c>
+      <c r="K112" s="13">
+        <f>K108-K109-K110-K111-K104</f>
+        <v/>
+      </c>
+      <c r="L112" s="13">
+        <f>L108-L109-L110-L111-L104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Pérdidas fiscales acumuladas</t>
         </is>
       </c>
-      <c r="B103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="12">
-        <f>MAX(0,B103-C102)</f>
-        <v/>
-      </c>
-      <c r="D103" s="12">
-        <f>MAX(0,C103-D102)</f>
-        <v/>
-      </c>
-      <c r="E103" s="12">
-        <f>MAX(0,D103-E102)</f>
-        <v/>
-      </c>
-      <c r="F103" s="12">
-        <f>MAX(0,E103-F102)</f>
-        <v/>
-      </c>
-      <c r="G103" s="12">
-        <f>MAX(0,F103-G102)</f>
-        <v/>
-      </c>
-      <c r="H103" s="12">
-        <f>MAX(0,G103-H102)</f>
-        <v/>
-      </c>
-      <c r="I103" s="12">
-        <f>MAX(0,H103-I102)</f>
-        <v/>
-      </c>
-      <c r="J103" s="12">
-        <f>MAX(0,I103-J102)</f>
-        <v/>
-      </c>
-      <c r="K103" s="12">
-        <f>MAX(0,J103-K102)</f>
-        <v/>
-      </c>
-      <c r="L103" s="12">
-        <f>MAX(0,K103-L102)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="B113" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="9">
+        <f>MAX(0,B113-C112)</f>
+        <v/>
+      </c>
+      <c r="D113" s="9">
+        <f>MAX(0,C113-D112)</f>
+        <v/>
+      </c>
+      <c r="E113" s="9">
+        <f>MAX(0,D113-E112)</f>
+        <v/>
+      </c>
+      <c r="F113" s="9">
+        <f>MAX(0,E113-F112)</f>
+        <v/>
+      </c>
+      <c r="G113" s="9">
+        <f>MAX(0,F113-G112)</f>
+        <v/>
+      </c>
+      <c r="H113" s="9">
+        <f>MAX(0,G113-H112)</f>
+        <v/>
+      </c>
+      <c r="I113" s="9">
+        <f>MAX(0,H113-I112)</f>
+        <v/>
+      </c>
+      <c r="J113" s="9">
+        <f>MAX(0,I113-J112)</f>
+        <v/>
+      </c>
+      <c r="K113" s="9">
+        <f>MAX(0,J113-K112)</f>
+        <v/>
+      </c>
+      <c r="L113" s="9">
+        <f>MAX(0,K113-L112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>(−) Impuesto sobre la renta</t>
         </is>
       </c>
-      <c r="B104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="12">
-        <f>$B$6*MAX(0,C102-B103)+$B$7*MAX(0,MAX(0,C102-B103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="D104" s="12">
-        <f>$B$6*MAX(0,D102-C103)+$B$7*MAX(0,MAX(0,D102-C103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="E104" s="12">
-        <f>$B$6*MAX(0,E102-D103)+$B$7*MAX(0,MAX(0,E102-D103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="F104" s="12">
-        <f>$B$6*MAX(0,F102-E103)+$B$7*MAX(0,MAX(0,F102-E103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="G104" s="12">
-        <f>$B$6*MAX(0,G102-F103)+$B$7*MAX(0,MAX(0,G102-F103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="H104" s="12">
-        <f>$B$6*MAX(0,H102-G103)+$B$7*MAX(0,MAX(0,H102-G103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="I104" s="12">
-        <f>$B$6*MAX(0,I102-H103)+$B$7*MAX(0,MAX(0,I102-H103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="J104" s="12">
-        <f>$B$6*MAX(0,J102-I103)+$B$7*MAX(0,MAX(0,J102-I103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="K104" s="12">
-        <f>$B$6*MAX(0,K102-J103)+$B$7*MAX(0,MAX(0,K102-J103)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="L104" s="12">
-        <f>$B$6*MAX(0,L102-K103)+$B$7*MAX(0,MAX(0,L102-K103)-$B$8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
+      <c r="B114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="9">
+        <f>$B$6*MAX(0,C112-B113)+$B$7*MAX(0,MAX(0,C112-B113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="D114" s="9">
+        <f>$B$6*MAX(0,D112-C113)+$B$7*MAX(0,MAX(0,D112-C113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="E114" s="9">
+        <f>$B$6*MAX(0,E112-D113)+$B$7*MAX(0,MAX(0,E112-D113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="F114" s="9">
+        <f>$B$6*MAX(0,F112-E113)+$B$7*MAX(0,MAX(0,F112-E113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="G114" s="9">
+        <f>$B$6*MAX(0,G112-F113)+$B$7*MAX(0,MAX(0,G112-F113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="H114" s="9">
+        <f>$B$6*MAX(0,H112-G113)+$B$7*MAX(0,MAX(0,H112-G113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="I114" s="9">
+        <f>$B$6*MAX(0,I112-H113)+$B$7*MAX(0,MAX(0,I112-H113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="J114" s="9">
+        <f>$B$6*MAX(0,J112-I113)+$B$7*MAX(0,MAX(0,J112-I113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="K114" s="9">
+        <f>$B$6*MAX(0,K112-J113)+$B$7*MAX(0,MAX(0,K112-J113)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="L114" s="9">
+        <f>$B$6*MAX(0,L112-K113)+$B$7*MAX(0,MAX(0,L112-K113)-$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>(=) Utilidad después de impuestos</t>
         </is>
       </c>
-      <c r="B105" s="16">
-        <f>B102-B104</f>
-        <v/>
-      </c>
-      <c r="C105" s="16">
-        <f>C102-C104</f>
-        <v/>
-      </c>
-      <c r="D105" s="16">
-        <f>D102-D104</f>
-        <v/>
-      </c>
-      <c r="E105" s="16">
-        <f>E102-E104</f>
-        <v/>
-      </c>
-      <c r="F105" s="16">
-        <f>F102-F104</f>
-        <v/>
-      </c>
-      <c r="G105" s="16">
-        <f>G102-G104</f>
-        <v/>
-      </c>
-      <c r="H105" s="16">
-        <f>H102-H104</f>
-        <v/>
-      </c>
-      <c r="I105" s="16">
-        <f>I102-I104</f>
-        <v/>
-      </c>
-      <c r="J105" s="16">
-        <f>J102-J104</f>
-        <v/>
-      </c>
-      <c r="K105" s="16">
-        <f>K102-K104</f>
-        <v/>
-      </c>
-      <c r="L105" s="16">
-        <f>L102-L104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="B115" s="9">
+        <f>B112-B114</f>
+        <v/>
+      </c>
+      <c r="C115" s="9">
+        <f>C112-C114</f>
+        <v/>
+      </c>
+      <c r="D115" s="9">
+        <f>D112-D114</f>
+        <v/>
+      </c>
+      <c r="E115" s="9">
+        <f>E112-E114</f>
+        <v/>
+      </c>
+      <c r="F115" s="9">
+        <f>F112-F114</f>
+        <v/>
+      </c>
+      <c r="G115" s="9">
+        <f>G112-G114</f>
+        <v/>
+      </c>
+      <c r="H115" s="9">
+        <f>H112-H114</f>
+        <v/>
+      </c>
+      <c r="I115" s="9">
+        <f>I112-I114</f>
+        <v/>
+      </c>
+      <c r="J115" s="9">
+        <f>J112-J114</f>
+        <v/>
+      </c>
+      <c r="K115" s="9">
+        <f>K112-K114</f>
+        <v/>
+      </c>
+      <c r="L115" s="9">
+        <f>L112-L114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>(+) Depreciación y amortización</t>
         </is>
       </c>
-      <c r="B106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="12">
+      <c r="B116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="9">
         <f>C79</f>
         <v/>
       </c>
-      <c r="D106" s="12">
+      <c r="D116" s="9">
         <f>D79</f>
         <v/>
       </c>
-      <c r="E106" s="12">
+      <c r="E116" s="9">
         <f>E79</f>
         <v/>
       </c>
-      <c r="F106" s="12">
+      <c r="F116" s="9">
         <f>F79</f>
         <v/>
       </c>
-      <c r="G106" s="12">
+      <c r="G116" s="9">
         <f>G79</f>
         <v/>
       </c>
-      <c r="H106" s="12">
+      <c r="H116" s="9">
         <f>H79</f>
         <v/>
       </c>
-      <c r="I106" s="12">
+      <c r="I116" s="9">
         <f>I79</f>
         <v/>
       </c>
-      <c r="J106" s="12">
+      <c r="J116" s="9">
         <f>J79</f>
         <v/>
       </c>
-      <c r="K106" s="12">
+      <c r="K116" s="9">
         <f>K79</f>
         <v/>
       </c>
-      <c r="L106" s="12">
+      <c r="L116" s="9">
         <f>L79</f>
         <v/>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>(+) Valor de desecho</t>
         </is>
       </c>
-      <c r="B107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="12">
+      <c r="B117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="9">
         <f>L83</f>
         <v/>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>(+) Recuperación capital de trabajo</t>
         </is>
       </c>
-      <c r="B108" s="12">
+      <c r="B118" s="9">
         <f>B86</f>
         <v/>
       </c>
-      <c r="C108" s="12">
+      <c r="C118" s="9">
         <f>C86</f>
         <v/>
       </c>
-      <c r="D108" s="12">
+      <c r="D118" s="9">
         <f>D86</f>
         <v/>
       </c>
-      <c r="E108" s="12">
+      <c r="E118" s="9">
         <f>E86</f>
         <v/>
       </c>
-      <c r="F108" s="12">
+      <c r="F118" s="9">
         <f>F86</f>
         <v/>
       </c>
-      <c r="G108" s="12">
+      <c r="G118" s="9">
         <f>G86</f>
         <v/>
       </c>
-      <c r="H108" s="12">
+      <c r="H118" s="9">
         <f>H86</f>
         <v/>
       </c>
-      <c r="I108" s="12">
+      <c r="I118" s="9">
         <f>I86</f>
         <v/>
       </c>
-      <c r="J108" s="12">
+      <c r="J118" s="9">
         <f>J86</f>
         <v/>
       </c>
-      <c r="K108" s="12">
+      <c r="K118" s="9">
         <f>K86</f>
         <v/>
       </c>
-      <c r="L108" s="12">
+      <c r="L118" s="9">
         <f>L86</f>
         <v/>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>(−) Inversión en activos fijos</t>
         </is>
       </c>
-      <c r="B109" s="12">
+      <c r="B119" s="9">
         <f>SUM(B28:B33)</f>
         <v/>
       </c>
-      <c r="C109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="C119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>(−) Inversión en capital de trabajo</t>
         </is>
       </c>
-      <c r="B110" s="12">
+      <c r="B120" s="9">
         <f>B85</f>
         <v/>
       </c>
-      <c r="C110" s="12">
+      <c r="C120" s="9">
         <f>C85</f>
         <v/>
       </c>
-      <c r="D110" s="12">
+      <c r="D120" s="9">
         <f>D85</f>
         <v/>
       </c>
-      <c r="E110" s="12">
+      <c r="E120" s="9">
         <f>E85</f>
         <v/>
       </c>
-      <c r="F110" s="12">
+      <c r="F120" s="9">
         <f>F85</f>
         <v/>
       </c>
-      <c r="G110" s="12">
+      <c r="G120" s="9">
         <f>G85</f>
         <v/>
       </c>
-      <c r="H110" s="12">
+      <c r="H120" s="9">
         <f>H85</f>
         <v/>
       </c>
-      <c r="I110" s="12">
+      <c r="I120" s="9">
         <f>I85</f>
         <v/>
       </c>
-      <c r="J110" s="12">
+      <c r="J120" s="9">
         <f>J85</f>
         <v/>
       </c>
-      <c r="K110" s="12">
+      <c r="K120" s="9">
         <f>K85</f>
         <v/>
       </c>
-      <c r="L110" s="12">
+      <c r="L120" s="9">
         <f>L85</f>
         <v/>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
         <is>
           <t>(=) FLUJO DE CAJA NETO</t>
         </is>
       </c>
-      <c r="B111" s="16">
-        <f>B105+B106+B107+B108-B109-B110</f>
-        <v/>
-      </c>
-      <c r="C111" s="16">
-        <f>C105+C106+C107+C108-C109-C110</f>
-        <v/>
-      </c>
-      <c r="D111" s="16">
-        <f>D105+D106+D107+D108-D109-D110</f>
-        <v/>
-      </c>
-      <c r="E111" s="16">
-        <f>E105+E106+E107+E108-E109-E110</f>
-        <v/>
-      </c>
-      <c r="F111" s="16">
-        <f>F105+F106+F107+F108-F109-F110</f>
-        <v/>
-      </c>
-      <c r="G111" s="16">
-        <f>G105+G106+G107+G108-G109-G110</f>
-        <v/>
-      </c>
-      <c r="H111" s="16">
-        <f>H105+H106+H107+H108-H109-H110</f>
-        <v/>
-      </c>
-      <c r="I111" s="16">
-        <f>I105+I106+I107+I108-I109-I110</f>
-        <v/>
-      </c>
-      <c r="J111" s="16">
-        <f>J105+J106+J107+J108-J109-J110</f>
-        <v/>
-      </c>
-      <c r="K111" s="16">
-        <f>K105+K106+K107+K108-K109-K110</f>
-        <v/>
-      </c>
-      <c r="L111" s="16">
-        <f>L105+L106+L107+L108-L109-L110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="21" t="inlineStr">
+      <c r="B121" s="13">
+        <f>B115+B116+B117+B118-B119-B120</f>
+        <v/>
+      </c>
+      <c r="C121" s="13">
+        <f>C115+C116+C117+C118-C119-C120</f>
+        <v/>
+      </c>
+      <c r="D121" s="13">
+        <f>D115+D116+D117+D118-D119-D120</f>
+        <v/>
+      </c>
+      <c r="E121" s="13">
+        <f>E115+E116+E117+E118-E119-E120</f>
+        <v/>
+      </c>
+      <c r="F121" s="13">
+        <f>F115+F116+F117+F118-F119-F120</f>
+        <v/>
+      </c>
+      <c r="G121" s="13">
+        <f>G115+G116+G117+G118-G119-G120</f>
+        <v/>
+      </c>
+      <c r="H121" s="13">
+        <f>H115+H116+H117+H118-H119-H120</f>
+        <v/>
+      </c>
+      <c r="I121" s="13">
+        <f>I115+I116+I117+I118-I119-I120</f>
+        <v/>
+      </c>
+      <c r="J121" s="13">
+        <f>J115+J116+J117+J118-J119-J120</f>
+        <v/>
+      </c>
+      <c r="K121" s="13">
+        <f>K115+K116+K117+K118-K119-K120</f>
+        <v/>
+      </c>
+      <c r="L121" s="13">
+        <f>L115+L116+L117+L118-L119-L120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Flujo de caja acumulado</t>
         </is>
       </c>
-      <c r="B112" s="22">
-        <f>B111</f>
-        <v/>
-      </c>
-      <c r="C112" s="22">
-        <f>B112+C111</f>
-        <v/>
-      </c>
-      <c r="D112" s="22">
-        <f>C112+D111</f>
-        <v/>
-      </c>
-      <c r="E112" s="22">
-        <f>D112+E111</f>
-        <v/>
-      </c>
-      <c r="F112" s="22">
-        <f>E112+F111</f>
-        <v/>
-      </c>
-      <c r="G112" s="22">
-        <f>F112+G111</f>
-        <v/>
-      </c>
-      <c r="H112" s="22">
-        <f>G112+H111</f>
-        <v/>
-      </c>
-      <c r="I112" s="22">
-        <f>H112+I111</f>
-        <v/>
-      </c>
-      <c r="J112" s="22">
-        <f>I112+J111</f>
-        <v/>
-      </c>
-      <c r="K112" s="22">
-        <f>J112+K111</f>
-        <v/>
-      </c>
-      <c r="L112" s="22">
-        <f>K112+L111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>10. FLUJO DE CAJA DEL PROYECTO (CON FINANCIAMIENTO)</t>
-        </is>
-      </c>
-      <c r="B114" s="27" t="n"/>
-      <c r="C114" s="27" t="n"/>
-      <c r="D114" s="27" t="n"/>
-      <c r="E114" s="27" t="n"/>
-      <c r="F114" s="27" t="n"/>
-      <c r="G114" s="27" t="n"/>
-      <c r="H114" s="27" t="n"/>
-      <c r="I114" s="27" t="n"/>
-      <c r="J114" s="27" t="n"/>
-      <c r="K114" s="27" t="n"/>
-      <c r="L114" s="28" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="B122" s="9">
+        <f>B121</f>
+        <v/>
+      </c>
+      <c r="C122" s="9">
+        <f>B122+C121</f>
+        <v/>
+      </c>
+      <c r="D122" s="9">
+        <f>C122+D121</f>
+        <v/>
+      </c>
+      <c r="E122" s="9">
+        <f>D122+E121</f>
+        <v/>
+      </c>
+      <c r="F122" s="9">
+        <f>E122+F121</f>
+        <v/>
+      </c>
+      <c r="G122" s="9">
+        <f>F122+G121</f>
+        <v/>
+      </c>
+      <c r="H122" s="9">
+        <f>G122+H121</f>
+        <v/>
+      </c>
+      <c r="I122" s="9">
+        <f>H122+I121</f>
+        <v/>
+      </c>
+      <c r="J122" s="9">
+        <f>I122+J121</f>
+        <v/>
+      </c>
+      <c r="K122" s="9">
+        <f>J122+K121</f>
+        <v/>
+      </c>
+      <c r="L122" s="9">
+        <f>K122+L121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>11. FLUJO DE CAJA DEL PROYECTO (CON FINANCIAMIENTO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Año 0</t>
         </is>
       </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="E115" s="5" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>Año 4</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>Año 5</t>
         </is>
       </c>
-      <c r="H115" s="5" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>Año 6</t>
         </is>
       </c>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>Año 7</t>
         </is>
       </c>
-      <c r="J115" s="5" t="inlineStr">
+      <c r="J125" s="4" t="inlineStr">
         <is>
           <t>Año 8</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr">
+      <c r="K125" s="4" t="inlineStr">
         <is>
           <t>Año 9</t>
         </is>
       </c>
-      <c r="L115" s="5" t="inlineStr">
+      <c r="L125" s="4" t="inlineStr">
         <is>
           <t>Año 10</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>(+) Ingreso por ventas</t>
         </is>
       </c>
-      <c r="B116" s="12">
+      <c r="B126" s="9">
         <f>B42</f>
         <v/>
       </c>
-      <c r="C116" s="12">
+      <c r="C126" s="9">
         <f>C42</f>
         <v/>
       </c>
-      <c r="D116" s="12">
+      <c r="D126" s="9">
         <f>D42</f>
         <v/>
       </c>
-      <c r="E116" s="12">
+      <c r="E126" s="9">
         <f>E42</f>
         <v/>
       </c>
-      <c r="F116" s="12">
+      <c r="F126" s="9">
         <f>F42</f>
         <v/>
       </c>
-      <c r="G116" s="12">
+      <c r="G126" s="9">
         <f>G42</f>
         <v/>
       </c>
-      <c r="H116" s="12">
+      <c r="H126" s="9">
         <f>H42</f>
         <v/>
       </c>
-      <c r="I116" s="12">
+      <c r="I126" s="9">
         <f>I42</f>
         <v/>
       </c>
-      <c r="J116" s="12">
+      <c r="J126" s="9">
         <f>J42</f>
         <v/>
       </c>
-      <c r="K116" s="12">
+      <c r="K126" s="9">
         <f>K42</f>
         <v/>
       </c>
-      <c r="L116" s="12">
+      <c r="L126" s="9">
         <f>L42</f>
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>(−) Costos variables</t>
         </is>
       </c>
-      <c r="B117" s="12">
+      <c r="B127" s="9">
         <f>B49</f>
         <v/>
       </c>
-      <c r="C117" s="12">
+      <c r="C127" s="9">
         <f>C49</f>
         <v/>
       </c>
-      <c r="D117" s="12">
+      <c r="D127" s="9">
         <f>D49</f>
         <v/>
       </c>
-      <c r="E117" s="12">
+      <c r="E127" s="9">
         <f>E49</f>
         <v/>
       </c>
-      <c r="F117" s="12">
+      <c r="F127" s="9">
         <f>F49</f>
         <v/>
       </c>
-      <c r="G117" s="12">
+      <c r="G127" s="9">
         <f>G49</f>
         <v/>
       </c>
-      <c r="H117" s="12">
+      <c r="H127" s="9">
         <f>H49</f>
         <v/>
       </c>
-      <c r="I117" s="12">
+      <c r="I127" s="9">
         <f>I49</f>
         <v/>
       </c>
-      <c r="J117" s="12">
+      <c r="J127" s="9">
         <f>J49</f>
         <v/>
       </c>
-      <c r="K117" s="12">
+      <c r="K127" s="9">
         <f>K49</f>
         <v/>
       </c>
-      <c r="L117" s="12">
+      <c r="L127" s="9">
         <f>L49</f>
         <v/>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>(−) Costos fijos</t>
         </is>
       </c>
-      <c r="B118" s="12">
+      <c r="B128" s="9">
         <f>B69</f>
         <v/>
       </c>
-      <c r="C118" s="12">
+      <c r="C128" s="9">
         <f>C69</f>
         <v/>
       </c>
-      <c r="D118" s="12">
+      <c r="D128" s="9">
         <f>D69</f>
         <v/>
       </c>
-      <c r="E118" s="12">
+      <c r="E128" s="9">
         <f>E69</f>
         <v/>
       </c>
-      <c r="F118" s="12">
+      <c r="F128" s="9">
         <f>F69</f>
         <v/>
       </c>
-      <c r="G118" s="12">
+      <c r="G128" s="9">
         <f>G69</f>
         <v/>
       </c>
-      <c r="H118" s="12">
+      <c r="H128" s="9">
         <f>H69</f>
         <v/>
       </c>
-      <c r="I118" s="12">
+      <c r="I128" s="9">
         <f>I69</f>
         <v/>
       </c>
-      <c r="J118" s="12">
+      <c r="J128" s="9">
         <f>J69</f>
         <v/>
       </c>
-      <c r="K118" s="12">
+      <c r="K128" s="9">
         <f>K69</f>
         <v/>
       </c>
-      <c r="L118" s="12">
+      <c r="L128" s="9">
         <f>L69</f>
         <v/>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>(−) Gastos financieros</t>
         </is>
       </c>
-      <c r="B119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" s="12">
+      <c r="B129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="9">
         <f>C92</f>
         <v/>
       </c>
-      <c r="D119" s="12">
+      <c r="D129" s="9">
         <f>D92</f>
         <v/>
       </c>
-      <c r="E119" s="12">
+      <c r="E129" s="9">
         <f>E92</f>
         <v/>
       </c>
-      <c r="F119" s="12">
+      <c r="F129" s="9">
         <f>F92</f>
         <v/>
       </c>
-      <c r="G119" s="12">
+      <c r="G129" s="9">
         <f>G92</f>
         <v/>
       </c>
-      <c r="H119" s="12">
+      <c r="H129" s="9">
         <f>H92</f>
         <v/>
       </c>
-      <c r="I119" s="12">
+      <c r="I129" s="9">
         <f>I92</f>
         <v/>
       </c>
-      <c r="J119" s="12">
+      <c r="J129" s="9">
         <f>J92</f>
         <v/>
       </c>
-      <c r="K119" s="12">
+      <c r="K129" s="9">
         <f>K92</f>
         <v/>
       </c>
-      <c r="L119" s="12">
+      <c r="L129" s="9">
         <f>L92</f>
         <v/>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>(−) Depreciación y amortización</t>
         </is>
       </c>
-      <c r="B120" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="12">
+      <c r="B130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="9">
         <f>C79</f>
         <v/>
       </c>
-      <c r="D120" s="12">
+      <c r="D130" s="9">
         <f>D79</f>
         <v/>
       </c>
-      <c r="E120" s="12">
+      <c r="E130" s="9">
         <f>E79</f>
         <v/>
       </c>
-      <c r="F120" s="12">
+      <c r="F130" s="9">
         <f>F79</f>
         <v/>
       </c>
-      <c r="G120" s="12">
+      <c r="G130" s="9">
         <f>G79</f>
         <v/>
       </c>
-      <c r="H120" s="12">
+      <c r="H130" s="9">
         <f>H79</f>
         <v/>
       </c>
-      <c r="I120" s="12">
+      <c r="I130" s="9">
         <f>I79</f>
         <v/>
       </c>
-      <c r="J120" s="12">
+      <c r="J130" s="9">
         <f>J79</f>
         <v/>
       </c>
-      <c r="K120" s="12">
+      <c r="K130" s="9">
         <f>K79</f>
         <v/>
       </c>
-      <c r="L120" s="12">
+      <c r="L130" s="9">
         <f>L79</f>
         <v/>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="15" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
         <is>
           <t>(=) Utilidad antes de impuestos</t>
         </is>
       </c>
-      <c r="B121" s="16">
-        <f>B116-B117-B118-B119-B120-B170</f>
-        <v/>
-      </c>
-      <c r="C121" s="16">
-        <f>C116-C117-C118-C119-C120-C170</f>
-        <v/>
-      </c>
-      <c r="D121" s="16">
-        <f>D116-D117-D118-D119-D120-D170</f>
-        <v/>
-      </c>
-      <c r="E121" s="16">
-        <f>E116-E117-E118-E119-E120-E170</f>
-        <v/>
-      </c>
-      <c r="F121" s="16">
-        <f>F116-F117-F118-F119-F120-F170</f>
-        <v/>
-      </c>
-      <c r="G121" s="16">
-        <f>G116-G117-G118-G119-G120-G170</f>
-        <v/>
-      </c>
-      <c r="H121" s="16">
-        <f>H116-H117-H118-H119-H120-H170</f>
-        <v/>
-      </c>
-      <c r="I121" s="16">
-        <f>I116-I117-I118-I119-I120-I170</f>
-        <v/>
-      </c>
-      <c r="J121" s="16">
-        <f>J116-J117-J118-J119-J120-J170</f>
-        <v/>
-      </c>
-      <c r="K121" s="16">
-        <f>K116-K117-K118-K119-K120-K170</f>
-        <v/>
-      </c>
-      <c r="L121" s="16">
-        <f>L116-L117-L118-L119-L120-L170</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="B131" s="13">
+        <f>B126-B127-B128-B129-B130-B104</f>
+        <v/>
+      </c>
+      <c r="C131" s="13">
+        <f>C126-C127-C128-C129-C130-C104</f>
+        <v/>
+      </c>
+      <c r="D131" s="13">
+        <f>D126-D127-D128-D129-D130-D104</f>
+        <v/>
+      </c>
+      <c r="E131" s="13">
+        <f>E126-E127-E128-E129-E130-E104</f>
+        <v/>
+      </c>
+      <c r="F131" s="13">
+        <f>F126-F127-F128-F129-F130-F104</f>
+        <v/>
+      </c>
+      <c r="G131" s="13">
+        <f>G126-G127-G128-G129-G130-G104</f>
+        <v/>
+      </c>
+      <c r="H131" s="13">
+        <f>H126-H127-H128-H129-H130-H104</f>
+        <v/>
+      </c>
+      <c r="I131" s="13">
+        <f>I126-I127-I128-I129-I130-I104</f>
+        <v/>
+      </c>
+      <c r="J131" s="13">
+        <f>J126-J127-J128-J129-J130-J104</f>
+        <v/>
+      </c>
+      <c r="K131" s="13">
+        <f>K126-K127-K128-K129-K130-K104</f>
+        <v/>
+      </c>
+      <c r="L131" s="13">
+        <f>L126-L127-L128-L129-L130-L104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Pérdidas fiscales acumuladas</t>
         </is>
       </c>
-      <c r="B122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="12">
-        <f>MAX(0,B122-C121)</f>
-        <v/>
-      </c>
-      <c r="D122" s="12">
-        <f>MAX(0,C122-D121)</f>
-        <v/>
-      </c>
-      <c r="E122" s="12">
-        <f>MAX(0,D122-E121)</f>
-        <v/>
-      </c>
-      <c r="F122" s="12">
-        <f>MAX(0,E122-F121)</f>
-        <v/>
-      </c>
-      <c r="G122" s="12">
-        <f>MAX(0,F122-G121)</f>
-        <v/>
-      </c>
-      <c r="H122" s="12">
-        <f>MAX(0,G122-H121)</f>
-        <v/>
-      </c>
-      <c r="I122" s="12">
-        <f>MAX(0,H122-I121)</f>
-        <v/>
-      </c>
-      <c r="J122" s="12">
-        <f>MAX(0,I122-J121)</f>
-        <v/>
-      </c>
-      <c r="K122" s="12">
-        <f>MAX(0,J122-K121)</f>
-        <v/>
-      </c>
-      <c r="L122" s="12">
-        <f>MAX(0,K122-L121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="B132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="9">
+        <f>MAX(0,B132-C131)</f>
+        <v/>
+      </c>
+      <c r="D132" s="9">
+        <f>MAX(0,C132-D131)</f>
+        <v/>
+      </c>
+      <c r="E132" s="9">
+        <f>MAX(0,D132-E131)</f>
+        <v/>
+      </c>
+      <c r="F132" s="9">
+        <f>MAX(0,E132-F131)</f>
+        <v/>
+      </c>
+      <c r="G132" s="9">
+        <f>MAX(0,F132-G131)</f>
+        <v/>
+      </c>
+      <c r="H132" s="9">
+        <f>MAX(0,G132-H131)</f>
+        <v/>
+      </c>
+      <c r="I132" s="9">
+        <f>MAX(0,H132-I131)</f>
+        <v/>
+      </c>
+      <c r="J132" s="9">
+        <f>MAX(0,I132-J131)</f>
+        <v/>
+      </c>
+      <c r="K132" s="9">
+        <f>MAX(0,J132-K131)</f>
+        <v/>
+      </c>
+      <c r="L132" s="9">
+        <f>MAX(0,K132-L131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>(−) Impuesto sobre la renta</t>
         </is>
       </c>
-      <c r="B123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="12">
-        <f>$B$6*MAX(0,C121-B122)+$B$7*MAX(0,MAX(0,C121-B122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="D123" s="12">
-        <f>$B$6*MAX(0,D121-C122)+$B$7*MAX(0,MAX(0,D121-C122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="E123" s="12">
-        <f>$B$6*MAX(0,E121-D122)+$B$7*MAX(0,MAX(0,E121-D122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="F123" s="12">
-        <f>$B$6*MAX(0,F121-E122)+$B$7*MAX(0,MAX(0,F121-E122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="G123" s="12">
-        <f>$B$6*MAX(0,G121-F122)+$B$7*MAX(0,MAX(0,G121-F122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="H123" s="12">
-        <f>$B$6*MAX(0,H121-G122)+$B$7*MAX(0,MAX(0,H121-G122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="I123" s="12">
-        <f>$B$6*MAX(0,I121-H122)+$B$7*MAX(0,MAX(0,I121-H122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="J123" s="12">
-        <f>$B$6*MAX(0,J121-I122)+$B$7*MAX(0,MAX(0,J121-I122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="K123" s="12">
-        <f>$B$6*MAX(0,K121-J122)+$B$7*MAX(0,MAX(0,K121-J122)-$B$8)</f>
-        <v/>
-      </c>
-      <c r="L123" s="12">
-        <f>$B$6*MAX(0,L121-K122)+$B$7*MAX(0,MAX(0,L121-K122)-$B$8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="inlineStr">
+      <c r="B133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="9">
+        <f>$B$6*MAX(0,C131-B132)+$B$7*MAX(0,MAX(0,C131-B132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="D133" s="9">
+        <f>$B$6*MAX(0,D131-C132)+$B$7*MAX(0,MAX(0,D131-C132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="E133" s="9">
+        <f>$B$6*MAX(0,E131-D132)+$B$7*MAX(0,MAX(0,E131-D132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="F133" s="9">
+        <f>$B$6*MAX(0,F131-E132)+$B$7*MAX(0,MAX(0,F131-E132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="G133" s="9">
+        <f>$B$6*MAX(0,G131-F132)+$B$7*MAX(0,MAX(0,G131-F132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="H133" s="9">
+        <f>$B$6*MAX(0,H131-G132)+$B$7*MAX(0,MAX(0,H131-G132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="I133" s="9">
+        <f>$B$6*MAX(0,I131-H132)+$B$7*MAX(0,MAX(0,I131-H132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="J133" s="9">
+        <f>$B$6*MAX(0,J131-I132)+$B$7*MAX(0,MAX(0,J131-I132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="K133" s="9">
+        <f>$B$6*MAX(0,K131-J132)+$B$7*MAX(0,MAX(0,K131-J132)-$B$8)</f>
+        <v/>
+      </c>
+      <c r="L133" s="9">
+        <f>$B$6*MAX(0,L131-K132)+$B$7*MAX(0,MAX(0,L131-K132)-$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>(=) Utilidad después de impuestos</t>
         </is>
       </c>
-      <c r="B124" s="16">
-        <f>B121-B123</f>
-        <v/>
-      </c>
-      <c r="C124" s="16">
-        <f>C121-C123</f>
-        <v/>
-      </c>
-      <c r="D124" s="16">
-        <f>D121-D123</f>
-        <v/>
-      </c>
-      <c r="E124" s="16">
-        <f>E121-E123</f>
-        <v/>
-      </c>
-      <c r="F124" s="16">
-        <f>F121-F123</f>
-        <v/>
-      </c>
-      <c r="G124" s="16">
-        <f>G121-G123</f>
-        <v/>
-      </c>
-      <c r="H124" s="16">
-        <f>H121-H123</f>
-        <v/>
-      </c>
-      <c r="I124" s="16">
-        <f>I121-I123</f>
-        <v/>
-      </c>
-      <c r="J124" s="16">
-        <f>J121-J123</f>
-        <v/>
-      </c>
-      <c r="K124" s="16">
-        <f>K121-K123</f>
-        <v/>
-      </c>
-      <c r="L124" s="16">
-        <f>L121-L123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="B134" s="9">
+        <f>B131-B133</f>
+        <v/>
+      </c>
+      <c r="C134" s="9">
+        <f>C131-C133</f>
+        <v/>
+      </c>
+      <c r="D134" s="9">
+        <f>D131-D133</f>
+        <v/>
+      </c>
+      <c r="E134" s="9">
+        <f>E131-E133</f>
+        <v/>
+      </c>
+      <c r="F134" s="9">
+        <f>F131-F133</f>
+        <v/>
+      </c>
+      <c r="G134" s="9">
+        <f>G131-G133</f>
+        <v/>
+      </c>
+      <c r="H134" s="9">
+        <f>H131-H133</f>
+        <v/>
+      </c>
+      <c r="I134" s="9">
+        <f>I131-I133</f>
+        <v/>
+      </c>
+      <c r="J134" s="9">
+        <f>J131-J133</f>
+        <v/>
+      </c>
+      <c r="K134" s="9">
+        <f>K131-K133</f>
+        <v/>
+      </c>
+      <c r="L134" s="9">
+        <f>L131-L133</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>(+) Depreciación y amortización</t>
         </is>
       </c>
-      <c r="B125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" s="12">
+      <c r="B135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="9">
         <f>C79</f>
         <v/>
       </c>
-      <c r="D125" s="12">
+      <c r="D135" s="9">
         <f>D79</f>
         <v/>
       </c>
-      <c r="E125" s="12">
+      <c r="E135" s="9">
         <f>E79</f>
         <v/>
       </c>
-      <c r="F125" s="12">
+      <c r="F135" s="9">
         <f>F79</f>
         <v/>
       </c>
-      <c r="G125" s="12">
+      <c r="G135" s="9">
         <f>G79</f>
         <v/>
       </c>
-      <c r="H125" s="12">
+      <c r="H135" s="9">
         <f>H79</f>
         <v/>
       </c>
-      <c r="I125" s="12">
+      <c r="I135" s="9">
         <f>I79</f>
         <v/>
       </c>
-      <c r="J125" s="12">
+      <c r="J135" s="9">
         <f>J79</f>
         <v/>
       </c>
-      <c r="K125" s="12">
+      <c r="K135" s="9">
         <f>K79</f>
         <v/>
       </c>
-      <c r="L125" s="12">
+      <c r="L135" s="9">
         <f>L79</f>
         <v/>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>(+) Valor de desecho</t>
         </is>
       </c>
-      <c r="B126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="12">
+      <c r="B136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="9">
         <f>L83</f>
         <v/>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>(+) Recuperación capital de trabajo</t>
         </is>
       </c>
-      <c r="B127" s="12">
+      <c r="B137" s="9">
         <f>B86</f>
         <v/>
       </c>
-      <c r="C127" s="12">
+      <c r="C137" s="9">
         <f>C86</f>
         <v/>
       </c>
-      <c r="D127" s="12">
+      <c r="D137" s="9">
         <f>D86</f>
         <v/>
       </c>
-      <c r="E127" s="12">
+      <c r="E137" s="9">
         <f>E86</f>
         <v/>
       </c>
-      <c r="F127" s="12">
+      <c r="F137" s="9">
         <f>F86</f>
         <v/>
       </c>
-      <c r="G127" s="12">
+      <c r="G137" s="9">
         <f>G86</f>
         <v/>
       </c>
-      <c r="H127" s="12">
+      <c r="H137" s="9">
         <f>H86</f>
         <v/>
       </c>
-      <c r="I127" s="12">
+      <c r="I137" s="9">
         <f>I86</f>
         <v/>
       </c>
-      <c r="J127" s="12">
+      <c r="J137" s="9">
         <f>J86</f>
         <v/>
       </c>
-      <c r="K127" s="12">
+      <c r="K137" s="9">
         <f>K86</f>
         <v/>
       </c>
-      <c r="L127" s="12">
+      <c r="L137" s="9">
         <f>L86</f>
         <v/>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>(+) Préstamo bancario (Año 0)</t>
         </is>
       </c>
-      <c r="B128" s="12">
+      <c r="B138" s="9">
         <f>D35</f>
         <v/>
       </c>
-      <c r="C128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
+      <c r="C138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>(−) Inversión en activos fijos</t>
         </is>
       </c>
-      <c r="B129" s="12">
+      <c r="B139" s="9">
         <f>SUM(B28:B33)</f>
         <v/>
       </c>
-      <c r="C129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="6" t="inlineStr">
+      <c r="C139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>(−) Inversión en capital de trabajo</t>
         </is>
       </c>
-      <c r="B130" s="12">
+      <c r="B140" s="9">
         <f>B85</f>
         <v/>
       </c>
-      <c r="C130" s="12">
+      <c r="C140" s="9">
         <f>C85</f>
         <v/>
       </c>
-      <c r="D130" s="12">
+      <c r="D140" s="9">
         <f>D85</f>
         <v/>
       </c>
-      <c r="E130" s="12">
+      <c r="E140" s="9">
         <f>E85</f>
         <v/>
       </c>
-      <c r="F130" s="12">
+      <c r="F140" s="9">
         <f>F85</f>
         <v/>
       </c>
-      <c r="G130" s="12">
+      <c r="G140" s="9">
         <f>G85</f>
         <v/>
       </c>
-      <c r="H130" s="12">
+      <c r="H140" s="9">
         <f>H85</f>
         <v/>
       </c>
-      <c r="I130" s="12">
+      <c r="I140" s="9">
         <f>I85</f>
         <v/>
       </c>
-      <c r="J130" s="12">
+      <c r="J140" s="9">
         <f>J85</f>
         <v/>
       </c>
-      <c r="K130" s="12">
+      <c r="K140" s="9">
         <f>K85</f>
         <v/>
       </c>
-      <c r="L130" s="12">
+      <c r="L140" s="9">
         <f>L85</f>
         <v/>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>(−) Abono a capital del préstamo</t>
         </is>
       </c>
-      <c r="B131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="12">
+      <c r="B141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="9">
         <f>C91</f>
         <v/>
       </c>
-      <c r="D131" s="12">
+      <c r="D141" s="9">
         <f>D91</f>
         <v/>
       </c>
-      <c r="E131" s="12">
+      <c r="E141" s="9">
         <f>E91</f>
         <v/>
       </c>
-      <c r="F131" s="12">
+      <c r="F141" s="9">
         <f>F91</f>
         <v/>
       </c>
-      <c r="G131" s="12">
+      <c r="G141" s="9">
         <f>G91</f>
         <v/>
       </c>
-      <c r="H131" s="12">
+      <c r="H141" s="9">
         <f>H91</f>
         <v/>
       </c>
-      <c r="I131" s="12">
+      <c r="I141" s="9">
         <f>I91</f>
         <v/>
       </c>
-      <c r="J131" s="12">
+      <c r="J141" s="9">
         <f>J91</f>
         <v/>
       </c>
-      <c r="K131" s="12">
+      <c r="K141" s="9">
         <f>K91</f>
         <v/>
       </c>
-      <c r="L131" s="12">
+      <c r="L141" s="9">
         <f>L91</f>
         <v/>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="15" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="12" t="inlineStr">
         <is>
           <t>(=) FLUJO DE CAJA NETO</t>
         </is>
       </c>
-      <c r="B132" s="16">
-        <f>B124+B125+B126+B127+B128-B129-B130-B131</f>
-        <v/>
-      </c>
-      <c r="C132" s="16">
-        <f>C124+C125+C126+C127+C128-C129-C130-C131</f>
-        <v/>
-      </c>
-      <c r="D132" s="16">
-        <f>D124+D125+D126+D127+D128-D129-D130-D131</f>
-        <v/>
-      </c>
-      <c r="E132" s="16">
-        <f>E124+E125+E126+E127+E128-E129-E130-E131</f>
-        <v/>
-      </c>
-      <c r="F132" s="16">
-        <f>F124+F125+F126+F127+F128-F129-F130-F131</f>
-        <v/>
-      </c>
-      <c r="G132" s="16">
-        <f>G124+G125+G126+G127+G128-G129-G130-G131</f>
-        <v/>
-      </c>
-      <c r="H132" s="16">
-        <f>H124+H125+H126+H127+H128-H129-H130-H131</f>
-        <v/>
-      </c>
-      <c r="I132" s="16">
-        <f>I124+I125+I126+I127+I128-I129-I130-I131</f>
-        <v/>
-      </c>
-      <c r="J132" s="16">
-        <f>J124+J125+J126+J127+J128-J129-J130-J131</f>
-        <v/>
-      </c>
-      <c r="K132" s="16">
-        <f>K124+K125+K126+K127+K128-K129-K130-K131</f>
-        <v/>
-      </c>
-      <c r="L132" s="16">
-        <f>L124+L125+L126+L127+L128-L129-L130-L131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="21" t="inlineStr">
+      <c r="B142" s="13">
+        <f>B134+B135+B136+B137+B138-B139-B140-B141</f>
+        <v/>
+      </c>
+      <c r="C142" s="13">
+        <f>C134+C135+C136+C137+C138-C139-C140-C141</f>
+        <v/>
+      </c>
+      <c r="D142" s="13">
+        <f>D134+D135+D136+D137+D138-D139-D140-D141</f>
+        <v/>
+      </c>
+      <c r="E142" s="13">
+        <f>E134+E135+E136+E137+E138-E139-E140-E141</f>
+        <v/>
+      </c>
+      <c r="F142" s="13">
+        <f>F134+F135+F136+F137+F138-F139-F140-F141</f>
+        <v/>
+      </c>
+      <c r="G142" s="13">
+        <f>G134+G135+G136+G137+G138-G139-G140-G141</f>
+        <v/>
+      </c>
+      <c r="H142" s="13">
+        <f>H134+H135+H136+H137+H138-H139-H140-H141</f>
+        <v/>
+      </c>
+      <c r="I142" s="13">
+        <f>I134+I135+I136+I137+I138-I139-I140-I141</f>
+        <v/>
+      </c>
+      <c r="J142" s="13">
+        <f>J134+J135+J136+J137+J138-J139-J140-J141</f>
+        <v/>
+      </c>
+      <c r="K142" s="13">
+        <f>K134+K135+K136+K137+K138-K139-K140-K141</f>
+        <v/>
+      </c>
+      <c r="L142" s="13">
+        <f>L134+L135+L136+L137+L138-L139-L140-L141</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Flujo de caja acumulado</t>
         </is>
       </c>
-      <c r="B133" s="22">
-        <f>B132</f>
-        <v/>
-      </c>
-      <c r="C133" s="22">
-        <f>B133+C132</f>
-        <v/>
-      </c>
-      <c r="D133" s="22">
-        <f>C133+D132</f>
-        <v/>
-      </c>
-      <c r="E133" s="22">
-        <f>D133+E132</f>
-        <v/>
-      </c>
-      <c r="F133" s="22">
-        <f>E133+F132</f>
-        <v/>
-      </c>
-      <c r="G133" s="22">
-        <f>F133+G132</f>
-        <v/>
-      </c>
-      <c r="H133" s="22">
-        <f>G133+H132</f>
-        <v/>
-      </c>
-      <c r="I133" s="22">
-        <f>H133+I132</f>
-        <v/>
-      </c>
-      <c r="J133" s="22">
-        <f>I133+J132</f>
-        <v/>
-      </c>
-      <c r="K133" s="22">
-        <f>J133+K132</f>
-        <v/>
-      </c>
-      <c r="L133" s="22">
-        <f>K133+L132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>11. COSTO DE CAPITAL SIN FINANCIAMIENTO</t>
-        </is>
-      </c>
-      <c r="B135" s="27" t="n"/>
-      <c r="C135" s="27" t="n"/>
-      <c r="D135" s="27" t="n"/>
-      <c r="E135" s="27" t="n"/>
-      <c r="F135" s="27" t="n"/>
-      <c r="G135" s="27" t="n"/>
-      <c r="H135" s="27" t="n"/>
-      <c r="I135" s="27" t="n"/>
-      <c r="J135" s="27" t="n"/>
-      <c r="K135" s="27" t="n"/>
-      <c r="L135" s="28" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>Monto</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>Participación</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Costo</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="inlineStr">
-        <is>
-          <t>Costo ponderado</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
-      <c r="J136" s="4" t="n"/>
-      <c r="K136" s="4" t="n"/>
-      <c r="L136" s="4" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>Recursos propios</t>
-        </is>
-      </c>
-      <c r="B137" s="12">
-        <f>B35</f>
-        <v/>
-      </c>
-      <c r="C137" s="23">
-        <f>B137/B138</f>
-        <v/>
-      </c>
-      <c r="D137" s="23">
-        <f>$B$12</f>
-        <v/>
-      </c>
-      <c r="E137" s="23">
-        <f>C137*D137</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="inlineStr">
-        <is>
-          <t>Tasa de descuento del proyecto</t>
-        </is>
-      </c>
-      <c r="B138" s="16">
-        <f>B137</f>
-        <v/>
-      </c>
-      <c r="C138" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E138" s="24">
-        <f>E137</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>12. INDICADORES FINANCIEROS SIN FINANCIAMIENTO</t>
-        </is>
-      </c>
-      <c r="B140" s="27" t="n"/>
-      <c r="C140" s="27" t="n"/>
-      <c r="D140" s="27" t="n"/>
-      <c r="E140" s="27" t="n"/>
-      <c r="F140" s="27" t="n"/>
-      <c r="G140" s="27" t="n"/>
-      <c r="H140" s="27" t="n"/>
-      <c r="I140" s="27" t="n"/>
-      <c r="J140" s="27" t="n"/>
-      <c r="K140" s="27" t="n"/>
-      <c r="L140" s="28" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="21" t="inlineStr">
-        <is>
-          <t>VAN</t>
-        </is>
-      </c>
-      <c r="B141" s="8">
-        <f>NPV(E138,C111:L111)+B111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="21" t="inlineStr">
-        <is>
-          <t>TIRM</t>
-        </is>
-      </c>
-      <c r="B142" s="7">
-        <f>MIRR(B111:L111,E138,E138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="21" t="inlineStr">
-        <is>
-          <t>PRI (años)</t>
-        </is>
-      </c>
       <c r="B143" s="9">
-        <f>IF(COUNTIF(B112:L112,"&lt;0")=11,"&gt;10",(COUNTIF(B112:L112,"&lt;0")-1)+(-INDEX(B112:L112,COUNTIF(B112:L112,"&lt;0")))/INDEX(B111:L111,COUNTIF(B112:L112,"&lt;0")+1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="21" t="inlineStr">
-        <is>
-          <t>Relación Beneficio/Costo</t>
-        </is>
-      </c>
-      <c r="B144" s="9">
-        <f>NPV(E138,C42:L42)/(B35+NPV(E138,C49:L49)+NPV(E138,C69:L69)+NPV(E138,C104:L104))</f>
-        <v/>
+        <f>B142</f>
+        <v/>
+      </c>
+      <c r="C143" s="9">
+        <f>B143+C142</f>
+        <v/>
+      </c>
+      <c r="D143" s="9">
+        <f>C143+D142</f>
+        <v/>
+      </c>
+      <c r="E143" s="9">
+        <f>D143+E142</f>
+        <v/>
+      </c>
+      <c r="F143" s="9">
+        <f>E143+F142</f>
+        <v/>
+      </c>
+      <c r="G143" s="9">
+        <f>F143+G142</f>
+        <v/>
+      </c>
+      <c r="H143" s="9">
+        <f>G143+H142</f>
+        <v/>
+      </c>
+      <c r="I143" s="9">
+        <f>H143+I142</f>
+        <v/>
+      </c>
+      <c r="J143" s="9">
+        <f>I143+J142</f>
+        <v/>
+      </c>
+      <c r="K143" s="9">
+        <f>J143+K142</f>
+        <v/>
+      </c>
+      <c r="L143" s="9">
+        <f>K143+L142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>12. COSTO DE CAPITAL SIN FINANCIAMIENTO</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>13. COSTO DE CAPITAL CON FINANCIAMIENTO (WACC)</t>
-        </is>
-      </c>
-      <c r="B146" s="27" t="n"/>
-      <c r="C146" s="27" t="n"/>
-      <c r="D146" s="27" t="n"/>
-      <c r="E146" s="27" t="n"/>
-      <c r="F146" s="27" t="n"/>
-      <c r="G146" s="27" t="n"/>
-      <c r="H146" s="27" t="n"/>
-      <c r="I146" s="27" t="n"/>
-      <c r="J146" s="27" t="n"/>
-      <c r="K146" s="27" t="n"/>
-      <c r="L146" s="28" t="n"/>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Monto</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Participación</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Costo ponderado</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Recursos propios</t>
+        </is>
+      </c>
+      <c r="B147" s="9">
+        <f>B35</f>
+        <v/>
+      </c>
+      <c r="C147" s="15">
+        <f>B147/B148</f>
+        <v/>
+      </c>
+      <c r="D147" s="15">
+        <f>$B$12</f>
+        <v/>
+      </c>
+      <c r="E147" s="15">
+        <f>C147*D147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>Tasa de descuento del proyecto</t>
+        </is>
+      </c>
+      <c r="B148" s="13">
+        <f>B147</f>
+        <v/>
+      </c>
+      <c r="C148" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" s="16">
+        <f>E147</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>13. INDICADORES FINANCIEROS SIN FINANCIAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="B151" s="6">
+        <f>NPV(E148,C121:L121)+B121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>TIRM</t>
+        </is>
+      </c>
+      <c r="B152" s="5">
+        <f>MIRR(B121:L121,E148,E148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>PRI (años)</t>
+        </is>
+      </c>
+      <c r="B153" s="18">
+        <f>IF(COUNTIF(B122:L122,"&lt;0")=11,"&gt;10",(COUNTIF(B122:L122,"&lt;0")-1)+(-INDEX(B122:L122,COUNTIF(B122:L122,"&lt;0")))/INDEX(B121:L121,COUNTIF(B122:L122,"&lt;0")+1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>Relación Beneficio/Costo</t>
+        </is>
+      </c>
+      <c r="B154" s="18">
+        <f>NPV(E148,C42:L42)/(B35+NPV(E148,C49:L49)+NPV(E148,C69:L69)+NPV(E148,C104:L104)+NPV(E148,C114:L114))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>14. COSTO DE CAPITAL CON FINANCIAMIENTO (WACC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t>Monto</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>Participación</t>
         </is>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
         <is>
           <t>Costo ponderado</t>
         </is>
       </c>
-      <c r="F147" s="4" t="n"/>
-      <c r="G147" s="4" t="n"/>
-      <c r="H147" s="4" t="n"/>
-      <c r="I147" s="4" t="n"/>
-      <c r="J147" s="4" t="n"/>
-      <c r="K147" s="4" t="n"/>
-      <c r="L147" s="4" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Préstamo bancario</t>
         </is>
       </c>
-      <c r="B148" s="12">
+      <c r="B158" s="9">
         <f>D35</f>
         <v/>
       </c>
-      <c r="C148" s="23">
-        <f>B148/B150</f>
-        <v/>
-      </c>
-      <c r="D148" s="23">
+      <c r="C158" s="15">
+        <f>B158/B160</f>
+        <v/>
+      </c>
+      <c r="D158" s="15">
         <f>$B$9*(1-$B$6)</f>
         <v/>
       </c>
-      <c r="E148" s="23">
-        <f>C148*D148</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
+      <c r="E158" s="15">
+        <f>C158*D158</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Recursos propios</t>
         </is>
       </c>
-      <c r="B149" s="12">
+      <c r="B159" s="9">
         <f>C35</f>
         <v/>
       </c>
-      <c r="C149" s="23">
-        <f>B149/B150</f>
-        <v/>
-      </c>
-      <c r="D149" s="23">
+      <c r="C159" s="15">
+        <f>B159/B160</f>
+        <v/>
+      </c>
+      <c r="D159" s="15">
         <f>$B$12</f>
         <v/>
       </c>
-      <c r="E149" s="23">
-        <f>C149*D149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="inlineStr">
+      <c r="E159" s="15">
+        <f>C159*D159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B150" s="16">
-        <f>B148+B149</f>
-        <v/>
-      </c>
-      <c r="C150" s="24" t="n">
+      <c r="B160" s="13">
+        <f>B158+B159</f>
+        <v/>
+      </c>
+      <c r="C160" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D150" s="25" t="inlineStr">
+      <c r="D160" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E150" s="24">
-        <f>E148+E149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>14. INDICADORES FINANCIEROS CON FINANCIAMIENTO</t>
-        </is>
-      </c>
-      <c r="B152" s="27" t="n"/>
-      <c r="C152" s="27" t="n"/>
-      <c r="D152" s="27" t="n"/>
-      <c r="E152" s="27" t="n"/>
-      <c r="F152" s="27" t="n"/>
-      <c r="G152" s="27" t="n"/>
-      <c r="H152" s="27" t="n"/>
-      <c r="I152" s="27" t="n"/>
-      <c r="J152" s="27" t="n"/>
-      <c r="K152" s="27" t="n"/>
-      <c r="L152" s="28" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="21" t="inlineStr">
+      <c r="E160" s="16">
+        <f>E158+E159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>15. INDICADORES FINANCIEROS CON FINANCIAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
         <is>
           <t>VAN</t>
         </is>
       </c>
-      <c r="B153" s="8">
-        <f>NPV(E150,C132:L132)+B132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="21" t="inlineStr">
+      <c r="B163" s="6">
+        <f>NPV(E160,C142:L142)+B142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
         <is>
           <t>TIRM</t>
         </is>
       </c>
-      <c r="B154" s="7">
-        <f>MIRR(B132:L132,E150,E150)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="21" t="inlineStr">
+      <c r="B164" s="5">
+        <f>MIRR(B142:L142,E160,E160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
         <is>
           <t>PRI (años)</t>
         </is>
       </c>
-      <c r="B155" s="9">
-        <f>IF(COUNTIF(B133:L133,"&lt;0")=11,"&gt;10",(COUNTIF(B133:L133,"&lt;0")-1)+(-INDEX(B133:L133,COUNTIF(B133:L133,"&lt;0")))/INDEX(B132:L132,COUNTIF(B133:L133,"&lt;0")+1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="21" t="inlineStr">
+      <c r="B165" s="18">
+        <f>IF(COUNTIF(B143:L143,"&lt;0")=11,"&gt;10",(COUNTIF(B143:L143,"&lt;0")-1)+(-INDEX(B143:L143,COUNTIF(B143:L143,"&lt;0")))/INDEX(B142:L142,COUNTIF(B143:L143,"&lt;0")+1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
         <is>
           <t>Relación Beneficio/Costo</t>
         </is>
       </c>
-      <c r="B156" s="9">
-        <f>NPV(E150,C42:L42)/(C35+NPV(E150,C49:L49)+NPV(E150,C69:L69)+NPV(E150,C119:L119)+NPV(E150,C123:L123)+NPV(E150,C131:L131))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>15. NOTAS LEGALES (cumplimiento normativo Honduras)</t>
-        </is>
-      </c>
-      <c r="B158" s="27" t="n"/>
-      <c r="C158" s="27" t="n"/>
-      <c r="D158" s="27" t="n"/>
-      <c r="E158" s="27" t="n"/>
-      <c r="F158" s="27" t="n"/>
-      <c r="G158" s="27" t="n"/>
-      <c r="H158" s="27" t="n"/>
-      <c r="I158" s="27" t="n"/>
-      <c r="J158" s="27" t="n"/>
-      <c r="K158" s="27" t="n"/>
-      <c r="L158" s="28" t="n"/>
-    </row>
-    <row r="159" ht="30" customHeight="1">
-      <c r="A159" s="26" t="inlineStr">
+      <c r="B166" s="18">
+        <f>NPV(E160,C42:L42)/(C35+NPV(E160,C49:L49)+NPV(E160,C69:L69)+NPV(E160,C104:L104)+NPV(E160,C129:L129)+NPV(E160,C133:L133)+NPV(E160,C141:L141))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>16. NOTAS LEGALES (cumplimiento normativo Honduras)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="19" t="inlineStr">
         <is>
           <t>• ISR: 25% + aportación solidaria 5% sobre el excedente de L 1,000,000 (Ley del ISR).</t>
         </is>
       </c>
-      <c r="B159" s="27" t="n"/>
-      <c r="C159" s="27" t="n"/>
-      <c r="D159" s="27" t="n"/>
-      <c r="E159" s="27" t="n"/>
-      <c r="F159" s="27" t="n"/>
-      <c r="G159" s="27" t="n"/>
-      <c r="H159" s="27" t="n"/>
-      <c r="I159" s="27" t="n"/>
-      <c r="J159" s="27" t="n"/>
-      <c r="K159" s="27" t="n"/>
-      <c r="L159" s="28" t="n"/>
-    </row>
-    <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="26" t="inlineStr">
-        <is>
-          <t>• Depreciación línea recta: maquinaria 10%; vehículos 10%-33% (aquí 20% = 5 años); diferidos 5 años.</t>
-        </is>
-      </c>
-      <c r="B160" s="27" t="n"/>
-      <c r="C160" s="27" t="n"/>
-      <c r="D160" s="27" t="n"/>
-      <c r="E160" s="27" t="n"/>
-      <c r="F160" s="27" t="n"/>
-      <c r="G160" s="27" t="n"/>
-      <c r="H160" s="27" t="n"/>
-      <c r="I160" s="27" t="n"/>
-      <c r="J160" s="27" t="n"/>
-      <c r="K160" s="27" t="n"/>
-      <c r="L160" s="28" t="n"/>
-    </row>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="26" t="inlineStr">
+    </row>
+    <row r="170">
+      <c r="A170" s="19" t="inlineStr">
+        <is>
+          <t>• Depreciación línea recta: maquinaria 10%; vehículos 10% a 33% (aquí 20% = 5 años); diferidos 5 años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="19" t="inlineStr">
         <is>
           <t>• Seguridad social patronal (techo L 11,109.36): IHSS EM 5% + IVM 2% + RP 0.2% = 7.2%; INFOP 1% sobre planilla sin techo. El RAP (1.5%) es opcional desde el fallo de 2022.</t>
         </is>
       </c>
-      <c r="B161" s="27" t="n"/>
-      <c r="C161" s="27" t="n"/>
-      <c r="D161" s="27" t="n"/>
-      <c r="E161" s="27" t="n"/>
-      <c r="F161" s="27" t="n"/>
-      <c r="G161" s="27" t="n"/>
-      <c r="H161" s="27" t="n"/>
-      <c r="I161" s="27" t="n"/>
-      <c r="J161" s="27" t="n"/>
-      <c r="K161" s="27" t="n"/>
-      <c r="L161" s="28" t="n"/>
-    </row>
-    <row r="162" ht="30" customHeight="1">
-      <c r="A162" s="26" t="inlineStr">
+    </row>
+    <row r="172">
+      <c r="A172" s="19" t="inlineStr">
         <is>
           <t>• Prestaciones: aguinaldo (13.º mes) y catorceavo (14.º mes), Código del Trabajo.</t>
         </is>
       </c>
-      <c r="B162" s="27" t="n"/>
-      <c r="C162" s="27" t="n"/>
-      <c r="D162" s="27" t="n"/>
-      <c r="E162" s="27" t="n"/>
-      <c r="F162" s="27" t="n"/>
-      <c r="G162" s="27" t="n"/>
-      <c r="H162" s="27" t="n"/>
-      <c r="I162" s="27" t="n"/>
-      <c r="J162" s="27" t="n"/>
-      <c r="K162" s="27" t="n"/>
-      <c r="L162" s="28" t="n"/>
-    </row>
-    <row r="163" ht="30" customHeight="1">
-      <c r="A163" s="26" t="inlineStr">
-        <is>
-          <t>• ISV: la leche fluida/pasteurizada está exenta; no se cobra ISV en ventas.</t>
-        </is>
-      </c>
-      <c r="B163" s="27" t="n"/>
-      <c r="C163" s="27" t="n"/>
-      <c r="D163" s="27" t="n"/>
-      <c r="E163" s="27" t="n"/>
-      <c r="F163" s="27" t="n"/>
-      <c r="G163" s="27" t="n"/>
-      <c r="H163" s="27" t="n"/>
-      <c r="I163" s="27" t="n"/>
-      <c r="J163" s="27" t="n"/>
-      <c r="K163" s="27" t="n"/>
-      <c r="L163" s="28" t="n"/>
-    </row>
-    <row r="164" ht="30" customHeight="1">
-      <c r="A164" s="26" t="inlineStr">
-        <is>
-          <t>• Arrastre de pérdidas fiscales: la manufactura puede compensarlas hasta 3 años (aplicado en el flujo, línea de pérdidas acumuladas).</t>
-        </is>
-      </c>
-      <c r="B164" s="27" t="n"/>
-      <c r="C164" s="27" t="n"/>
-      <c r="D164" s="27" t="n"/>
-      <c r="E164" s="27" t="n"/>
-      <c r="F164" s="27" t="n"/>
-      <c r="G164" s="27" t="n"/>
-      <c r="H164" s="27" t="n"/>
-      <c r="I164" s="27" t="n"/>
-      <c r="J164" s="27" t="n"/>
-      <c r="K164" s="27" t="n"/>
-      <c r="L164" s="28" t="n"/>
-    </row>
-    <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="26" t="inlineStr">
-        <is>
-          <t>• Impuesto al Activo Neto 1% (deducción L3M; exento en preoperación; se paga solo si supera al ISR).</t>
-        </is>
-      </c>
-      <c r="B165" s="27" t="n"/>
-      <c r="C165" s="27" t="n"/>
-      <c r="D165" s="27" t="n"/>
-      <c r="E165" s="27" t="n"/>
-      <c r="F165" s="27" t="n"/>
-      <c r="G165" s="27" t="n"/>
-      <c r="H165" s="27" t="n"/>
-      <c r="I165" s="27" t="n"/>
-      <c r="J165" s="27" t="n"/>
-      <c r="K165" s="27" t="n"/>
-      <c r="L165" s="28" t="n"/>
-    </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="26" t="inlineStr">
-        <is>
-          <t>• Capital de trabajo: 1 mes de costos operativos, financiado con crédito de proveedores (CREL/ganaderos).</t>
-        </is>
-      </c>
-      <c r="B166" s="27" t="n"/>
-      <c r="C166" s="27" t="n"/>
-      <c r="D166" s="27" t="n"/>
-      <c r="E166" s="27" t="n"/>
-      <c r="F166" s="27" t="n"/>
-      <c r="G166" s="27" t="n"/>
-      <c r="H166" s="27" t="n"/>
-      <c r="I166" s="27" t="n"/>
-      <c r="J166" s="27" t="n"/>
-      <c r="K166" s="27" t="n"/>
-      <c r="L166" s="28" t="n"/>
-    </row>
-    <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="26" t="inlineStr">
-        <is>
-          <t>• Impuesto municipal de Comayagua: Industria, Comercio y Servicios sobre ingresos (Art. 78, escala por millar); el Impuesto sobre Bienes Inmuebles no se cuantifica por ser terreno e instalación propios sin avalúo catastral.</t>
-        </is>
-      </c>
-      <c r="B167" s="27" t="n"/>
-      <c r="C167" s="27" t="n"/>
-      <c r="D167" s="27" t="n"/>
-      <c r="E167" s="27" t="n"/>
-      <c r="F167" s="27" t="n"/>
-      <c r="G167" s="27" t="n"/>
-      <c r="H167" s="27" t="n"/>
-      <c r="I167" s="27" t="n"/>
-      <c r="J167" s="27" t="n"/>
-      <c r="K167" s="27" t="n"/>
-      <c r="L167" s="28" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>16. IMPUESTO MUNICIPAL DE COMAYAGUA (ICS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>Impuesto de Industria, Comercio y Servicios (sobre ingresos, Art. 78 Ley de Municipalidades)</t>
-        </is>
-      </c>
-      <c r="B170" s="12">
-        <f>0.3/1000*MIN(B42,500000)+0.4/1000*MAX(0,MIN(B42,10000000)-500000)+0.3/1000*MAX(0,MIN(B42,20000000)-10000000)+0.2/1000*MAX(0,MIN(B42,30000000)-20000000)+0.15/1000*MAX(0,B42-30000000)</f>
-        <v/>
-      </c>
-      <c r="C170" s="12">
-        <f>0.3/1000*MIN(C42,500000)+0.4/1000*MAX(0,MIN(C42,10000000)-500000)+0.3/1000*MAX(0,MIN(C42,20000000)-10000000)+0.2/1000*MAX(0,MIN(C42,30000000)-20000000)+0.15/1000*MAX(0,C42-30000000)</f>
-        <v/>
-      </c>
-      <c r="D170" s="12">
-        <f>0.3/1000*MIN(D42,500000)+0.4/1000*MAX(0,MIN(D42,10000000)-500000)+0.3/1000*MAX(0,MIN(D42,20000000)-10000000)+0.2/1000*MAX(0,MIN(D42,30000000)-20000000)+0.15/1000*MAX(0,D42-30000000)</f>
-        <v/>
-      </c>
-      <c r="E170" s="12">
-        <f>0.3/1000*MIN(E42,500000)+0.4/1000*MAX(0,MIN(E42,10000000)-500000)+0.3/1000*MAX(0,MIN(E42,20000000)-10000000)+0.2/1000*MAX(0,MIN(E42,30000000)-20000000)+0.15/1000*MAX(0,E42-30000000)</f>
-        <v/>
-      </c>
-      <c r="F170" s="12">
-        <f>0.3/1000*MIN(F42,500000)+0.4/1000*MAX(0,MIN(F42,10000000)-500000)+0.3/1000*MAX(0,MIN(F42,20000000)-10000000)+0.2/1000*MAX(0,MIN(F42,30000000)-20000000)+0.15/1000*MAX(0,F42-30000000)</f>
-        <v/>
-      </c>
-      <c r="G170" s="12">
-        <f>0.3/1000*MIN(G42,500000)+0.4/1000*MAX(0,MIN(G42,10000000)-500000)+0.3/1000*MAX(0,MIN(G42,20000000)-10000000)+0.2/1000*MAX(0,MIN(G42,30000000)-20000000)+0.15/1000*MAX(0,G42-30000000)</f>
-        <v/>
-      </c>
-      <c r="H170" s="12">
-        <f>0.3/1000*MIN(H42,500000)+0.4/1000*MAX(0,MIN(H42,10000000)-500000)+0.3/1000*MAX(0,MIN(H42,20000000)-10000000)+0.2/1000*MAX(0,MIN(H42,30000000)-20000000)+0.15/1000*MAX(0,H42-30000000)</f>
-        <v/>
-      </c>
-      <c r="I170" s="12">
-        <f>0.3/1000*MIN(I42,500000)+0.4/1000*MAX(0,MIN(I42,10000000)-500000)+0.3/1000*MAX(0,MIN(I42,20000000)-10000000)+0.2/1000*MAX(0,MIN(I42,30000000)-20000000)+0.15/1000*MAX(0,I42-30000000)</f>
-        <v/>
-      </c>
-      <c r="J170" s="12">
-        <f>0.3/1000*MIN(J42,500000)+0.4/1000*MAX(0,MIN(J42,10000000)-500000)+0.3/1000*MAX(0,MIN(J42,20000000)-10000000)+0.2/1000*MAX(0,MIN(J42,30000000)-20000000)+0.15/1000*MAX(0,J42-30000000)</f>
-        <v/>
-      </c>
-      <c r="K170" s="12">
-        <f>0.3/1000*MIN(K42,500000)+0.4/1000*MAX(0,MIN(K42,10000000)-500000)+0.3/1000*MAX(0,MIN(K42,20000000)-10000000)+0.2/1000*MAX(0,MIN(K42,30000000)-20000000)+0.15/1000*MAX(0,K42-30000000)</f>
-        <v/>
-      </c>
-      <c r="L170" s="12">
-        <f>0.3/1000*MIN(L42,500000)+0.4/1000*MAX(0,MIN(L42,10000000)-500000)+0.3/1000*MAX(0,MIN(L42,20000000)-10000000)+0.2/1000*MAX(0,MIN(L42,30000000)-20000000)+0.15/1000*MAX(0,L42-30000000)</f>
-        <v/>
+    </row>
+    <row r="173">
+      <c r="A173" s="19" t="inlineStr">
+        <is>
+          <t>• ISV: la leche fluida pasteurizada está exenta; no se cobra ISV en ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="19" t="inlineStr">
+        <is>
+          <t>• Arrastre de pérdidas fiscales: la manufactura puede compensarlas hasta 3 años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
+        <is>
+          <t>• Impuesto municipal de Comayagua: Industria, Comercio y Servicios sobre ingresos (Art. 78, escala por millar de la sección 9); el Impuesto sobre Bienes Inmuebles no se cuantifica por ser terreno e instalación propios sin avalúo catastral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="19" t="inlineStr">
+        <is>
+          <t>• Capital de trabajo: 1 mes de costos operativos, financiado con crédito de proveedores.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="D57:L57"/>
-    <mergeCell ref="A164:L164"/>
+  <mergeCells count="25">
+    <mergeCell ref="A172:L172"/>
+    <mergeCell ref="A174:L174"/>
     <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A158:L158"/>
-    <mergeCell ref="D53:L53"/>
-    <mergeCell ref="A163:L163"/>
+    <mergeCell ref="A145:L145"/>
     <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A175:L175"/>
     <mergeCell ref="A71:L71"/>
-    <mergeCell ref="A160:L160"/>
-    <mergeCell ref="D56:L56"/>
-    <mergeCell ref="D58:L58"/>
-    <mergeCell ref="A159:L159"/>
-    <mergeCell ref="A135:L135"/>
-    <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A150:L150"/>
+    <mergeCell ref="A106:L106"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="D55:L55"/>
     <mergeCell ref="A81:L81"/>
     <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A165:L165"/>
-    <mergeCell ref="A161:L161"/>
-    <mergeCell ref="A152:L152"/>
-    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="A156:L156"/>
+    <mergeCell ref="A171:L171"/>
+    <mergeCell ref="A170:L170"/>
     <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A167:L167"/>
-    <mergeCell ref="D59:L59"/>
-    <mergeCell ref="A114:L114"/>
+    <mergeCell ref="A173:L173"/>
+    <mergeCell ref="A176:L176"/>
     <mergeCell ref="A64:L64"/>
-    <mergeCell ref="A166:L166"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A169:L169"/>
     <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A168:L168"/>
     <mergeCell ref="A88:L88"/>
-    <mergeCell ref="A146:L146"/>
     <mergeCell ref="A162:L162"/>
-    <mergeCell ref="C60:L60"/>
-    <mergeCell ref="D52:L52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5753,200 +5598,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Explicación del Estudio Financiero</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Productora de Leche Pasteurizada «Pura»</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="31" t="inlineStr"/>
+      <c r="A3" s="22" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>El estudio mide si conviene montar la planta de leche pasteurizada Pura. Proyecta los ingresos, los costos y el flujo de caja del proyecto durante diez años y calcula los indicadores de rentabilidad en dos escenarios: financiado con recursos propios y financiado con préstamo bancario.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr"/>
+      <c r="A6" s="22" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Supuestos base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Todas las cifras están en Lempiras. La inflación anual es de 4.5% y se aplica por igual a los precios de venta y a los costos, para que el margen del negocio no se distorsione. El impuesto sobre la renta es de 25%, más una aportación solidaria de 5% sobre la parte de la utilidad que supera un millón de Lempiras. El proyecto se financia mitad con préstamo bancario al 14% anual y mitad con recursos propios. La tasa de descuento del escenario sin financiamiento es de 15% y el costo promedio ponderado de capital del escenario con financiamiento es de 12.75%.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr"/>
+      <c r="A9" s="22" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Cómo se construye el estudio</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>1. Plan de inversiones. Reúne la maquinaria, el camión, los gastos diferidos y el capital de trabajo inicial. La inversión total es de 1,784,058 Lempiras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>2. Producción y ventas. El volumen se obtiene multiplicando los clientes por el consumo mensual de 150 litros y por 12 meses. El precio parte de 28 Lempiras por litro y sube cada año con la inflación.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>3. Costos variables. Incluyen la leche cruda con merma, el empaque y el combustible de reparto. Crecen con el volumen y con la inflación.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>4. Costo de personal. Seis puestos con salario, aguinaldo, catorceavo mes y las cargas de seguridad social calculadas sobre el techo de cotización de ley.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>5. Costos fijos. Reúnen los costos fijos operativos, los gastos administrativos y el personal, todos ajustados por inflación.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>6. Depreciación y amortización. Se calcula por línea recta. La maquinaria se deprecia en diez años, el camión en cinco años y los gastos diferidos se amortizan en cinco años.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>7. Valor de desecho y capital de trabajo. El capital de trabajo equivale a un mes de costos operativos y se recupera en el último año.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>8. Amortización del préstamo. Muestra la cuota anual fija, los intereses y los abonos a capital del préstamo bancario a cinco años.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>9 y 10. Flujo de caja. Arma el flujo del proyecto sin financiamiento y con financiamiento. A la utilidad se le restan los impuestos, aprovechando el arrastre de pérdidas de los primeros años, y se le suman las partidas que no son salida de efectivo, como la depreciación.</t>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>9. Impuesto municipal de Comayagua. Calcula el Impuesto de Industria, Comercio y Servicios sobre los ingresos anuales. Se desglosa en cinco tramos, cada uno con su tarifa por millar según la Ley de Municipalidades, y luego se suman.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>11 a 14. Costo de capital e indicadores. Con la tasa de descuento y el WACC se calculan el VAN, la TIRM, el período de recuperación y la relación beneficio/costo en los dos escenarios.</t>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>10 y 11. Flujo de caja. Arma el flujo del proyecto sin financiamiento y con financiamiento. A la utilidad se le restan los impuestos, aprovechando el arrastre de pérdidas de los primeros años, y se le suman las partidas que no son salida de efectivo, como la depreciación.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr"/>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>12 a 15. Costo de capital e indicadores. Con la tasa de descuento y el WACC se calculan el VAN, la TIRM, el período de recuperación y la relación beneficio/costo en los dos escenarios.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Qué significan los indicadores</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>El VAN es el valor de hoy de todo el efectivo que deja el proyecto después de cubrir la inversión; si es positivo, el proyecto crea valor. La TIRM es el rendimiento anual del proyecto suponiendo que las ganancias se reinvierten al costo de capital, por lo que resulta más realista que la TIR simple. El PRI es el tiempo, en años, que tarda en recuperarse la inversión. La relación beneficio/costo compara el valor presente de los ingresos con el de los egresos; si es mayor que uno, conviene invertir.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Resultados</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Sin financiamiento: VAN de 15,370,632 Lempiras, TIRM de 40.38%, recuperación en 3.67 años y relación beneficio/costo de 1.23.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Con financiamiento: VAN de 18,261,296 Lempiras, TIRM de 42.46%, recuperación en 3.66 años y relación beneficio/costo de 1.24.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>En los dos escenarios el proyecto recupera la inversión antes de cuatro años y rinde por encima de la tasa exigida, por lo que es financieramente viable.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="31" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Cumplimiento legal en Honduras</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>El estudio aplica el impuesto sobre la renta de 25% más 5% de aportación solidaria, la depreciación por línea recta permitida por el reglamento (vehículos entre 10% y 33%, aquí 20%), la seguridad social patronal del 7.2% al IHSS más 1% de INFOP con su techo de cotización, el aguinaldo y el catorceavo mes del Código del Trabajo, la exención del impuesto sobre ventas para la leche fluida, el arrastre de pérdidas de hasta tres años para la manufactura, y el impuesto municipal de Comayagua de Industria, Comercio y Servicios sobre los ingresos anuales según la escala de la Ley de Municipalidades.</t>
         </is>

--- a/Estudio_Financiero_Pura.xlsx
+++ b/Estudio_Financiero_Pura.xlsx
@@ -742,7 +742,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Meses de capital de trabajo (crédito de proveedores)</t>
+          <t>Meses de capital de trabajo</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
@@ -5556,7 +5556,7 @@
     <row r="176">
       <c r="A176" s="19" t="inlineStr">
         <is>
-          <t>• Capital de trabajo: 1 mes de costos operativos, financiado con crédito de proveedores.</t>
+          <t>• Capital de trabajo: equivale a 1 mes de costos operativos; forma parte de la inversión inicial (financiada 50% con préstamo y 50% con recursos propios) y se recupera en el año 10.</t>
         </is>
       </c>
     </row>
